--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqzk</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2645</v>
+        <v>142</v>
       </c>
       <c r="Q2" t="n">
-        <v>4698</v>
+        <v>532</v>
       </c>
       <c r="R2" t="n">
-        <v>7343</v>
+        <v>674</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,29 +657,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/herricane</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47wce</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,17 +813,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="R4" t="n">
-        <v>402</v>
+        <v>116</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/axis_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,23 +886,27 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4toem</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="Q5" t="n">
-        <v>30</v>
+        <v>243</v>
       </c>
       <c r="R5" t="n">
-        <v>49</v>
+        <v>359</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,24 +952,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jggy</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,17 +1009,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>233</v>
       </c>
       <c r="R6" t="n">
-        <v>44</v>
+        <v>318</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>codelegend@naver.com</t>
+          <t>hegardengym_suyu-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pressgym___</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49479</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="R7" t="n">
-        <v>267</v>
+        <v>92</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>NH FITNESS CLUB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/highend_gym/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,17 +1201,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1793</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>1235</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3028</v>
+        <v>8</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>honeymusclegym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/curves</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,20 +1274,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t1ci</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="R9" t="n">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,23 +1372,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwrhsu4</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1704</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
-        <v>363</v>
+        <v>31</v>
       </c>
       <c r="R10" t="n">
-        <v>2067</v>
+        <v>50</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trend_hd4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1442,20 +1470,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wqdd</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2234</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="n">
-        <v>1394</v>
+        <v>210</v>
       </c>
       <c r="R11" t="n">
-        <v>3628</v>
+        <v>238</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,39 +1536,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>godgod9193@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1552,7 +1584,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>319</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>569</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>888</v>
+        <v>10</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1608,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1598,29 +1630,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>godgod9193@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjfit_7707</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1630,7 +1662,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1651,17 +1683,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,12 +1702,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1692,24 +1724,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1734,10 +1766,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v4ny</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1745,17 +1781,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1793</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>1227</v>
       </c>
       <c r="R14" t="n">
-        <v>10</v>
+        <v>3020</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,12 +1800,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1786,29 +1822,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifeplus_bd/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1818,7 +1854,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1828,10 +1864,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rzh6</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1843,13 +1883,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>687</v>
+        <v>612</v>
       </c>
       <c r="Q15" t="n">
-        <v>138</v>
+        <v>339</v>
       </c>
       <c r="R15" t="n">
-        <v>825</v>
+        <v>951</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,12 +1898,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1880,20 +1920,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>가인헬스클럽</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1419-2268</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1933,13 +1977,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,12 +1992,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1970,24 +2014,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>io15io15@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2012,28 +2056,32 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41vr7</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>461</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>682</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2090,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2064,29 +2112,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blueskirt0704</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2096,23 +2144,27 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yudn</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2173,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>142</v>
+        <v>464</v>
       </c>
       <c r="Q18" t="n">
-        <v>539</v>
+        <v>785</v>
       </c>
       <c r="R18" t="n">
-        <v>681</v>
+        <v>1249</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,12 +2188,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2158,44 +2210,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2206,22 +2258,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>239</v>
+        <v>38</v>
       </c>
       <c r="Q19" t="n">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="R19" t="n">
-        <v>345</v>
+        <v>54</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,12 +2282,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2252,29 +2304,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>더블플러스휘트니스클럽</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h9a1n94</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2284,12 +2336,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,17 +2357,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="Q20" t="n">
-        <v>334</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>449</v>
+        <v>13</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,12 +2376,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2346,34 +2398,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>419gym@naver.com</t>
+          <t>fa_sport@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/419gym_official</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2383,7 +2435,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2394,7 +2446,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2403,13 +2455,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>37</v>
+        <v>239</v>
       </c>
       <c r="Q21" t="n">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="R21" t="n">
-        <v>92</v>
+        <v>345</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,12 +2470,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2440,29 +2492,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>acrogym1@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acrogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2472,12 +2524,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2493,17 +2545,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1923</v>
+        <v>40</v>
       </c>
       <c r="Q22" t="n">
-        <v>821</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>2744</v>
+        <v>44</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,12 +2564,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2534,29 +2586,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,7 +2618,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2576,10 +2628,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e814</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2591,13 +2647,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>112</v>
+        <v>2649</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>4706</v>
       </c>
       <c r="R23" t="n">
-        <v>117</v>
+        <v>7355</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,12 +2662,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2628,29 +2684,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1478-5103</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2660,20 +2712,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy43x6v</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>O</t>
@@ -2685,13 +2741,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>221</v>
+        <v>89</v>
       </c>
       <c r="Q24" t="n">
-        <v>466</v>
+        <v>158</v>
       </c>
       <c r="R24" t="n">
-        <v>687</v>
+        <v>247</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,12 +2756,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2722,29 +2778,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>junggyo777@naver.com</t>
+          <t>pressgym@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team_whale_mia</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2754,7 +2810,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2764,10 +2820,14 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8bi</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2779,13 +2839,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>114</v>
+        <v>229</v>
       </c>
       <c r="Q25" t="n">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="R25" t="n">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,12 +2854,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2816,29 +2876,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2848,20 +2908,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9thbkj</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2873,13 +2937,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,12 +2952,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2905,35 +2969,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>thebarunpt@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>02-986-2534</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2948,10 +3016,14 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7sz75u</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>X</t>
@@ -2963,13 +3035,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="Q27" t="n">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="R27" t="n">
-        <v>279</v>
+        <v>183</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,12 +3050,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3000,24 +3072,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3042,10 +3114,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdf2zxw</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3057,13 +3133,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="R28" t="n">
-        <v>13</v>
+        <v>310</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,12 +3148,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3094,24 +3170,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nicenet@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3147,17 +3223,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1311</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>882</v>
       </c>
       <c r="R29" t="n">
-        <v>12</v>
+        <v>2193</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,12 +3242,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3183,29 +3259,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>070-4535-3457</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3245,13 +3321,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,12 +3336,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>1255857101</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/1255857101</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3282,29 +3358,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3314,7 +3390,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3324,10 +3400,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48ak4</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3339,13 +3419,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>116</v>
+        <v>688</v>
       </c>
       <c r="Q31" t="n">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="R31" t="n">
-        <v>359</v>
+        <v>826</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,12 +3434,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3376,29 +3456,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany87</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3408,12 +3488,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3429,17 +3509,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1450</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>1690</v>
+        <v>202</v>
       </c>
       <c r="R32" t="n">
-        <v>3140</v>
+        <v>212</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,12 +3528,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3470,39 +3550,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>nrkmhhuppr297@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3512,10 +3592,14 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcqxln1</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>X</t>
@@ -3527,13 +3611,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>348</v>
+        <v>75</v>
       </c>
       <c r="Q33" t="n">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="R33" t="n">
-        <v>937</v>
+        <v>168</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,12 +3626,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3564,29 +3648,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>uptfitness@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1351-2438</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baekyuri802</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3596,12 +3676,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3617,17 +3697,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>612</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>339</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>951</v>
+        <v>7</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,12 +3716,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3658,29 +3738,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietmode-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3690,20 +3770,24 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5j3</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3711,17 +3795,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>99</v>
+        <v>1708</v>
       </c>
       <c r="Q35" t="n">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="R35" t="n">
-        <v>310</v>
+        <v>2070</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,12 +3814,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3747,34 +3831,34 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>ddt341@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3784,12 +3868,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3809,13 +3893,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="Q36" t="n">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="R36" t="n">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,12 +3908,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3846,29 +3930,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ask4554</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3878,20 +3962,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43zk4</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3899,17 +3987,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="Q37" t="n">
-        <v>202</v>
+        <v>344</v>
       </c>
       <c r="R37" t="n">
-        <v>212</v>
+        <v>694</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3918,12 +4006,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3940,29 +4028,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>업타운 휘트니스 미아사거리점</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>uptownfitness1@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02-945-8883</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 41-1 4층 업타운휘트니스</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uptown_fitness1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3972,7 +4060,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3982,10 +4070,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we2yppk</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -3997,13 +4089,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="Q38" t="n">
-        <v>506</v>
+        <v>216</v>
       </c>
       <c r="R38" t="n">
-        <v>946</v>
+        <v>633</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4012,12 +4104,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1135005736</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135005736</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4034,35 +4126,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1354-5063</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4072,10 +4168,14 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wui0kyi</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>X</t>
@@ -4083,17 +4183,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>590</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>938</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,12 +4202,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4124,29 +4224,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>hanwnsdn@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1417-9917</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sd670</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4156,12 +4252,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4177,17 +4273,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="n">
-        <v>233</v>
+        <v>6</v>
       </c>
       <c r="R40" t="n">
-        <v>318</v>
+        <v>13</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,12 +4292,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4213,34 +4309,34 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtu.be/U5NY3gY-89E?si=LfEDQDEA_0ObG6l9</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4250,7 +4346,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4260,10 +4356,14 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sncb</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4271,17 +4371,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,12 +4390,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4307,34 +4407,34 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4344,7 +4444,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4354,13 +4454,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfi5my</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4369,13 +4473,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>232</v>
+        <v>2234</v>
       </c>
       <c r="Q42" t="n">
-        <v>581</v>
+        <v>1396</v>
       </c>
       <c r="R42" t="n">
-        <v>813</v>
+        <v>3630</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,12 +4488,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4406,29 +4510,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4438,12 +4542,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4459,17 +4563,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1072</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1912</v>
+        <v>8</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,12 +4582,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4495,43 +4599,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
+          <t>gymboxx@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>myeonghui5402@gmail.com</t>
+          <t>info@suppliesfitness.com</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4541,18 +4645,22 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4561,13 +4669,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>86</v>
+        <v>1106</v>
       </c>
       <c r="Q44" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="R44" t="n">
-        <v>177</v>
+        <v>1146</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4576,12 +4684,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4598,29 +4706,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4655,13 +4763,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>37</v>
+        <v>691</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>728</v>
       </c>
       <c r="R45" t="n">
-        <v>57</v>
+        <v>1419</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4670,12 +4778,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4692,29 +4800,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/enermeca2/</t>
+          <t>http://blog.naver.com/herricane</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4729,7 +4837,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4745,17 +4853,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1311</v>
+        <v>206</v>
       </c>
       <c r="Q46" t="n">
-        <v>882</v>
+        <v>196</v>
       </c>
       <c r="R46" t="n">
-        <v>2193</v>
+        <v>402</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4764,12 +4872,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4786,29 +4894,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssdaw1234</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4843,13 +4951,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>23</v>
+        <v>1288</v>
       </c>
       <c r="Q47" t="n">
-        <v>93</v>
+        <v>1921</v>
       </c>
       <c r="R47" t="n">
-        <v>116</v>
+        <v>3209</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4858,12 +4966,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4880,29 +4988,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4937,13 +5045,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1287</v>
+        <v>95</v>
       </c>
       <c r="Q48" t="n">
-        <v>1918</v>
+        <v>296</v>
       </c>
       <c r="R48" t="n">
-        <v>3205</v>
+        <v>391</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4952,12 +5060,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4969,34 +5077,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5006,7 +5114,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5027,17 +5135,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1603</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1187</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2790</v>
+        <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5046,12 +5154,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5068,29 +5176,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5100,12 +5208,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5125,13 +5233,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="Q50" t="n">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="R50" t="n">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5140,12 +5248,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5162,29 +5270,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5194,7 +5302,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5204,13 +5312,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wellmvw</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5219,13 +5331,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>116</v>
+        <v>811</v>
       </c>
       <c r="Q51" t="n">
-        <v>200</v>
+        <v>644</v>
       </c>
       <c r="R51" t="n">
-        <v>316</v>
+        <v>1455</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5234,12 +5346,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5251,29 +5363,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>somedayday00@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5313,13 +5425,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5328,12 +5440,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5350,34 +5462,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1421-2221</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5392,10 +5500,14 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc215t</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5407,13 +5519,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="Q53" t="n">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="R53" t="n">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5422,12 +5534,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5444,34 +5556,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nyh314</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5481,33 +5593,37 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o0p2</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="Q54" t="n">
-        <v>364</v>
+        <v>569</v>
       </c>
       <c r="R54" t="n">
-        <v>698</v>
+        <v>889</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5516,12 +5632,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5538,25 +5654,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>업타운 휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>uptownfitness1@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>02-945-8883</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 도봉로 41-1 4층 업타운휘트니스</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5566,7 +5686,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5576,13 +5696,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcd3ju</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5591,13 +5715,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>90</v>
+        <v>440</v>
       </c>
       <c r="Q55" t="n">
-        <v>158</v>
+        <v>506</v>
       </c>
       <c r="R55" t="n">
-        <v>248</v>
+        <v>946</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5606,12 +5730,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>1135005736</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/1135005736</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5628,29 +5752,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5660,20 +5784,24 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs9wn</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>X</t>
@@ -5685,13 +5813,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2721</v>
+        <v>1072</v>
       </c>
       <c r="Q56" t="n">
-        <v>2329</v>
+        <v>836</v>
       </c>
       <c r="R56" t="n">
-        <v>5050</v>
+        <v>1908</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5700,12 +5828,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5722,29 +5850,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5754,20 +5882,24 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sak0</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>X</t>
@@ -5779,13 +5911,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>691</v>
+        <v>1450</v>
       </c>
       <c r="Q57" t="n">
-        <v>728</v>
+        <v>1692</v>
       </c>
       <c r="R57" t="n">
-        <v>1419</v>
+        <v>3142</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5794,12 +5926,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5816,48 +5948,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>hsyqz13@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5868,7 +5996,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5877,13 +6005,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1102</v>
+        <v>114</v>
       </c>
       <c r="Q58" t="n">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="R58" t="n">
-        <v>1142</v>
+        <v>232</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5892,12 +6020,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5909,34 +6037,34 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5946,20 +6074,24 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43knh</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>X</t>
@@ -5971,13 +6103,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>80</v>
+        <v>4535</v>
       </c>
       <c r="Q59" t="n">
-        <v>103</v>
+        <v>1324</v>
       </c>
       <c r="R59" t="n">
-        <v>183</v>
+        <v>5859</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5986,12 +6118,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6008,29 +6140,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://youtu.be/U5NY3gY-89E?si=LfEDQDEA_0ObG6l9</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6050,14 +6182,10 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sncb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>X</t>
@@ -6069,13 +6197,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="Q60" t="n">
-        <v>320</v>
+        <v>201</v>
       </c>
       <c r="R60" t="n">
-        <v>423</v>
+        <v>317</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6084,12 +6212,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6106,24 +6234,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6153,12 +6281,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wellmvw</t>
+          <t>https://talk.naver.com/ct/w4f9qn</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6167,13 +6295,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>810</v>
+        <v>112</v>
       </c>
       <c r="Q61" t="n">
-        <v>658</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>1468</v>
+        <v>117</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6182,12 +6310,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6204,24 +6332,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6251,7 +6379,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43knh</t>
+          <t>https://talk.naver.com/ct/w40kte</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6265,13 +6393,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>4535</v>
+        <v>2723</v>
       </c>
       <c r="Q62" t="n">
-        <v>1350</v>
+        <v>2327</v>
       </c>
       <c r="R62" t="n">
-        <v>5885</v>
+        <v>5050</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6280,12 +6408,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6302,24 +6430,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6344,10 +6472,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc0yw3</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6359,13 +6491,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2747</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6374,12 +6506,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6396,29 +6528,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6428,7 +6560,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6438,14 +6570,10 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wqdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>X</t>
@@ -6457,13 +6585,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>28</v>
+        <v>1603</v>
       </c>
       <c r="Q64" t="n">
-        <v>210</v>
+        <v>1187</v>
       </c>
       <c r="R64" t="n">
-        <v>238</v>
+        <v>2790</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6472,12 +6600,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6489,29 +6617,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6541,12 +6669,12 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yudn</t>
+          <t>https://talk.naver.com/ct/wa2rxwt</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6555,13 +6683,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>464</v>
+        <v>25</v>
       </c>
       <c r="Q65" t="n">
-        <v>787</v>
+        <v>142</v>
       </c>
       <c r="R65" t="n">
-        <v>1251</v>
+        <v>167</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6570,12 +6698,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6587,29 +6715,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>070-4535-3457</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6634,10 +6762,14 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4egpq</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>X</t>
@@ -6645,17 +6777,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6664,12 +6796,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1255857101</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1255857101</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6686,24 +6818,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>배용덕헬스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>nicenet@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6728,14 +6860,10 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/we2yppk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6743,17 +6871,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="R67" t="n">
-        <v>632</v>
+        <v>12</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6762,12 +6890,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6784,24 +6912,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>nrkmhhuppr297@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6826,14 +6954,10 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcqxln1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6845,13 +6969,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="Q68" t="n">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="R68" t="n">
-        <v>168</v>
+        <v>305</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6860,12 +6984,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6877,29 +7001,29 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6924,28 +7048,32 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405s2</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>8</v>
+        <v>232</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>813</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6954,12 +7082,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6976,39 +7104,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ExmdAX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7018,13 +7146,17 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3oe822</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7033,13 +7165,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q70" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7048,12 +7180,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7070,25 +7202,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1382-4849</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7098,7 +7234,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7108,10 +7244,14 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zmep</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7123,13 +7263,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>529</v>
+        <v>190</v>
       </c>
       <c r="Q71" t="n">
-        <v>2235</v>
+        <v>500</v>
       </c>
       <c r="R71" t="n">
-        <v>2764</v>
+        <v>690</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7138,12 +7278,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7160,29 +7300,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7192,7 +7332,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7202,10 +7342,14 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnugfn3</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>X</t>
@@ -7217,13 +7361,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="Q72" t="n">
-        <v>219</v>
+        <v>373</v>
       </c>
       <c r="R72" t="n">
-        <v>298</v>
+        <v>519</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7232,12 +7376,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7254,34 +7398,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7291,15 +7435,19 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdgwqtj</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
@@ -7311,13 +7459,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Q73" t="n">
-        <v>165</v>
+        <v>534</v>
       </c>
       <c r="R73" t="n">
-        <v>245</v>
+        <v>695</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7326,12 +7474,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7348,39 +7496,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>winnnig@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xtmxjax</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7390,10 +7538,14 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lqb7</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7401,17 +7553,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="R74" t="n">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7420,12 +7572,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7464,7 +7616,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_performance</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7474,7 +7626,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7536,29 +7688,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7568,20 +7720,24 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7t3tx8</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7593,13 +7749,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="Q76" t="n">
-        <v>534</v>
+        <v>55</v>
       </c>
       <c r="R76" t="n">
-        <v>695</v>
+        <v>92</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7608,12 +7764,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7630,25 +7786,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1362-0934</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestgym24/223778254580</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7658,20 +7818,24 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45d9r</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>X</t>
@@ -7679,17 +7843,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="Q77" t="n">
-        <v>6</v>
+        <v>1250</v>
       </c>
       <c r="R77" t="n">
-        <v>27</v>
+        <v>1328</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7698,12 +7862,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7720,29 +7884,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1404-1390</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7752,20 +7912,24 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9vb</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr">
         <is>
           <t>X</t>
@@ -7773,17 +7937,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4</v>
+        <v>245</v>
       </c>
       <c r="Q78" t="n">
-        <v>43</v>
+        <v>1341</v>
       </c>
       <c r="R78" t="n">
-        <v>47</v>
+        <v>1586</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7792,12 +7956,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7814,29 +7978,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1301-9491</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hypedobby</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7846,7 +8006,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7856,10 +8016,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jtey</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -7871,13 +8035,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R79" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7886,12 +8050,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7908,29 +8072,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7945,7 +8109,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7965,13 +8129,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="Q80" t="n">
-        <v>373</v>
+        <v>219</v>
       </c>
       <c r="R80" t="n">
-        <v>519</v>
+        <v>298</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7980,12 +8144,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8002,29 +8166,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8034,20 +8198,24 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu8v0g9</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t>X</t>
@@ -8059,13 +8227,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="Q81" t="n">
-        <v>1247</v>
+        <v>47</v>
       </c>
       <c r="R81" t="n">
-        <v>1325</v>
+        <v>75</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8074,12 +8242,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8096,39 +8264,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8153,13 +8321,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>636</v>
+        <v>20</v>
       </c>
       <c r="Q82" t="n">
-        <v>696</v>
+        <v>44</v>
       </c>
       <c r="R82" t="n">
-        <v>1332</v>
+        <v>64</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8168,12 +8336,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8190,25 +8358,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1437-5900</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8218,20 +8390,24 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zcrh</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
           <t>X</t>
@@ -8243,13 +8419,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>245</v>
+        <v>30</v>
       </c>
       <c r="Q83" t="n">
-        <v>1341</v>
+        <v>29</v>
       </c>
       <c r="R83" t="n">
-        <v>1586</v>
+        <v>59</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8258,12 +8434,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8280,29 +8456,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>0507-1366-4502</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8312,12 +8484,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8337,13 +8509,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="Q84" t="n">
-        <v>180</v>
+        <v>6</v>
       </c>
       <c r="R84" t="n">
-        <v>269</v>
+        <v>27</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8352,12 +8524,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8374,25 +8546,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1404-1390</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8402,20 +8578,24 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9cv7l2</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr">
         <is>
           <t>X</t>
@@ -8423,17 +8603,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q85" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="R85" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8442,12 +8622,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8464,29 +8644,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0507-1458-1884</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymseungeun/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8496,7 +8672,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8521,13 +8697,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>28</v>
+        <v>529</v>
       </c>
       <c r="Q86" t="n">
-        <v>47</v>
+        <v>2235</v>
       </c>
       <c r="R86" t="n">
-        <v>75</v>
+        <v>2764</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8536,12 +8712,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8558,24 +8734,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1385-0454</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8605,7 +8781,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7t3tx8</t>
+          <t>https://talk.naver.com/ct/w5i7ji</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -8615,17 +8791,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="Q87" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="R87" t="n">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8634,12 +8810,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8656,20 +8832,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1485-1323</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8694,28 +8874,32 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4utrl</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1</v>
+        <v>636</v>
       </c>
       <c r="Q88" t="n">
-        <v>41</v>
+        <v>696</v>
       </c>
       <c r="R88" t="n">
-        <v>42</v>
+        <v>1332</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8724,12 +8908,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8746,29 +8930,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1437-5900</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/xtmxjax</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8778,24 +8962,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zcrh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>X</t>
@@ -8803,17 +8983,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q89" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="R89" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8822,12 +9002,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8844,24 +9024,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0507-1382-4849</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8886,14 +9062,10 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zmep</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
@@ -8901,17 +9073,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>500</v>
+        <v>41</v>
       </c>
       <c r="R90" t="n">
-        <v>690</v>
+        <v>42</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8920,12 +9092,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8964,7 +9136,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumanner_only_lounge</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8974,7 +9146,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8984,10 +9156,14 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cztg</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr">
         <is>
           <t>O</t>
@@ -9002,10 +9178,10 @@
         <v>171</v>
       </c>
       <c r="Q91" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="R91" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V92"/>
+  <dimension ref="A1:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,24 +564,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>ddt341@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqzk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="n">
-        <v>532</v>
+        <v>20</v>
       </c>
       <c r="R2" t="n">
-        <v>674</v>
+        <v>57</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,56 +636,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1811</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2995</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kdhonepick</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47wce</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="Q4" t="n">
-        <v>93</v>
+        <v>243</v>
       </c>
       <c r="R4" t="n">
-        <v>116</v>
+        <v>359</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,46 +824,46 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4toem</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,46 +918,46 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jggy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hegardengym_suyu-@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1433-5131</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/f45suyu/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1092,17 +1072,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49479</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="n">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="R7" t="n">
-        <v>92</v>
+        <v>252</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1148,24 +1124,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,10 +1166,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy486uk</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1201,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>689</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>1417</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,66 +1200,70 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,12 +1273,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t1ci</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>86</v>
+        <v>1135</v>
       </c>
       <c r="Q9" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="R9" t="n">
-        <v>177</v>
+        <v>1176</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1340,24 +1324,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1382,17 +1366,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwrhsu4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>335</v>
       </c>
       <c r="R10" t="n">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1438,24 +1418,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1485,7 +1465,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wqdd</t>
+          <t>https://talk.naver.com/ct/w40kte</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>28</v>
+        <v>2744</v>
       </c>
       <c r="Q11" t="n">
-        <v>210</v>
+        <v>2338</v>
       </c>
       <c r="R11" t="n">
-        <v>238</v>
+        <v>5082</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1494,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1536,24 +1516,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>godgod9193@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1578,10 +1558,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sak0</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1593,13 +1577,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>1461</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1720</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>3181</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,17 +1592,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1630,24 +1614,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>io15io15@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1687,13 +1671,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1702,51 +1686,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>thebarunpt@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1756,12 +1740,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1771,7 +1755,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v4ny</t>
+          <t>https://talk.naver.com/ct/w7sz75u</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1785,13 +1769,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1793</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="n">
-        <v>1227</v>
+        <v>104</v>
       </c>
       <c r="R14" t="n">
-        <v>3020</v>
+        <v>184</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1800,17 +1784,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1822,29 +1806,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1854,24 +1838,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rzh6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1883,13 +1863,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>612</v>
+        <v>175</v>
       </c>
       <c r="Q15" t="n">
-        <v>339</v>
+        <v>130</v>
       </c>
       <c r="R15" t="n">
-        <v>951</v>
+        <v>305</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1898,17 +1878,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1920,29 +1900,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymchoi</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1952,12 +1932,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1973,17 +1953,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>347</v>
       </c>
       <c r="R16" t="n">
-        <v>10</v>
+        <v>693</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1992,17 +1972,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2014,29 +1994,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2046,7 +2026,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2056,17 +2036,13 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41vr7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2075,13 +2051,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>221</v>
+        <v>1331</v>
       </c>
       <c r="Q17" t="n">
-        <v>461</v>
+        <v>885</v>
       </c>
       <c r="R17" t="n">
-        <v>682</v>
+        <v>2216</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2090,17 +2066,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2112,29 +2088,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2144,24 +2120,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yudn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>O</t>
@@ -2173,13 +2145,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>464</v>
+        <v>24</v>
       </c>
       <c r="Q18" t="n">
-        <v>785</v>
+        <v>43</v>
       </c>
       <c r="R18" t="n">
-        <v>1249</v>
+        <v>67</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2188,17 +2160,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2210,24 +2182,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>배용덕헬스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>nicenet@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2267,13 +2239,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R19" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2282,17 +2254,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2304,39 +2276,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2352,22 +2324,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>817</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>559</v>
       </c>
       <c r="R20" t="n">
-        <v>13</v>
+        <v>1376</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2376,17 +2348,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2398,34 +2370,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2446,7 +2418,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2455,13 +2427,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>239</v>
+        <v>95</v>
       </c>
       <c r="Q21" t="n">
-        <v>106</v>
+        <v>297</v>
       </c>
       <c r="R21" t="n">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2470,17 +2442,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2492,24 +2464,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2534,10 +2506,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9thbkj</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>X</t>
@@ -2545,17 +2521,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2564,17 +2540,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2586,29 +2562,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ssdaw1234</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2618,24 +2594,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e814</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2647,13 +2619,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2649</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
-        <v>4706</v>
+        <v>93</v>
       </c>
       <c r="R23" t="n">
-        <v>7355</v>
+        <v>117</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2662,17 +2634,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2656,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2697,12 +2669,12 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2712,7 +2684,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2727,12 +2699,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy43x6v</t>
+          <t>https://talk.naver.com/ct/wc215t</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2741,13 +2713,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Q24" t="n">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="R24" t="n">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2756,17 +2728,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2778,24 +2750,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pressgym@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2825,7 +2797,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i8bi</t>
+          <t>https://talk.naver.com/ct/w4egpq</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2839,13 +2811,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>229</v>
+        <v>43</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>267</v>
+        <v>50</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2854,46 +2826,46 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2918,14 +2890,10 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9thbkj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2933,7 +2901,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2952,51 +2920,51 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>thebarunpt@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3006,12 +2974,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3021,7 +2989,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7sz75u</t>
+          <t>https://talk.naver.com/ct/w4jggy</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3035,13 +3003,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Q27" t="n">
-        <v>103</v>
+        <v>235</v>
       </c>
       <c r="R27" t="n">
-        <v>183</v>
+        <v>322</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3050,17 +3018,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3072,24 +3040,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>somedayday00@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3119,7 +3087,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdf2zxw</t>
+          <t>https://talk.naver.com/ct/wpw1lb4</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3133,13 +3101,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>99</v>
+        <v>334</v>
       </c>
       <c r="Q28" t="n">
-        <v>211</v>
+        <v>365</v>
       </c>
       <c r="R28" t="n">
-        <v>310</v>
+        <v>699</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3148,17 +3116,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3170,24 +3138,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3227,13 +3195,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1311</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
-        <v>882</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2193</v>
+        <v>10</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3242,61 +3210,61 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>070-4535-3457</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_QERxeG</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3312,22 +3280,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3336,17 +3304,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1255857101</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1255857101</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3358,29 +3326,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtu.be/U5NY3gY-89E?si=LfEDQDEA_0ObG6l9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3390,7 +3358,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3405,7 +3373,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48ak4</t>
+          <t>https://talk.naver.com/ct/w4sncb</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3419,13 +3387,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>688</v>
+        <v>103</v>
       </c>
       <c r="Q31" t="n">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="R31" t="n">
-        <v>826</v>
+        <v>423</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3434,17 +3402,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3456,39 +3424,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3509,17 +3477,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>10</v>
+        <v>349</v>
       </c>
       <c r="Q32" t="n">
-        <v>202</v>
+        <v>609</v>
       </c>
       <c r="R32" t="n">
-        <v>212</v>
+        <v>958</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3528,17 +3496,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3550,59 +3518,55 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nrkmhhuppr297@naver.com</t>
+          <t>fa_sport@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcqxln1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3611,13 +3575,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="Q33" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="R33" t="n">
-        <v>168</v>
+        <v>345</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3626,42 +3590,46 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1334-6825</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3686,28 +3654,32 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405s2</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>583</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>813</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3716,17 +3688,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3710,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3785,7 +3757,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5j3</t>
+          <t>https://talk.naver.com/ct/w4rzh6</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3799,13 +3771,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1708</v>
+        <v>618</v>
       </c>
       <c r="Q35" t="n">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="R35" t="n">
-        <v>2070</v>
+        <v>957</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3814,46 +3786,46 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ddt341@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3878,10 +3850,14 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa2rxwt</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>X</t>
@@ -3893,13 +3869,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q36" t="n">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="R36" t="n">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3908,17 +3884,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3930,24 +3906,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3977,7 +3953,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43zk4</t>
+          <t>https://talk.naver.com/ct/wc0yw3</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3991,13 +3967,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>350</v>
+        <v>1933</v>
       </c>
       <c r="Q37" t="n">
-        <v>344</v>
+        <v>828</v>
       </c>
       <c r="R37" t="n">
-        <v>694</v>
+        <v>2761</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -4006,17 +3982,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4028,24 +4004,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>hsyqz13@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4070,14 +4046,10 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/we2yppk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -4089,13 +4061,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>417</v>
+        <v>114</v>
       </c>
       <c r="Q38" t="n">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="R38" t="n">
-        <v>633</v>
+        <v>239</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4104,17 +4076,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4126,39 +4098,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4173,7 +4145,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wui0kyi</t>
+          <t>https://talk.naver.com/ct/w481k9</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4183,17 +4155,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="Q39" t="n">
-        <v>590</v>
+        <v>198</v>
       </c>
       <c r="R39" t="n">
-        <v>938</v>
+        <v>404</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4202,17 +4174,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4224,20 +4196,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02-990-3912</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4262,10 +4238,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5j3</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4273,17 +4253,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>7</v>
+        <v>1713</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>379</v>
       </c>
       <c r="R40" t="n">
-        <v>13</v>
+        <v>2092</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4292,17 +4272,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4314,29 +4294,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://youtu.be/U5NY3gY-89E?si=LfEDQDEA_0ObG6l9</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4346,7 +4326,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4356,14 +4336,10 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sncb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4371,17 +4347,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="Q41" t="n">
-        <v>320</v>
+        <v>16</v>
       </c>
       <c r="R41" t="n">
-        <v>423</v>
+        <v>54</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4390,17 +4366,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4412,24 +4388,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4454,14 +4430,10 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfi5my</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>X</t>
@@ -4469,17 +4441,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2234</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="n">
-        <v>1396</v>
+        <v>202</v>
       </c>
       <c r="R42" t="n">
-        <v>3630</v>
+        <v>212</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4488,17 +4460,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4510,24 +4482,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>NH FITNESS CLUB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4582,17 +4554,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4604,78 +4576,70 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>tjdghksfl20@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1106</v>
+        <v>40</v>
       </c>
       <c r="Q44" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1146</v>
+        <v>44</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4684,17 +4648,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4706,29 +4670,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>uptfitness@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1420-9036</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4738,12 +4698,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4759,17 +4719,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>691</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>728</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>1419</v>
+        <v>7</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4778,17 +4738,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4800,29 +4760,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/herricane</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4837,7 +4797,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4853,17 +4813,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>206</v>
+        <v>1618</v>
       </c>
       <c r="Q46" t="n">
-        <v>196</v>
+        <v>1194</v>
       </c>
       <c r="R46" t="n">
-        <v>402</v>
+        <v>2812</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4872,17 +4832,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4894,29 +4854,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4926,20 +4886,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we2yppk</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>X</t>
@@ -4951,13 +4915,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1288</v>
+        <v>425</v>
       </c>
       <c r="Q47" t="n">
-        <v>1921</v>
+        <v>221</v>
       </c>
       <c r="R47" t="n">
-        <v>3209</v>
+        <v>646</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4966,51 +4930,51 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5020,12 +4984,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5041,17 +5005,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5060,46 +5024,46 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>가인헬스클럽</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5142,10 +5106,10 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5154,17 +5118,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5176,24 +5140,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5218,10 +5182,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfi5my</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>X</t>
@@ -5233,13 +5201,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>115</v>
+        <v>2255</v>
       </c>
       <c r="Q50" t="n">
-        <v>335</v>
+        <v>1429</v>
       </c>
       <c r="R50" t="n">
-        <v>450</v>
+        <v>3684</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5248,17 +5216,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5270,24 +5238,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>pressgym@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5317,12 +5285,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wellmvw</t>
+          <t>https://talk.naver.com/ct/w5i8bi</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5331,13 +5299,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>811</v>
+        <v>233</v>
       </c>
       <c r="Q51" t="n">
-        <v>644</v>
+        <v>44</v>
       </c>
       <c r="R51" t="n">
-        <v>1455</v>
+        <v>277</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5346,17 +5314,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5368,24 +5336,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>somedayday00@naver.com</t>
+          <t>nrkmhhuppr297@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5410,10 +5378,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcqxln1</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5421,17 +5393,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>334</v>
+        <v>75</v>
       </c>
       <c r="Q52" t="n">
-        <v>364</v>
+        <v>94</v>
       </c>
       <c r="R52" t="n">
-        <v>698</v>
+        <v>169</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5440,17 +5412,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5462,52 +5434,52 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02-986-0188</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc215t</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5515,17 +5487,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>192</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>279</v>
+        <v>3</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5534,17 +5506,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5556,39 +5528,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5603,27 +5575,27 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o0p2</t>
+          <t>https://talk.naver.com/ct/wdf2zxw</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>320</v>
+        <v>99</v>
       </c>
       <c r="Q54" t="n">
-        <v>569</v>
+        <v>211</v>
       </c>
       <c r="R54" t="n">
-        <v>889</v>
+        <v>310</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5632,17 +5604,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5654,29 +5626,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>업타운 휘트니스 미아사거리점</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>uptownfitness1@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02-945-8883</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 41-1 4층 업타운휘트니스</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5686,7 +5658,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5696,14 +5668,10 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcd3ju</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>X</t>
@@ -5715,13 +5683,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>440</v>
+        <v>125</v>
       </c>
       <c r="Q55" t="n">
-        <v>506</v>
+        <v>216</v>
       </c>
       <c r="R55" t="n">
-        <v>946</v>
+        <v>341</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5730,17 +5698,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1135005736</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135005736</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5752,24 +5720,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5799,7 +5767,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcs9wn</t>
+          <t>https://talk.naver.com/ct/w4e814</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5813,13 +5781,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1072</v>
+        <v>2657</v>
       </c>
       <c r="Q56" t="n">
-        <v>836</v>
+        <v>4788</v>
       </c>
       <c r="R56" t="n">
-        <v>1908</v>
+        <v>7445</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5828,46 +5796,46 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>honeymusclegym@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5897,7 +5865,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sak0</t>
+          <t>https://talk.naver.com/ct/w5t1ci</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5911,13 +5879,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1450</v>
+        <v>86</v>
       </c>
       <c r="Q57" t="n">
-        <v>1692</v>
+        <v>91</v>
       </c>
       <c r="R57" t="n">
-        <v>3142</v>
+        <v>177</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5926,17 +5894,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5948,24 +5916,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>hsyqz13@naver.com</t>
+          <t>hegardengym_suyu-@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5990,10 +5958,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49479</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
@@ -6005,13 +5977,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="Q58" t="n">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="R58" t="n">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6020,17 +5992,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6014,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6089,7 +6061,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43knh</t>
+          <t>https://talk.naver.com/ct/w48ak4</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6103,13 +6075,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>4535</v>
+        <v>694</v>
       </c>
       <c r="Q59" t="n">
-        <v>1324</v>
+        <v>142</v>
       </c>
       <c r="R59" t="n">
-        <v>5859</v>
+        <v>836</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6118,17 +6090,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6140,29 +6112,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6172,7 +6144,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6182,10 +6154,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43knh</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>X</t>
@@ -6197,13 +6173,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>116</v>
+        <v>4545</v>
       </c>
       <c r="Q60" t="n">
-        <v>201</v>
+        <v>1203</v>
       </c>
       <c r="R60" t="n">
-        <v>317</v>
+        <v>5748</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6212,46 +6188,46 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>070-5250-6614</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6276,14 +6252,10 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f9qn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>X</t>
@@ -6291,17 +6263,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6310,46 +6282,46 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6374,14 +6346,10 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40kte</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6389,17 +6357,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2723</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2327</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>5050</v>
+        <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6408,17 +6376,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6430,24 +6398,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>acrogym1@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6477,7 +6445,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc0yw3</t>
+          <t>https://talk.naver.com/ct/w4f9qn</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6491,13 +6459,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1923</v>
+        <v>113</v>
       </c>
       <c r="Q63" t="n">
-        <v>824</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>2747</v>
+        <v>118</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6506,17 +6474,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6528,29 +6496,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>더블플러스휘트니스클럽</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6560,7 +6528,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6581,17 +6549,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1603</v>
+        <v>7</v>
       </c>
       <c r="Q64" t="n">
-        <v>1187</v>
+        <v>6</v>
       </c>
       <c r="R64" t="n">
-        <v>2790</v>
+        <v>13</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6600,46 +6568,46 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6669,7 +6637,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa2rxwt</t>
+          <t>https://talk.naver.com/ct/w4dqzk</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6683,13 +6651,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="Q65" t="n">
-        <v>142</v>
+        <v>485</v>
       </c>
       <c r="R65" t="n">
-        <v>167</v>
+        <v>627</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6698,17 +6666,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6720,39 +6688,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6767,12 +6735,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4egpq</t>
+          <t>https://talk.naver.com/ct/w4o0p2</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6781,13 +6749,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>43</v>
+        <v>322</v>
       </c>
       <c r="Q66" t="n">
-        <v>7</v>
+        <v>578</v>
       </c>
       <c r="R66" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6796,17 +6764,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6818,24 +6786,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nicenet@naver.com</t>
+          <t>hanwnsdn@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>02-980-2004</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6875,13 +6839,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6890,17 +6854,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6912,24 +6876,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6954,10 +6918,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ham5</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6969,13 +6937,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>175</v>
+        <v>1290</v>
       </c>
       <c r="Q68" t="n">
-        <v>130</v>
+        <v>1948</v>
       </c>
       <c r="R68" t="n">
-        <v>305</v>
+        <v>3238</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6984,46 +6952,46 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7053,12 +7021,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w405s2</t>
+          <t>https://talk.naver.com/ct/w5wqdd</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7067,13 +7035,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>232</v>
+        <v>28</v>
       </c>
       <c r="Q69" t="n">
-        <v>581</v>
+        <v>211</v>
       </c>
       <c r="R69" t="n">
-        <v>813</v>
+        <v>239</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7082,46 +7050,46 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1301-9491</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7151,7 +7119,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3oe822</t>
+          <t>https://talk.naver.com/ct/wcs9wn</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7165,13 +7133,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>25</v>
+        <v>1086</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="R70" t="n">
-        <v>25</v>
+        <v>1938</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7180,46 +7148,46 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7249,12 +7217,12 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4zmep</t>
+          <t>https://talk.naver.com/ct/w41vr7</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7263,13 +7231,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="Q71" t="n">
-        <v>500</v>
+        <v>423</v>
       </c>
       <c r="R71" t="n">
-        <v>690</v>
+        <v>649</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7278,17 +7246,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7300,24 +7268,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1309-1030</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7347,7 +7311,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wnugfn3</t>
+          <t>https://talk.naver.com/ct/w5u9vb</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7361,13 +7325,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="Q72" t="n">
-        <v>373</v>
+        <v>1343</v>
       </c>
       <c r="R72" t="n">
-        <v>519</v>
+        <v>1589</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7376,17 +7340,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7398,29 +7362,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>winnnig@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7430,12 +7394,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7445,7 +7409,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdgwqtj</t>
+          <t>https://talk.naver.com/ct/w4lqb7</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7459,13 +7423,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="Q73" t="n">
-        <v>534</v>
+        <v>165</v>
       </c>
       <c r="R73" t="n">
-        <v>695</v>
+        <v>244</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7474,17 +7438,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7496,39 +7460,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>winnnig@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7538,14 +7502,10 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lqb7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7557,13 +7517,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q74" t="n">
-        <v>165</v>
+        <v>1295</v>
       </c>
       <c r="R74" t="n">
-        <v>245</v>
+        <v>1373</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7572,17 +7532,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7559,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>dailybom@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7616,7 +7576,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dyb_performance</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7626,7 +7586,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7676,7 +7636,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7688,24 +7648,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1385-0454</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7735,7 +7695,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7t3tx8</t>
+          <t>https://talk.naver.com/ct/w9cv7l2</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7745,17 +7705,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="Q76" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="R76" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7764,17 +7724,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7786,24 +7746,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0507-1362-0934</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7828,14 +7784,10 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45d9r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>X</t>
@@ -7843,17 +7795,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>1250</v>
+        <v>41</v>
       </c>
       <c r="R77" t="n">
-        <v>1328</v>
+        <v>42</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7862,17 +7814,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7884,20 +7836,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1437-5900</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7927,7 +7883,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u9vb</t>
+          <t>https://talk.naver.com/ct/w4zcrh</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7941,13 +7897,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="Q78" t="n">
-        <v>1341</v>
+        <v>29</v>
       </c>
       <c r="R78" t="n">
-        <v>1586</v>
+        <v>61</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7956,17 +7912,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7978,25 +7934,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1366-4502</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8006,24 +7966,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jtey</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -8031,17 +7987,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="Q79" t="n">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="R79" t="n">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -8050,17 +8006,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8072,29 +8028,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://smartstore.naver.com/runandlift</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8129,13 +8085,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="Q80" t="n">
-        <v>219</v>
+        <v>501</v>
       </c>
       <c r="R80" t="n">
-        <v>298</v>
+        <v>692</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8144,17 +8100,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8166,24 +8122,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>0507-1458-1884</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8208,14 +8160,10 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wu8v0g9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>X</t>
@@ -8223,18 +8171,18 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P81" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>7</v>
+      </c>
+      <c r="R81" t="n">
         <v>28</v>
       </c>
-      <c r="Q81" t="n">
-        <v>47</v>
-      </c>
-      <c r="R81" t="n">
-        <v>75</v>
-      </c>
       <c r="S81" t="inlineStr">
         <is>
           <t>X</t>
@@ -8242,17 +8190,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8264,24 +8212,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8306,13 +8254,17 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdgwqtj</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8321,13 +8273,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="Q82" t="n">
-        <v>44</v>
+        <v>545</v>
       </c>
       <c r="R82" t="n">
-        <v>64</v>
+        <v>707</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8336,17 +8288,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8358,24 +8310,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1437-5900</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8400,14 +8352,10 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zcrh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>X</t>
@@ -8415,17 +8363,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q83" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="R83" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8434,17 +8382,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8456,20 +8404,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1368-4511</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8505,17 +8457,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="Q84" t="n">
-        <v>6</v>
+        <v>220</v>
       </c>
       <c r="R84" t="n">
-        <v>27</v>
+        <v>299</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8524,17 +8476,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8546,24 +8498,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8593,7 +8545,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9cv7l2</t>
+          <t>https://talk.naver.com/ct/wnugfn3</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -8603,17 +8555,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>5</v>
+        <v>146</v>
       </c>
       <c r="Q85" t="n">
-        <v>44</v>
+        <v>373</v>
       </c>
       <c r="R85" t="n">
-        <v>49</v>
+        <v>519</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8622,17 +8574,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8605,11 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1404-1363</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
@@ -8697,13 +8653,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="Q86" t="n">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="R86" t="n">
-        <v>2764</v>
+        <v>2768</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8722,7 +8678,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8734,24 +8690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8781,7 +8737,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i7ji</t>
+          <t>https://talk.naver.com/ct/wxl9x94</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -8791,17 +8747,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="Q87" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>269</v>
+        <v>39</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8810,17 +8766,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8832,29 +8788,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0507-1485-1323</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8864,27 +8816,23 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4utrl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8893,13 +8841,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>636</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="n">
-        <v>696</v>
+        <v>19</v>
       </c>
       <c r="R88" t="n">
-        <v>1332</v>
+        <v>21</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8908,17 +8856,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8930,29 +8878,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xtmxjax</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8962,38 +8910,42 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4utrl</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>33</v>
+        <v>637</v>
       </c>
       <c r="Q89" t="n">
-        <v>10</v>
+        <v>699</v>
       </c>
       <c r="R89" t="n">
-        <v>43</v>
+        <v>1336</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -9002,17 +8954,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -9024,20 +8976,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1458-1884</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9062,10 +9018,14 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu8v0g9</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
@@ -9073,17 +9033,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="Q90" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="R90" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -9092,46 +9052,46 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>왁싱,제모</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>알유매너온리움 왁싱뷰티라운지</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>rumanneronly@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1352-6560</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 376 2층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9161,12 +9121,12 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cztg</t>
+          <t>https://talk.naver.com/ct/w7t3tx8</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9175,13 +9135,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="Q91" t="n">
-        <v>432</v>
+        <v>60</v>
       </c>
       <c r="R91" t="n">
-        <v>603</v>
+        <v>103</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9190,57 +9150,61 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1294064124</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294064124</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>체력단련,운동</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DL 운동센터</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>gunwigun_official@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1377-5126</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로22가길 11 2층 201호</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://litt.ly/d.l.trainer</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9265,32 +9229,122 @@
         </is>
       </c>
       <c r="P92" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>51</v>
+      </c>
+      <c r="R92" t="n">
+        <v>72</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>2013060255</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013060255</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>체력단련,운동</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DL 운동센터</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>gunwigun_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로22가길 11 2층 201호</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://litt.ly/d.l.trainer</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
         <v>4</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="Q93" t="n">
         <v>2</v>
       </c>
-      <c r="R92" t="n">
+      <c r="R93" t="n">
         <v>6</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
         <is>
           <t>1479834103</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1479834103</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddt341@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/blueskirt0704</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>502</v>
       </c>
       <c r="R2" t="n">
-        <v>57</v>
+        <v>644</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1811</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1184</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>2995</v>
+        <v>3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="Q4" t="n">
-        <v>243</v>
+        <v>130</v>
       </c>
       <c r="R4" t="n">
-        <v>359</v>
+        <v>305</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,46 +824,46 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +888,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9thbkj</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,17 +903,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,46 +922,46 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +986,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ham5</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,17 +1001,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1949</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3239</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,25 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>02-990-3912</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,7 +1074,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1072,13 +1084,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5j3</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>91</v>
+        <v>1717</v>
       </c>
       <c r="Q7" t="n">
-        <v>161</v>
+        <v>385</v>
       </c>
       <c r="R7" t="n">
-        <v>252</v>
+        <v>2102</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1124,24 +1140,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1171,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy486uk</t>
+          <t>https://talk.naver.com/ct/w4sncb</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1185,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>689</v>
+        <v>103</v>
       </c>
       <c r="Q8" t="n">
-        <v>728</v>
+        <v>320</v>
       </c>
       <c r="R8" t="n">
-        <v>1417</v>
+        <v>423</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1222,78 +1238,66 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1391-2161</t>
-        </is>
-      </c>
+          <t>uptfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1135</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1176</v>
+        <v>7</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1324,39 +1328,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1366,13 +1370,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o0p2</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1381,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>115</v>
+        <v>322</v>
       </c>
       <c r="Q10" t="n">
-        <v>335</v>
+        <v>580</v>
       </c>
       <c r="R10" t="n">
-        <v>450</v>
+        <v>902</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1418,24 +1426,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1465,7 +1473,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40kte</t>
+          <t>https://talk.naver.com/ct/w4toem</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1479,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2744</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="n">
-        <v>2338</v>
+        <v>243</v>
       </c>
       <c r="R11" t="n">
-        <v>5082</v>
+        <v>359</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,17 +1502,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1516,34 +1524,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1553,19 +1561,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sak0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1577,13 +1581,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1461</v>
+        <v>1812</v>
       </c>
       <c r="Q12" t="n">
-        <v>1720</v>
+        <v>1185</v>
       </c>
       <c r="R12" t="n">
-        <v>3181</v>
+        <v>2997</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1592,17 +1596,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1614,24 +1618,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1656,10 +1660,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wqdd</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1667,17 +1675,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>211</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>239</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1686,51 +1694,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>thebarunpt@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1740,24 +1748,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7sz75u</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1765,17 +1769,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1784,17 +1788,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1806,29 +1810,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>somedayday00@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1838,20 +1842,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpw1lb4</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1859,17 +1867,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>175</v>
+        <v>334</v>
       </c>
       <c r="Q15" t="n">
-        <v>130</v>
+        <v>365</v>
       </c>
       <c r="R15" t="n">
-        <v>305</v>
+        <v>699</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1878,17 +1886,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1900,29 +1908,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1932,20 +1940,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47wce</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>X</t>
@@ -1957,13 +1969,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>346</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="n">
-        <v>347</v>
+        <v>93</v>
       </c>
       <c r="R16" t="n">
-        <v>693</v>
+        <v>117</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1972,17 +1984,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1994,29 +2006,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>hegardengym_suyu-@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/enermeca2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2026,7 +2038,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2036,10 +2048,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49479</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>X</t>
@@ -2051,13 +2067,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1331</v>
+        <v>37</v>
       </c>
       <c r="Q17" t="n">
-        <v>885</v>
+        <v>56</v>
       </c>
       <c r="R17" t="n">
-        <v>2216</v>
+        <v>93</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2066,51 +2082,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/axis_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2120,20 +2136,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405s2</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>O</t>
@@ -2145,13 +2165,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="Q18" t="n">
-        <v>43</v>
+        <v>584</v>
       </c>
       <c r="R18" t="n">
-        <v>67</v>
+        <v>814</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2160,17 +2180,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2182,29 +2202,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nicenet@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2214,12 +2234,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2230,22 +2250,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>423</v>
       </c>
       <c r="R19" t="n">
-        <v>13</v>
+        <v>649</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2254,17 +2274,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2276,34 +2296,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ZWKxjn</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2313,7 +2333,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2333,13 +2353,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>817</v>
+        <v>25</v>
       </c>
       <c r="Q20" t="n">
-        <v>559</v>
+        <v>44</v>
       </c>
       <c r="R20" t="n">
-        <v>1376</v>
+        <v>69</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2348,17 +2368,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2370,29 +2390,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2427,13 +2447,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>95</v>
+        <v>689</v>
       </c>
       <c r="Q21" t="n">
-        <v>297</v>
+        <v>728</v>
       </c>
       <c r="R21" t="n">
-        <v>392</v>
+        <v>1417</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2442,17 +2462,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2464,24 +2484,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2511,12 +2531,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9thbkj</t>
+          <t>https://talk.naver.com/ct/wellmvw</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2525,13 +2545,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>35</v>
+        <v>821</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="R22" t="n">
-        <v>35</v>
+        <v>1380</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2540,17 +2560,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2562,29 +2582,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssdaw1234</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2599,7 +2619,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2619,13 +2639,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>1331</v>
       </c>
       <c r="Q23" t="n">
-        <v>93</v>
+        <v>885</v>
       </c>
       <c r="R23" t="n">
-        <v>117</v>
+        <v>2216</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2634,17 +2654,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2656,25 +2676,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1459-7599</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2694,14 +2718,10 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc215t</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>X</t>
@@ -2713,13 +2733,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>87</v>
+        <v>426</v>
       </c>
       <c r="Q24" t="n">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="R24" t="n">
-        <v>280</v>
+        <v>647</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2728,17 +2748,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2750,24 +2770,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>NH FITNESS CLUB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2792,14 +2812,10 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egpq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2807,17 +2823,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2826,51 +2842,51 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>070-4535-3463</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2880,12 +2896,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2901,17 +2917,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2920,17 +2936,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2942,29 +2958,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dietmode-</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2974,24 +2990,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jggy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>X</t>
@@ -2999,17 +3011,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="Q27" t="n">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="R27" t="n">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3018,17 +3030,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3040,24 +3052,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>가인헬스클럽</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>somedayday00@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3082,14 +3094,10 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpw1lb4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3101,13 +3109,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>365</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>699</v>
+        <v>10</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3116,51 +3124,55 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>myeonghui5402@gmail.com</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3170,7 +3182,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3195,13 +3207,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="R29" t="n">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3210,17 +3222,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3232,39 +3244,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1336-7184</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QERxeG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3274,10 +3282,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy43x6v</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>O</t>
@@ -3289,13 +3301,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>462</v>
+        <v>91</v>
       </c>
       <c r="Q30" t="n">
-        <v>795</v>
+        <v>161</v>
       </c>
       <c r="R30" t="n">
-        <v>1257</v>
+        <v>252</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3304,17 +3316,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3326,29 +3338,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://youtu.be/U5NY3gY-89E?si=LfEDQDEA_0ObG6l9</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3358,7 +3370,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3373,12 +3385,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sncb</t>
+          <t>https://talk.naver.com/ct/w5yudn</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3387,13 +3399,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>103</v>
+        <v>462</v>
       </c>
       <c r="Q31" t="n">
-        <v>320</v>
+        <v>795</v>
       </c>
       <c r="R31" t="n">
-        <v>423</v>
+        <v>1257</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3402,17 +3414,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3424,39 +3436,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3466,10 +3478,14 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfi5my</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3481,13 +3497,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>349</v>
+        <v>2264</v>
       </c>
       <c r="Q32" t="n">
-        <v>609</v>
+        <v>1432</v>
       </c>
       <c r="R32" t="n">
-        <v>958</v>
+        <v>3696</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3496,17 +3512,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3518,44 +3534,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3566,22 +3582,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>239</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>345</v>
+        <v>11</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3590,46 +3606,46 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3654,32 +3670,28 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w405s2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>583</v>
+        <v>202</v>
       </c>
       <c r="R34" t="n">
-        <v>813</v>
+        <v>212</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3688,17 +3700,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3710,44 +3722,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1351-2438</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3757,7 +3765,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4rzh6</t>
+          <t>https://talk.naver.com/ct/wc215t</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3771,13 +3779,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>618</v>
+        <v>87</v>
       </c>
       <c r="Q35" t="n">
-        <v>339</v>
+        <v>193</v>
       </c>
       <c r="R35" t="n">
-        <v>957</v>
+        <v>280</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3786,46 +3794,46 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>hsyqz13@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3850,14 +3858,10 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa2rxwt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>X</t>
@@ -3869,13 +3873,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="Q36" t="n">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="R36" t="n">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3884,17 +3888,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3906,24 +3910,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>acrogym1@naver.com</t>
-        </is>
-      </c>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3948,14 +3948,10 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc0yw3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3963,17 +3959,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1933</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="n">
-        <v>828</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>2761</v>
+        <v>13</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3982,17 +3978,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4004,29 +4000,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hsyqz13@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4036,12 +4032,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4061,13 +4057,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="Q38" t="n">
-        <v>125</v>
+        <v>297</v>
       </c>
       <c r="R38" t="n">
-        <v>239</v>
+        <v>392</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4076,17 +4072,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4098,24 +4094,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4140,14 +4136,10 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w481k9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>X</t>
@@ -4159,13 +4151,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="Q39" t="n">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="R39" t="n">
-        <v>404</v>
+        <v>54</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4174,17 +4166,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4196,29 +4188,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jjfit_7707</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4228,7 +4220,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4238,14 +4230,10 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r5j3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4257,13 +4245,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1713</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2092</v>
+        <v>10</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4272,17 +4260,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4294,39 +4282,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4347,17 +4335,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>38</v>
+        <v>351</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="R41" t="n">
-        <v>54</v>
+        <v>967</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4366,17 +4354,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4388,29 +4376,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://cafe.naver.com/curves</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4420,12 +4408,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4441,17 +4429,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="Q42" t="n">
-        <v>202</v>
+        <v>7</v>
       </c>
       <c r="R42" t="n">
-        <v>212</v>
+        <v>50</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4460,17 +4448,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4482,29 +4470,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>bum903@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bum903</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4514,12 +4502,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4535,17 +4523,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R43" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4554,17 +4542,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4576,44 +4564,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>fa_sport@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4624,22 +4612,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>40</v>
+        <v>239</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="R44" t="n">
-        <v>44</v>
+        <v>345</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4648,17 +4636,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4670,25 +4658,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>codelegend@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1344-9688</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/pressgym___</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4698,7 +4690,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4719,17 +4711,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>234</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="R45" t="n">
-        <v>7</v>
+        <v>279</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4738,17 +4730,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4760,29 +4752,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4797,7 +4789,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4817,13 +4809,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1618</v>
+        <v>4547</v>
       </c>
       <c r="Q46" t="n">
-        <v>1194</v>
+        <v>1204</v>
       </c>
       <c r="R46" t="n">
-        <v>2812</v>
+        <v>5751</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4832,17 +4824,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4854,29 +4846,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>uckyfycmko336@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4886,7 +4878,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4896,14 +4888,10 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/we2yppk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>X</t>
@@ -4915,13 +4903,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>425</v>
+        <v>75</v>
       </c>
       <c r="Q47" t="n">
-        <v>221</v>
+        <v>94</v>
       </c>
       <c r="R47" t="n">
-        <v>646</v>
+        <v>169</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4930,46 +4918,46 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>070-5250-1469</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5009,13 +4997,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5024,17 +5012,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1910693072</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910693072</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5046,24 +5034,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>hanwnsdn@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1419-2268</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5103,13 +5087,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R49" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5118,17 +5102,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5140,29 +5124,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5172,7 +5156,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5182,14 +5166,10 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfi5my</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>X</t>
@@ -5201,13 +5181,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2255</v>
+        <v>694</v>
       </c>
       <c r="Q50" t="n">
-        <v>1429</v>
+        <v>144</v>
       </c>
       <c r="R50" t="n">
-        <v>3684</v>
+        <v>838</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5216,17 +5196,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5238,29 +5218,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pressgym@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5270,24 +5250,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5i8bi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>X</t>
@@ -5299,13 +5275,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>233</v>
+        <v>1086</v>
       </c>
       <c r="Q51" t="n">
-        <v>44</v>
+        <v>864</v>
       </c>
       <c r="R51" t="n">
-        <v>277</v>
+        <v>1950</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5314,17 +5290,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5336,29 +5312,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nrkmhhuppr297@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany87</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5368,24 +5344,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcqxln1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5397,13 +5369,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>75</v>
+        <v>1463</v>
       </c>
       <c r="Q52" t="n">
-        <v>94</v>
+        <v>1726</v>
       </c>
       <c r="R52" t="n">
-        <v>169</v>
+        <v>3189</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5412,17 +5384,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5434,29 +5406,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>io15io15@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/baekyuri802</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5466,12 +5438,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5487,17 +5459,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>339</v>
       </c>
       <c r="R53" t="n">
-        <v>3</v>
+        <v>961</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5506,17 +5478,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5528,29 +5500,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5560,7 +5532,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5570,14 +5542,10 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdf2zxw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>X</t>
@@ -5585,17 +5553,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>99</v>
+        <v>1620</v>
       </c>
       <c r="Q54" t="n">
-        <v>211</v>
+        <v>1195</v>
       </c>
       <c r="R54" t="n">
-        <v>310</v>
+        <v>2815</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5604,17 +5572,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5626,29 +5594,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>https://blog.naver.com/h9a1n94</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5663,7 +5631,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5683,13 +5651,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="Q55" t="n">
-        <v>216</v>
+        <v>335</v>
       </c>
       <c r="R55" t="n">
-        <v>341</v>
+        <v>450</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5698,17 +5666,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5720,29 +5688,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5752,24 +5720,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e814</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>X</t>
@@ -5781,13 +5745,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2657</v>
+        <v>1936</v>
       </c>
       <c r="Q56" t="n">
-        <v>4788</v>
+        <v>828</v>
       </c>
       <c r="R56" t="n">
-        <v>7445</v>
+        <v>2764</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5796,81 +5760,81 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5t1ci</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5879,13 +5843,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>86</v>
+        <v>1139</v>
       </c>
       <c r="Q57" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="R57" t="n">
-        <v>177</v>
+        <v>1180</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5894,51 +5858,51 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>hegardengym_suyu-@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5948,24 +5912,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49479</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
@@ -5977,13 +5937,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="Q58" t="n">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="R58" t="n">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5992,17 +5952,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6014,24 +5974,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6061,7 +6021,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48ak4</t>
+          <t>https://talk.naver.com/ct/w481k9</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6071,17 +6031,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>694</v>
+        <v>206</v>
       </c>
       <c r="Q59" t="n">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="R59" t="n">
-        <v>836</v>
+        <v>404</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6090,46 +6050,46 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6154,14 +6114,10 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43knh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>X</t>
@@ -6169,17 +6125,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>4545</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1203</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>5748</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6188,46 +6144,46 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>070-5250-6614</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6252,10 +6208,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3azy9n</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>X</t>
@@ -6263,17 +6223,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6282,24 +6242,24 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1349373253</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349373253</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6315,13 +6275,13 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>070-4535-0883</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6376,17 +6336,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1476244634</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476244634</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6398,29 +6358,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany52</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6430,24 +6390,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f9qn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6459,13 +6415,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>113</v>
+        <v>2747</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>2339</v>
       </c>
       <c r="R63" t="n">
-        <v>118</v>
+        <v>5086</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6474,17 +6430,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6496,29 +6452,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymchoi</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6528,12 +6484,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6549,17 +6505,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>7</v>
+        <v>347</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>347</v>
       </c>
       <c r="R64" t="n">
-        <v>13</v>
+        <v>694</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6568,17 +6524,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6590,24 +6546,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6637,7 +6593,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dqzk</t>
+          <t>https://talk.naver.com/ct/w4f9qn</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6651,13 +6607,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="Q65" t="n">
-        <v>485</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>627</v>
+        <v>118</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6666,61 +6622,57 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>lifebuildingmia@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>070-5250-6614</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6730,32 +6682,28 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o0p2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6764,42 +6712,46 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>070-4535-3463</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6839,13 +6791,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6854,46 +6806,46 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6918,14 +6870,10 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ham5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6933,17 +6881,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1948</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3238</v>
+        <v>0</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6952,17 +6900,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6974,24 +6922,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>배용덕헬스</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>nicenet@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7016,14 +6964,10 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wqdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>X</t>
@@ -7031,17 +6975,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="R69" t="n">
-        <v>239</v>
+        <v>13</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7050,17 +6994,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7072,29 +7016,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7104,24 +7048,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs9wn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>X</t>
@@ -7133,13 +7073,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1086</v>
+        <v>2661</v>
       </c>
       <c r="Q70" t="n">
-        <v>852</v>
+        <v>4788</v>
       </c>
       <c r="R70" t="n">
-        <v>1938</v>
+        <v>7449</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7148,17 +7088,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7170,29 +7110,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sd670</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7202,27 +7142,23 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41vr7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7231,13 +7167,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>226</v>
+        <v>87</v>
       </c>
       <c r="Q71" t="n">
-        <v>423</v>
+        <v>235</v>
       </c>
       <c r="R71" t="n">
-        <v>649</v>
+        <v>322</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7246,17 +7182,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7268,25 +7204,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1404-1363</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7296,7 +7236,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7306,14 +7246,10 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u9vb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>X</t>
@@ -7325,13 +7261,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>246</v>
+        <v>532</v>
       </c>
       <c r="Q72" t="n">
-        <v>1343</v>
+        <v>2236</v>
       </c>
       <c r="R72" t="n">
-        <v>1589</v>
+        <v>2768</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7340,17 +7276,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7362,29 +7298,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>winnnig@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7404,14 +7340,10 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lqb7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
@@ -7419,17 +7351,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="Q73" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="R73" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7438,17 +7370,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7460,29 +7392,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://www.instagram.com/sunghyunle2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7497,7 +7429,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7517,13 +7449,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="Q74" t="n">
-        <v>1295</v>
+        <v>29</v>
       </c>
       <c r="R74" t="n">
-        <v>1373</v>
+        <v>61</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7532,17 +7464,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7554,29 +7486,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1436-2922</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_performance</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7586,7 +7518,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7596,10 +7528,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxl9x94</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7611,13 +7547,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="Q75" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7626,17 +7562,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7648,24 +7584,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7690,14 +7626,10 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9cv7l2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7709,13 +7641,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="Q76" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="R76" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7724,17 +7656,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7746,25 +7678,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1385-0454</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7774,7 +7710,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7795,17 +7731,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q77" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="R77" t="n">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7814,17 +7750,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7836,29 +7772,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1437-5900</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7868,7 +7804,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7878,14 +7814,10 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zcrh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>X</t>
@@ -7897,13 +7829,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Q78" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="R78" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7912,17 +7844,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7934,29 +7866,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1366-4502</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7966,20 +7894,24 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9vb</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -7987,17 +7919,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="Q79" t="n">
-        <v>180</v>
+        <v>1343</v>
       </c>
       <c r="R79" t="n">
-        <v>269</v>
+        <v>1590</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -8006,17 +7938,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8028,44 +7960,44 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>hyomin_nase@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/runandlift</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8085,13 +8017,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="Q80" t="n">
-        <v>501</v>
+        <v>165</v>
       </c>
       <c r="R80" t="n">
-        <v>692</v>
+        <v>244</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8100,17 +8032,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8122,20 +8054,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>forestgym24@naver.com</t>
-        </is>
-      </c>
+          <t>디와이비퍼포먼스트레이닝</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1436-2922</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8171,17 +8103,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="Q81" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="R81" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8190,17 +8122,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8212,24 +8144,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>0507-1467-8213</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8254,14 +8182,10 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdgwqtj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>X</t>
@@ -8269,17 +8193,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>545</v>
+        <v>41</v>
       </c>
       <c r="R82" t="n">
-        <v>707</v>
+        <v>42</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8288,17 +8212,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8310,24 +8234,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0507-1318-2087</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8352,10 +8272,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jtey</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
           <t>X</t>
@@ -8363,17 +8287,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="R83" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8382,17 +8306,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8404,29 +8328,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8436,12 +8360,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8461,13 +8385,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="Q84" t="n">
-        <v>220</v>
+        <v>375</v>
       </c>
       <c r="R84" t="n">
-        <v>299</v>
+        <v>521</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8476,17 +8400,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8498,29 +8422,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8530,7 +8454,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8540,14 +8464,10 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnugfn3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>X</t>
@@ -8559,13 +8479,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="Q85" t="n">
-        <v>373</v>
+        <v>220</v>
       </c>
       <c r="R85" t="n">
-        <v>519</v>
+        <v>298</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8574,17 +8494,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8596,29 +8516,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0507-1404-1363</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8628,12 +8544,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8649,17 +8565,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>532</v>
+        <v>21</v>
       </c>
       <c r="Q86" t="n">
-        <v>2236</v>
+        <v>7</v>
       </c>
       <c r="R86" t="n">
-        <v>2768</v>
+        <v>28</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8668,17 +8584,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8690,29 +8606,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1301-9491</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wellcare093</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8722,24 +8638,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxl9x94</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>X</t>
@@ -8747,17 +8659,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R87" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8766,17 +8678,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8788,30 +8700,34 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1377-5126</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>https://pf.kakao.com/_ExmdAX</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8821,7 +8737,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8832,7 +8748,7 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8841,13 +8757,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="Q88" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="R88" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8856,17 +8772,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8878,24 +8794,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8925,12 +8841,12 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4utrl</t>
+          <t>https://talk.naver.com/ct/w45d9r</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8939,13 +8855,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>637</v>
+        <v>78</v>
       </c>
       <c r="Q89" t="n">
-        <v>699</v>
+        <v>1298</v>
       </c>
       <c r="R89" t="n">
-        <v>1336</v>
+        <v>1376</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8954,17 +8870,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8976,24 +8892,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9023,7 +8939,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wu8v0g9</t>
+          <t>https://talk.naver.com/ct/w4zmep</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -9037,13 +8953,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>28</v>
+        <v>193</v>
       </c>
       <c r="Q90" t="n">
-        <v>47</v>
+        <v>501</v>
       </c>
       <c r="R90" t="n">
-        <v>75</v>
+        <v>694</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -9052,17 +8968,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9074,24 +8990,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1385-0454</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9121,12 +9037,12 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7t3tx8</t>
+          <t>https://talk.naver.com/ct/w4utrl</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9135,13 +9051,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>43</v>
+        <v>637</v>
       </c>
       <c r="Q91" t="n">
-        <v>60</v>
+        <v>699</v>
       </c>
       <c r="R91" t="n">
-        <v>103</v>
+        <v>1336</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9150,17 +9066,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9172,29 +9088,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9204,12 +9120,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9220,7 +9136,7 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9229,13 +9145,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="Q92" t="n">
-        <v>51</v>
+        <v>547</v>
       </c>
       <c r="R92" t="n">
-        <v>72</v>
+        <v>709</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9244,17 +9160,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9269,11 +9185,7 @@
           <t>DL 운동센터</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>gunwigun_official@naver.com</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
@@ -9344,7 +9256,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>070-5250-6614</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blueskirt0704</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,29 +653,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>io15io15@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -718,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>175</v>
+        <v>1331</v>
       </c>
       <c r="Q4" t="n">
-        <v>130</v>
+        <v>885</v>
       </c>
       <c r="R4" t="n">
-        <v>305</v>
+        <v>2216</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>가인헬스클럽</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9thbkj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -966,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ham5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1042,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1074,24 +1066,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r5j3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1103,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1717</v>
+        <v>1086</v>
       </c>
       <c r="Q7" t="n">
-        <v>385</v>
+        <v>864</v>
       </c>
       <c r="R7" t="n">
-        <v>2102</v>
+        <v>1950</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,29 +1128,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1359-6850</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/f45suyu/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1172,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1182,17 +1166,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sncb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1201,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Q8" t="n">
-        <v>320</v>
+        <v>161</v>
       </c>
       <c r="R8" t="n">
-        <v>423</v>
+        <v>252</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,25 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02-997-7330</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://cafe.naver.com/curves</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1266,12 +1250,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1287,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,34 +1312,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1365,22 +1349,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o0p2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1389,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>322</v>
+        <v>4547</v>
       </c>
       <c r="Q10" t="n">
-        <v>580</v>
+        <v>1204</v>
       </c>
       <c r="R10" t="n">
-        <v>902</v>
+        <v>5751</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1421,34 +1401,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1458,24 +1438,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4toem</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1487,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="R11" t="n">
-        <v>359</v>
+        <v>181</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1524,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1556,12 +1532,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1572,7 +1548,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1581,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1812</v>
+        <v>821</v>
       </c>
       <c r="Q12" t="n">
-        <v>1185</v>
+        <v>559</v>
       </c>
       <c r="R12" t="n">
-        <v>2997</v>
+        <v>1380</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1596,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1618,59 +1594,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wqdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1679,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>28</v>
+        <v>1139</v>
       </c>
       <c r="Q13" t="n">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="R13" t="n">
-        <v>239</v>
+        <v>1180</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1694,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1711,44 +1687,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1764,22 +1740,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1788,12 +1764,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1805,34 +1781,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>somedayday00@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>myeonghui5402@gmail.com</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1842,7 +1822,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1852,14 +1832,10 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpw1lb4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1867,17 +1843,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>334</v>
+        <v>86</v>
       </c>
       <c r="Q15" t="n">
-        <v>365</v>
+        <v>91</v>
       </c>
       <c r="R15" t="n">
-        <v>699</v>
+        <v>177</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1886,12 +1862,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1908,24 +1884,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>배용덕헬스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>nicenet@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,14 +1926,10 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47wce</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>X</t>
@@ -1965,17 +1937,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1984,12 +1956,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2006,29 +1978,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hegardengym_suyu-@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2038,7 +2010,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2048,14 +2020,10 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49479</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>X</t>
@@ -2067,13 +2035,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>37</v>
+        <v>426</v>
       </c>
       <c r="Q17" t="n">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="R17" t="n">
-        <v>93</v>
+        <v>647</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2082,12 +2050,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2099,34 +2067,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2136,27 +2104,23 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w405s2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2165,13 +2129,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>230</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>814</v>
+        <v>47</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2180,12 +2144,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2202,29 +2166,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>https://blog.naver.com/blueskirt0704</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2250,7 +2214,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2259,13 +2223,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>226</v>
+        <v>142</v>
       </c>
       <c r="Q19" t="n">
-        <v>423</v>
+        <v>503</v>
       </c>
       <c r="R19" t="n">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2274,12 +2238,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2296,29 +2260,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/axis_pt</t>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2333,7 +2297,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2344,7 +2308,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2353,13 +2317,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="R20" t="n">
-        <v>69</v>
+        <v>423</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2368,12 +2332,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2385,34 +2349,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2422,12 +2386,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2443,17 +2407,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1417</v>
+        <v>0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2462,12 +2426,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2484,24 +2448,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2526,32 +2490,28 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wellmvw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>821</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>559</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1380</v>
+        <v>11</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2560,12 +2520,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2582,29 +2542,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/enermeca2/</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2619,7 +2579,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2630,7 +2590,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2639,13 +2599,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1331</v>
+        <v>226</v>
       </c>
       <c r="Q23" t="n">
-        <v>885</v>
+        <v>423</v>
       </c>
       <c r="R23" t="n">
-        <v>2216</v>
+        <v>649</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2654,12 +2614,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2676,29 +2636,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gungympt</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2733,13 +2693,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>426</v>
+        <v>1620</v>
       </c>
       <c r="Q24" t="n">
-        <v>221</v>
+        <v>1195</v>
       </c>
       <c r="R24" t="n">
-        <v>647</v>
+        <v>2815</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2748,12 +2708,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2770,29 +2730,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>419gym@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/419gym_official</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2802,7 +2762,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2823,17 +2783,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R25" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2842,12 +2802,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2859,34 +2819,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://blog.naver.com/trend_hd4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2921,13 +2881,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>2264</v>
       </c>
       <c r="Q26" t="n">
-        <v>157</v>
+        <v>1432</v>
       </c>
       <c r="R26" t="n">
-        <v>181</v>
+        <v>3696</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2936,12 +2896,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2958,29 +2918,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietmode-</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3006,22 +2966,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="n">
-        <v>211</v>
+        <v>44</v>
       </c>
       <c r="R27" t="n">
-        <v>310</v>
+        <v>69</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3030,12 +2990,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3052,29 +3012,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>bum903@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bum903</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3084,12 +3044,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3105,17 +3065,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3124,12 +3084,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3141,38 +3101,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>NH FITNESS CLUB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>myeonghui5402@gmail.com</t>
-        </is>
-      </c>
+          <t>jjoseohyun@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3182,7 +3138,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3203,17 +3159,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="Q29" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3222,12 +3178,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3244,25 +3200,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1344-1650</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nyh314</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3272,42 +3232,38 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wy43x6v</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>91</v>
+        <v>334</v>
       </c>
       <c r="Q30" t="n">
-        <v>161</v>
+        <v>365</v>
       </c>
       <c r="R30" t="n">
-        <v>252</v>
+        <v>699</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3316,12 +3272,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3338,29 +3294,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3370,7 +3326,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3380,17 +3336,13 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yudn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3399,13 +3351,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>462</v>
+        <v>1717</v>
       </c>
       <c r="Q31" t="n">
-        <v>795</v>
+        <v>388</v>
       </c>
       <c r="R31" t="n">
-        <v>1257</v>
+        <v>2105</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3414,12 +3366,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3436,29 +3388,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ask4554</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3468,24 +3420,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfi5my</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3493,17 +3441,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2264</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>1432</v>
+        <v>202</v>
       </c>
       <c r="R32" t="n">
-        <v>3696</v>
+        <v>212</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3512,12 +3460,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3534,34 +3482,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3571,7 +3519,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3587,17 +3535,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>10</v>
+        <v>1811</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>1185</v>
       </c>
       <c r="R33" t="n">
-        <v>11</v>
+        <v>2996</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3606,12 +3554,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3628,24 +3576,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>uptfitness@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1370-4554</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3685,13 +3629,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>202</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>212</v>
+        <v>7</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3700,12 +3644,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3722,52 +3666,52 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>02-986-0188</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc215t</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3775,17 +3719,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>193</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>280</v>
+        <v>3</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3794,12 +3738,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3816,29 +3760,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>hsyqz13@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany87</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3848,12 +3792,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3873,13 +3817,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>114</v>
+        <v>1463</v>
       </c>
       <c r="Q36" t="n">
-        <v>125</v>
+        <v>1726</v>
       </c>
       <c r="R36" t="n">
-        <v>239</v>
+        <v>3189</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3888,12 +3832,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3905,25 +3849,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3963,13 +3911,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3978,12 +3926,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4000,29 +3948,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4057,13 +4005,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>95</v>
+        <v>2659</v>
       </c>
       <c r="Q38" t="n">
-        <v>297</v>
+        <v>4788</v>
       </c>
       <c r="R38" t="n">
-        <v>392</v>
+        <v>7447</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4072,12 +4020,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4094,29 +4042,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4126,7 +4074,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4147,17 +4095,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="R39" t="n">
-        <v>54</v>
+        <v>343</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4166,12 +4114,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4188,29 +4136,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjfit_7707</t>
+          <t>https://blog.naver.com/baekyuri802</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4225,7 +4173,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4245,13 +4193,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>10</v>
+        <v>622</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="R40" t="n">
-        <v>10</v>
+        <v>961</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4260,12 +4208,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4282,34 +4230,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4339,13 +4287,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>351</v>
+        <v>694</v>
       </c>
       <c r="Q41" t="n">
-        <v>616</v>
+        <v>144</v>
       </c>
       <c r="R41" t="n">
-        <v>967</v>
+        <v>838</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4354,12 +4302,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4376,29 +4324,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>uckyfycmko336@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/curves</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4408,20 +4356,24 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcqxln1</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>X</t>
@@ -4433,13 +4385,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="R42" t="n">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4448,12 +4400,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4465,34 +4417,34 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4502,12 +4454,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4523,17 +4475,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4542,12 +4494,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4564,34 +4516,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4612,7 +4564,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4621,13 +4573,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>239</v>
+        <v>689</v>
       </c>
       <c r="Q44" t="n">
-        <v>106</v>
+        <v>728</v>
       </c>
       <c r="R44" t="n">
-        <v>345</v>
+        <v>1417</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4636,12 +4588,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4658,29 +4610,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>codelegend@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pressgym___</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4695,7 +4647,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4715,13 +4667,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>234</v>
+        <v>95</v>
       </c>
       <c r="Q45" t="n">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="R45" t="n">
-        <v>279</v>
+        <v>392</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4730,12 +4682,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4752,29 +4704,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>codelegend@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>https://www.instagram.com/pressgym___</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4789,7 +4741,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4809,13 +4761,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4547</v>
+        <v>234</v>
       </c>
       <c r="Q46" t="n">
-        <v>1204</v>
+        <v>45</v>
       </c>
       <c r="R46" t="n">
-        <v>5751</v>
+        <v>279</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4824,12 +4776,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4846,29 +4798,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>uckyfycmko336@naver.com</t>
+          <t>hanwnsdn@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1380-1962</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4878,7 +4826,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4899,17 +4847,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="Q47" t="n">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="R47" t="n">
-        <v>169</v>
+        <v>14</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4918,12 +4866,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4940,29 +4888,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ssdaw1234</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4972,12 +4920,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4993,17 +4941,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="R48" t="n">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5012,12 +4960,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5034,25 +4982,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1321-8296</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymchoi</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5062,12 +5014,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5083,17 +5035,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>7</v>
+        <v>347</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>347</v>
       </c>
       <c r="R49" t="n">
-        <v>14</v>
+        <v>694</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5102,12 +5054,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5124,29 +5076,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifeplus_bd/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5156,7 +5108,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5181,13 +5133,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>694</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>838</v>
+        <v>10</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5196,12 +5148,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5218,29 +5170,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1430-3344</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5255,7 +5203,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5275,13 +5223,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1086</v>
+        <v>87</v>
       </c>
       <c r="Q51" t="n">
-        <v>864</v>
+        <v>193</v>
       </c>
       <c r="R51" t="n">
-        <v>1950</v>
+        <v>280</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5290,12 +5238,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5312,29 +5260,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany87</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5344,20 +5292,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdf2zxw</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5365,17 +5317,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1463</v>
+        <v>99</v>
       </c>
       <c r="Q52" t="n">
-        <v>1726</v>
+        <v>211</v>
       </c>
       <c r="R52" t="n">
-        <v>3189</v>
+        <v>310</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5384,12 +5336,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5406,29 +5358,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>junggyo777@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baekyuri802</t>
+          <t>https://www.instagram.com/team_whale_mia</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5443,7 +5395,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5463,13 +5415,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>622</v>
+        <v>114</v>
       </c>
       <c r="Q53" t="n">
-        <v>339</v>
+        <v>125</v>
       </c>
       <c r="R53" t="n">
-        <v>961</v>
+        <v>239</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5478,12 +5430,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5495,34 +5447,34 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>thebarunpt@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5537,15 +5489,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7sz75u</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>X</t>
@@ -5557,13 +5513,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1620</v>
+        <v>80</v>
       </c>
       <c r="Q54" t="n">
-        <v>1195</v>
+        <v>104</v>
       </c>
       <c r="R54" t="n">
-        <v>2815</v>
+        <v>184</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5572,12 +5528,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5594,29 +5550,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h9a1n94</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5626,12 +5582,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5647,17 +5603,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="Q55" t="n">
-        <v>335</v>
+        <v>16</v>
       </c>
       <c r="R55" t="n">
-        <v>450</v>
+        <v>54</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5666,12 +5622,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5782,33 +5738,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>fa_sport@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5843,13 +5795,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1139</v>
+        <v>239</v>
       </c>
       <c r="Q57" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="R57" t="n">
-        <v>1180</v>
+        <v>345</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5858,12 +5810,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5880,29 +5832,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5912,23 +5864,27 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405s2</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5937,13 +5893,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="Q58" t="n">
-        <v>104</v>
+        <v>584</v>
       </c>
       <c r="R58" t="n">
-        <v>184</v>
+        <v>814</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5952,12 +5908,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5974,24 +5930,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6016,14 +5972,10 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w481k9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>X</t>
@@ -6031,17 +5983,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="Q59" t="n">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="R59" t="n">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6050,12 +6002,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6166,24 +6118,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6213,12 +6165,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3azy9n</t>
+          <t>https://talk.naver.com/ct/w5yudn</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6227,13 +6179,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>125</v>
+        <v>462</v>
       </c>
       <c r="Q61" t="n">
-        <v>218</v>
+        <v>795</v>
       </c>
       <c r="R61" t="n">
-        <v>343</v>
+        <v>1257</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6242,12 +6194,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6259,29 +6211,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6321,13 +6273,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6336,12 +6288,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6380,7 +6332,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6390,20 +6342,24 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40kte</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6415,13 +6371,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="Q63" t="n">
         <v>2339</v>
       </c>
       <c r="R63" t="n">
-        <v>5086</v>
+        <v>5085</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6452,29 +6408,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>더블플러스휘트니스클럽</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6484,12 +6440,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6505,17 +6461,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>347</v>
+        <v>7</v>
       </c>
       <c r="Q64" t="n">
-        <v>347</v>
+        <v>6</v>
       </c>
       <c r="R64" t="n">
-        <v>694</v>
+        <v>13</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6524,12 +6480,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6546,24 +6502,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6593,7 +6549,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f9qn</t>
+          <t>https://talk.naver.com/ct/w5wqdd</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6607,13 +6563,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>211</v>
       </c>
       <c r="R65" t="n">
-        <v>118</v>
+        <v>239</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6622,12 +6578,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6639,25 +6595,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>에스핏 휘트니스 수유점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>kdhonepick@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>070-5250-6614</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6682,10 +6642,14 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4toem</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>X</t>
@@ -6693,17 +6657,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6712,12 +6676,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1349373253</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349373253</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6729,44 +6693,44 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>070-4535-3463</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6776,10 +6740,14 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wui0kyi</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6787,17 +6755,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6806,12 +6774,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6823,29 +6791,29 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>070-4535-0883</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6870,10 +6838,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9qn</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6881,17 +6853,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6900,12 +6872,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1476244634</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476244634</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6922,24 +6894,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>nicenet@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6975,17 +6947,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="Q69" t="n">
-        <v>13</v>
+        <v>335</v>
       </c>
       <c r="R69" t="n">
-        <v>13</v>
+        <v>450</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6994,12 +6966,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7016,29 +6988,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7048,20 +7020,24 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jggy</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>X</t>
@@ -7073,13 +7049,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2661</v>
+        <v>87</v>
       </c>
       <c r="Q70" t="n">
-        <v>4788</v>
+        <v>235</v>
       </c>
       <c r="R70" t="n">
-        <v>7449</v>
+        <v>322</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7088,12 +7064,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7110,29 +7086,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sd670</t>
+          <t>http://blog.naver.com/herricane</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7163,17 +7139,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="Q71" t="n">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="R71" t="n">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7182,12 +7158,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7204,29 +7180,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1404-1363</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7261,13 +7237,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="Q72" t="n">
-        <v>2236</v>
+        <v>220</v>
       </c>
       <c r="R72" t="n">
-        <v>2768</v>
+        <v>298</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7276,12 +7252,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7298,34 +7274,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>https://pf.kakao.com/_ExmdAX</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7335,7 +7311,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7346,22 +7322,22 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="Q73" t="n">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="R73" t="n">
-        <v>269</v>
+        <v>76</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7370,12 +7346,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7392,29 +7368,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1437-5900</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunghyunle2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7424,7 +7396,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7445,17 +7417,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="R74" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7464,12 +7436,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7486,29 +7458,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1301-9491</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7518,24 +7486,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxl9x94</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7547,13 +7511,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R75" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7562,12 +7526,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7584,29 +7548,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sunghyunle2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7616,7 +7580,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7637,17 +7601,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="R76" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7656,12 +7620,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7678,29 +7642,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>hyomin_nase@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1385-0454</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.dailypt</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7715,7 +7679,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7735,13 +7699,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="Q77" t="n">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="R77" t="n">
-        <v>107</v>
+        <v>244</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7750,12 +7714,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7772,29 +7736,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymseungeun/</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7809,7 +7773,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7829,13 +7793,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="Q78" t="n">
-        <v>47</v>
+        <v>375</v>
       </c>
       <c r="R78" t="n">
-        <v>76</v>
+        <v>521</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7844,12 +7808,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7866,25 +7830,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1301-9491</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hypedobby</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7894,7 +7862,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7904,14 +7872,10 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u9vb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -7923,13 +7887,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="Q79" t="n">
-        <v>1343</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>1590</v>
+        <v>40</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7938,12 +7902,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7960,44 +7924,44 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>https://smartstore.naver.com/runandlift</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8017,13 +7981,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="Q80" t="n">
-        <v>165</v>
+        <v>501</v>
       </c>
       <c r="R80" t="n">
-        <v>244</v>
+        <v>694</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8032,12 +7996,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8054,25 +8018,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>goodfit9008@naver.com</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>0507-1436-2922</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8082,12 +8046,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8107,13 +8071,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="Q81" t="n">
-        <v>59</v>
+        <v>1343</v>
       </c>
       <c r="R81" t="n">
-        <v>116</v>
+        <v>1590</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8122,12 +8086,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8144,25 +8108,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1385-0454</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8172,7 +8140,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8193,17 +8161,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q82" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="R82" t="n">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8212,12 +8180,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8234,25 +8202,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>디와이비퍼포먼스트레이닝</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1436-2922</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dyb_performance</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8262,7 +8234,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8272,14 +8244,10 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jtey</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>X</t>
@@ -8291,13 +8259,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Q83" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="R83" t="n">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8306,12 +8274,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8328,29 +8296,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8385,13 +8353,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="Q84" t="n">
-        <v>375</v>
+        <v>1300</v>
       </c>
       <c r="R84" t="n">
-        <v>521</v>
+        <v>1378</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8400,12 +8368,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8422,29 +8390,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8479,13 +8447,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="Q85" t="n">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="R85" t="n">
-        <v>298</v>
+        <v>76</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8494,12 +8462,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8516,25 +8484,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1404-1363</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestgym24/223778254580</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8549,7 +8521,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8565,17 +8537,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>21</v>
+        <v>532</v>
       </c>
       <c r="Q86" t="n">
-        <v>7</v>
+        <v>2236</v>
       </c>
       <c r="R86" t="n">
-        <v>28</v>
+        <v>2768</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8584,12 +8556,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8606,29 +8578,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8638,38 +8610,42 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4utrl</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>8</v>
+        <v>637</v>
       </c>
       <c r="Q87" t="n">
-        <v>53</v>
+        <v>699</v>
       </c>
       <c r="R87" t="n">
-        <v>61</v>
+        <v>1336</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8678,12 +8654,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8700,39 +8676,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ExmdAX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8742,13 +8718,17 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdgwqtj</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8757,13 +8737,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="Q88" t="n">
-        <v>54</v>
+        <v>547</v>
       </c>
       <c r="R88" t="n">
-        <v>76</v>
+        <v>709</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8772,12 +8752,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8794,29 +8774,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8826,24 +8806,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45d9r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>X</t>
@@ -8851,17 +8827,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="Q89" t="n">
-        <v>1298</v>
+        <v>180</v>
       </c>
       <c r="R89" t="n">
-        <v>1376</v>
+        <v>269</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8870,12 +8846,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8892,24 +8868,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8939,7 +8915,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4zmep</t>
+          <t>https://talk.naver.com/ct/w9cv7l2</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -8949,17 +8925,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="Q90" t="n">
-        <v>501</v>
+        <v>53</v>
       </c>
       <c r="R90" t="n">
-        <v>694</v>
+        <v>61</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8968,12 +8944,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8990,24 +8966,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0507-1485-1323</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9032,32 +9004,28 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4utrl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>637</v>
+        <v>21</v>
       </c>
       <c r="Q91" t="n">
-        <v>699</v>
+        <v>7</v>
       </c>
       <c r="R91" t="n">
-        <v>1336</v>
+        <v>28</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9066,12 +9034,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9088,29 +9056,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9120,12 +9088,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9141,17 +9109,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="Q92" t="n">
-        <v>547</v>
+        <v>10</v>
       </c>
       <c r="R92" t="n">
-        <v>709</v>
+        <v>43</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9160,12 +9128,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9185,7 +9153,11 @@
           <t>DL 운동센터</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>gunwigun_official@naver.com</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>myeonghui5402@gmail.com</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +605,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e814</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2659</v>
+        <v>86</v>
       </c>
       <c r="Q2" t="n">
-        <v>4788</v>
+        <v>91</v>
       </c>
       <c r="R2" t="n">
-        <v>7447</v>
+        <v>177</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>https://www.instagram.com/kdhonepick</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +699,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43knh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4547</v>
+        <v>116</v>
       </c>
       <c r="Q3" t="n">
-        <v>1204</v>
+        <v>243</v>
       </c>
       <c r="R3" t="n">
-        <v>5751</v>
+        <v>359</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +788,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs9wn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1086</v>
+        <v>38</v>
       </c>
       <c r="Q4" t="n">
-        <v>865</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>1951</v>
+        <v>54</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>https://blog.naver.com/gymchoi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40kte</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2746</v>
+        <v>347</v>
       </c>
       <c r="Q5" t="n">
-        <v>2339</v>
+        <v>347</v>
       </c>
       <c r="R5" t="n">
-        <v>5085</v>
+        <v>694</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>uckyfycmko336@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r5j3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1717</v>
+        <v>75</v>
       </c>
       <c r="Q6" t="n">
-        <v>389</v>
+        <v>94</v>
       </c>
       <c r="R6" t="n">
-        <v>2106</v>
+        <v>169</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>codelegend@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pressgym___</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1075,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5i8bi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>234</v>
+        <v>95</v>
       </c>
       <c r="Q7" t="n">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="R7" t="n">
-        <v>279</v>
+        <v>392</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trend_hd4</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1194,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfi5my</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2264</v>
+        <v>689</v>
       </c>
       <c r="Q8" t="n">
-        <v>1432</v>
+        <v>728</v>
       </c>
       <c r="R8" t="n">
-        <v>3696</v>
+        <v>1417</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,44 +1221,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>wefit100@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ZWKxjn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,32 +1264,28 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wellmvw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>821</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,96 +1311,7830 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>https://blog.naver.com/acrogym1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1936</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>828</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2764</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1492139790</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1492139790</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>woojoogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1354-5063</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://litt.ly/woojoogym</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>616</v>
+      </c>
+      <c r="R11" t="n">
+        <v>967</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1022408622</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1022408622</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>크로스핏FA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fa_sport@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02-990-1317</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://www.fasports.kr/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>106</v>
+      </c>
+      <c r="R12" t="n">
+        <v>345</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1623128626</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1623128626</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>070-5250-6614</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 번동</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1349373253</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349373253</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lifebuildingmia@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1332-1672</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://landing-mia-ebon.vercel.app/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>581</v>
+      </c>
+      <c r="R14" t="n">
+        <v>902</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>36362933</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36362933</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ready4gymsuyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1430-3344</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1086</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>867</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1953</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>38648497</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38648497</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>highend_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1417-2362</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1811</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1185</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2996</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1953510990</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1953510990</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>find_me_pt_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1478-5103</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>423</v>
+      </c>
+      <c r="R17" t="n">
+        <v>649</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1116831923</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1116831923</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>uphoria6825@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1334-6825</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uphoria_mia_1/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>584</v>
+      </c>
+      <c r="R18" t="n">
+        <v>814</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1037773645</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037773645</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>070-5250-1469</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1910693072</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1910693072</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SK북한산시티 헬스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>tjdghksfl20@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02-987-0111</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 174</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>44</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1259645750</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1259645750</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>419gym</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>419gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1433-5131</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/419gym_official</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>56</v>
+      </c>
+      <c r="R21" t="n">
+        <v>93</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1310458215</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1310458215</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>에너메카 휘트니스 미아점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nyh314@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1344-1650</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nyh314</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>365</v>
+      </c>
+      <c r="R22" t="n">
+        <v>699</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>37615690</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37615690</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>프레스짐 헬스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>codelegend@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1344-9688</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pressgym___</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>279</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1695685266</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1695685266</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>스포애니 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>spoany87@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1338-9618</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany87</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1463</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1726</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3189</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1790576623</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1790576623</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>미아동주민자치위원회 헬스장</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>hanwnsdn@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>14</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1404617649</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404617649</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>밀리언짐 수유점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>milliongym-suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1357-9092</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/milliongym-suyu</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>47</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2061019894</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2061019894</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>제이짐 휘트니스 4.19점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>herricane@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>02-999-9905</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://blog.naver.com/herricane</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>206</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>198</v>
+      </c>
+      <c r="R27" t="n">
+        <v>404</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>37174895</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37174895</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>위핏헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>wefit100@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1490-2127</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>821</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>559</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1380</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1661637243</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1661637243</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>F45 수유</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>f45_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45suyu/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>161</v>
+      </c>
+      <c r="R29" t="n">
+        <v>252</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1853806359</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853806359</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rkdqnr7184@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1336-7184</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QERxeG</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>462</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>795</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1257</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1172555749</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172555749</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dwgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1370-7849</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dwgym1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>2659</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4787</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7446</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1284235115</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284235115</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>woojoogym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1362-5063</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>218</v>
+      </c>
+      <c r="R32" t="n">
+        <v>343</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2089127568</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2089127568</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>io15io15@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>02-986-0188</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 숭인로 39</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1185468645</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185468645</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M스피닝 강사 교육</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>m_spinning@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://www.mspinning.co.kr/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>193</v>
+      </c>
+      <c r="R34" t="n">
+        <v>280</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>31222668</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31222668</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>미아동헬스장</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>uptfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로61길 46</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>18603866</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18603866</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>blueskirt0704@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1338-1501</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blueskirt0704</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>507</v>
+      </c>
+      <c r="R36" t="n">
+        <v>649</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1914282686</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914282686</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>엘투휘트니스 수유번동점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1369-2202</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>11</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2045876824</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2045876824</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>팀웨일 트레이닝 미아</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>junggyo777@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1417-7120</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/team_whale_mia</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>125</v>
+      </c>
+      <c r="R38" t="n">
+        <v>239</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1430890119</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1430890119</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>크로스핏샤크</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>fatdogxp@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1386-8834</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfitshark_jangwi</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>211</v>
+      </c>
+      <c r="R39" t="n">
+        <v>239</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1209016130</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1209016130</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>노블휘트니스</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>noble_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1421-2221</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/noble_fitness</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>130</v>
+      </c>
+      <c r="R40" t="n">
+        <v>305</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>36246823</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36246823</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>070-4535-8515</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유동</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1239590728</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1239590728</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1306-3451</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>13</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1035955167</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1035955167</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>피트니스 베네핏 수유역점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>baekyuri802@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1351-2438</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/baekyuri802</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>339</v>
+      </c>
+      <c r="R43" t="n">
+        <v>961</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1550724103</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1550724103</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>에이블짐 수유점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ablegym33@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1340-7281</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>4547</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1204</v>
+      </c>
+      <c r="R44" t="n">
+        <v>5751</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1745960523</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1745960523</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>070-4535-0870</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1865696490</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1865696490</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>trend_hd4@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02-988-3124</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trend_hd4</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>2264</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1432</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3696</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1885902314</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1885902314</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>제이핏 여성전용피티샵</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>02-982-7707</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jjfit_7707</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>804545907</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/804545907</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>소울휘트니스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h9a1n94@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>02-985-5553</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/h9a1n94</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>335</v>
+      </c>
+      <c r="R48" t="n">
+        <v>450</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>37240884</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37240884</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>빌리프짐 수유점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>beliefgym4@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1343-9679</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1620</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2815</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1058492468</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1058492468</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>070-4535-3463</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 우이동</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1779765773</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1779765773</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>라이프플러스휘트니스 번동점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lifeplus1209@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1362-4534</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>694</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>144</v>
+      </c>
+      <c r="R51" t="n">
+        <v>838</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1877606346</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1877606346</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NH FITNESS CLUB</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>jjoseohyun@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>02-903-7009</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>8</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>37438317</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37438317</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>배용덕헬스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02-980-2004</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로46길 15</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>13</v>
+      </c>
+      <c r="R53" t="n">
+        <v>13</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>13158296</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13158296</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ask4554@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1370-4554</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ask4554</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>202</v>
+      </c>
+      <c r="R54" t="n">
+        <v>212</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1735126857</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735126857</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>범휘트니스  수유점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bum903@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1409-0851</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 293</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bum903</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>20</v>
+      </c>
+      <c r="R55" t="n">
+        <v>57</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>13162791</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13162791</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>바디채널 광산사거리점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bodyfit_@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1359-6850</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>320</v>
+      </c>
+      <c r="R56" t="n">
+        <v>423</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1089484623</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089484623</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>엑시스피티</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>axis_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1339-8603</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/axis_pt</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>44</v>
+      </c>
+      <c r="R57" t="n">
+        <v>69</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2055534881</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2055534881</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>프리원핏 수유점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>osbum0224@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1301-1607</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/freewantfit_suyu/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>119</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1611482879</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1611482879</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>플로리다휘트니스 삼양동점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sd670@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1417-9917</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sd670</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>235</v>
+      </c>
+      <c r="R59" t="n">
+        <v>322</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>33937785</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33937785</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>drawgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1304-4992</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/drawgym</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1289</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1949</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3238</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1268963442</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1268963442</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>다이어트모드 휘트니스 수유점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>dietmode-@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1301-8244</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dietmode-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>211</v>
+      </c>
+      <c r="R61" t="n">
+        <v>310</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>37637672</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37637672</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>스포애니 수유역점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>spoany52@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1310-9628</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany52</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>2747</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2339</v>
+      </c>
+      <c r="R62" t="n">
+        <v>5086</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1440007035</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1440007035</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>02-986-2534</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://www.thebarunfitness.com</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>104</v>
+      </c>
+      <c r="R63" t="n">
+        <v>184</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>38636716</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38636716</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>더 퍼스트짐</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ssdaw1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1353-7541</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ssdaw1234</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>93</v>
+      </c>
+      <c r="R64" t="n">
+        <v>117</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1176777711</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176777711</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>에너메카휘트니스 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nyh314@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1320-7744</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enermeca2/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1332</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>885</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2217</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1756863852</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1756863852</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>97_cosat@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1308-4535</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유로 81 3층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/97_cosat</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>157</v>
+      </c>
+      <c r="R66" t="n">
+        <v>181</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1604797933</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1604797933</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>가인헬스클럽</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1419-2268</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>10</v>
+      </c>
+      <c r="R67" t="n">
+        <v>10</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1434719389</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1434719389</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 수유역점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02-990-3912</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1717</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>391</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2108</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1985390755</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1985390755</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>건짐 수유역점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>gungympt@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1459-7599</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gungympt</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>426</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>221</v>
+      </c>
+      <c r="R69" t="n">
+        <v>647</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1381178715</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1381178715</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>커브스 수유클럽</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>haon8312@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>02-997-7330</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/curves</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>7</v>
+      </c>
+      <c r="R70" t="n">
+        <v>50</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>36906152</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36906152</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 미아사거리역점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1391-2161</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1139</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>41</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1180</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2099546838</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099546838</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>존버짐 미아뉴타운점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jonbergym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1368-4511</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jonbergym3</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>220</v>
+      </c>
+      <c r="R72" t="n">
+        <v>298</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1293414126</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293414126</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>이성현퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sunghyunle2@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1437-5900</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sunghyunle2</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>29</v>
+      </c>
+      <c r="R73" t="n">
+        <v>61</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>35384521</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35384521</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>the GoodFit</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>goodfit9008@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodfit9008</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>19</v>
+      </c>
+      <c r="R74" t="n">
+        <v>21</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1222324632</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1222324632</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>올레이디짐 가오리점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>hyomin_nase@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1369-0010</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://allladygym.imweb.me/</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>165</v>
+      </c>
+      <c r="R75" t="n">
+        <v>244</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1633562526</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1633562526</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>라이프빌딩PT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>life_building_@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1404-1363</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2236</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2768</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1906517072</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1906517072</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>핏의공식</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>gymseungeun@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1458-1884</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wu8v0g9</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
         <v>29</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q77" t="n">
         <v>47</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R77" t="n">
         <v>76</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
         <is>
           <t>2024627135</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>97_cosat@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1467-8213</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/97_cosat</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>547</v>
+      </c>
+      <c r="R78" t="n">
+        <v>709</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1431265273</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1431265273</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>블랙핏pt샵 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>blackfit123@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1309-1030</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blackfit123</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>375</v>
+      </c>
+      <c r="R79" t="n">
+        <v>521</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1105932712</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105932712</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>크로스핏 알앤엘 수유</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>crossfitrnl_su@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1382-4849</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/runandlift</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>501</v>
+      </c>
+      <c r="R80" t="n">
+        <v>694</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>31777480</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31777480</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>wellcare093@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1404-1390</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wellcare093</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>53</v>
+      </c>
+      <c r="R81" t="n">
+        <v>61</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2039688284</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2039688284</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>핏라인점핑</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>shinycaptain@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>41</v>
+      </c>
+      <c r="R82" t="n">
+        <v>42</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1880264222</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1880264222</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>데일리PT샵 미아본점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>dailypt0926@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1362-0934</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 98</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dailypt0926</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1378</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1069239956</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1069239956</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>버클필라테스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>buckle1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1485-1323</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>637</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>699</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1336</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1358291633</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1358291633</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>디와이비퍼포먼스트레이닝</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1436-2922</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dyb_performance</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>59</v>
+      </c>
+      <c r="R85" t="n">
+        <v>116</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1667051610</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1667051610</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>goodfit9008@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodfit9008</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1343</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1590</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1850055844</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850055844</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>하이프핏, 수유PT샵</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>her__zz@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1301-9491</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hypedobby</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>40</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2099905937</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099905937</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>올바른PT 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>olbareunpt4_@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1366-4502</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/olbareunpt4_</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>180</v>
+      </c>
+      <c r="R88" t="n">
+        <v>269</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1034422634</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034422634</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>dailygrouppt@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1385-0454</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luv.dailypt</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>64</v>
+      </c>
+      <c r="R89" t="n">
+        <v>107</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2069382925</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2069382925</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>통증&amp;교정연구소</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>xtmxjax@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1318-2087</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/xtmxjax</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>10</v>
+      </c>
+      <c r="R90" t="n">
+        <v>43</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1975301409</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975301409</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>포레스트PT짐</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>forestgym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>7</v>
+      </c>
+      <c r="R91" t="n">
+        <v>28</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1008319723</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1008319723</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>수유 재활운동센터 라이프리턴</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>lifereturn_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1377-5126</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_ExmdAX</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>55</v>
+      </c>
+      <c r="R92" t="n">
+        <v>77</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>2013060255</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013060255</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>체력단련,운동</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DL 운동센터</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>gunwigun_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로22가길 11 2층 201호</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://litt.ly/d.l.trainer</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1479834103</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479834103</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -559,38 +559,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>myeonghui5402@gmail.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -600,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -621,17 +613,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,34 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -719,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>116</v>
+        <v>351</v>
       </c>
       <c r="Q3" t="n">
-        <v>243</v>
+        <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>359</v>
+        <v>967</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,29 +743,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sukja7820@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -813,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +816,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>https://blog.naver.com/sd670</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -907,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>347</v>
+        <v>87</v>
       </c>
       <c r="Q5" t="n">
-        <v>347</v>
+        <v>235</v>
       </c>
       <c r="R5" t="n">
-        <v>694</v>
+        <v>322</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -939,39 +927,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>uckyfycmko336@naver.com</t>
+          <t>honeymusclegym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1001,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="R6" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1004,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1033,34 +1021,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>linegym_@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>070-5250-6614</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,12 +1054,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,17 +1075,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1094,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,39 +1116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1189,13 +1173,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>689</v>
+        <v>1814</v>
       </c>
       <c r="Q8" t="n">
-        <v>728</v>
+        <v>1185</v>
       </c>
       <c r="R8" t="n">
-        <v>1417</v>
+        <v>2999</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1188,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,30 +1205,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>제이짐 휘트니스 4.19점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>herricane@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>070-4535-0883</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://blog.naver.com/herricane</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,12 +1242,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1476244634</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476244634</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,34 +1304,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>acrogym1@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acrogym1</t>
+          <t>http://pf.kakao.com/_QERxeG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1341,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,7 +1352,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1936</v>
+        <v>462</v>
       </c>
       <c r="Q10" t="n">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="R10" t="n">
-        <v>2764</v>
+        <v>1257</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1376,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,34 +1398,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,7 +1435,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>351</v>
+        <v>1086</v>
       </c>
       <c r="Q11" t="n">
-        <v>616</v>
+        <v>870</v>
       </c>
       <c r="R11" t="n">
-        <v>967</v>
+        <v>1956</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1470,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,34 +1492,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>419gym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>http://www.instagram.com/419gym_official</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1541,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1552,7 +1540,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>239</v>
+        <v>37</v>
       </c>
       <c r="Q12" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="R12" t="n">
-        <v>345</v>
+        <v>93</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1564,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1593,30 +1581,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gymchoi@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>070-5250-6614</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymchoi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,12 +1618,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,17 +1639,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1658,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1349373253</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349373253</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1688,29 +1680,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1745,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>321</v>
+        <v>822</v>
       </c>
       <c r="Q14" t="n">
-        <v>581</v>
+        <v>559</v>
       </c>
       <c r="R14" t="n">
-        <v>902</v>
+        <v>1381</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,12 +1752,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1782,29 +1774,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1839,13 +1831,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1086</v>
+        <v>2659</v>
       </c>
       <c r="Q15" t="n">
-        <v>867</v>
+        <v>4787</v>
       </c>
       <c r="R15" t="n">
-        <v>1953</v>
+        <v>7446</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,12 +1846,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1876,34 +1868,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>highend_fit@naver.com</t>
-        </is>
-      </c>
+          <t>NH FITNESS CLUB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1913,7 +1901,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1929,17 +1917,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1811</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1185</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2996</v>
+        <v>8</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,12 +1936,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1970,29 +1958,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>https://www.instagram.com/kdhonepick</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2007,7 +1995,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2018,7 +2006,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2027,13 +2015,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>226</v>
+        <v>116</v>
       </c>
       <c r="Q17" t="n">
-        <v>423</v>
+        <v>243</v>
       </c>
       <c r="R17" t="n">
-        <v>649</v>
+        <v>359</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2030,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2059,34 +2047,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2101,7 +2089,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2112,7 +2100,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2109,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>230</v>
+        <v>689</v>
       </c>
       <c r="Q18" t="n">
-        <v>584</v>
+        <v>728</v>
       </c>
       <c r="R18" t="n">
-        <v>814</v>
+        <v>1417</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,12 +2124,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2153,34 +2141,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>070-5250-1469</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2190,7 +2178,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2211,17 +2199,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,12 +2218,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1910693072</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910693072</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2252,29 +2240,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2284,12 +2272,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,17 +2293,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
       <c r="R20" t="n">
-        <v>44</v>
+        <v>392</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,12 +2312,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2346,29 +2334,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>419gym</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>419gym@naver.com</t>
-        </is>
-      </c>
+          <t>미아동주민자치위원회 헬스장</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1433-5131</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/419gym_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2378,7 +2358,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2399,17 +2379,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,12 +2398,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2440,7 +2420,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2451,18 +2431,18 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nyh314</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,7 +2457,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2493,17 +2473,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>334</v>
+        <v>1333</v>
       </c>
       <c r="Q22" t="n">
-        <v>365</v>
+        <v>885</v>
       </c>
       <c r="R22" t="n">
-        <v>699</v>
+        <v>2218</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,12 +2492,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2534,29 +2514,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>codelegend@naver.com</t>
-        </is>
-      </c>
+          <t>배용덕헬스</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pressgym___</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,7 +2542,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2587,17 +2563,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="R23" t="n">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,12 +2582,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2628,29 +2604,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>spoany87@naver.com</t>
-        </is>
-      </c>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany87</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2660,12 +2632,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2681,17 +2653,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1463</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="n">
-        <v>1726</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>3189</v>
+        <v>13</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,12 +2672,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2717,30 +2689,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1334-6825</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/uphoria_mia_1/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2750,7 +2726,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2766,22 +2742,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>584</v>
       </c>
       <c r="R25" t="n">
-        <v>14</v>
+        <v>814</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,12 +2766,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2812,29 +2788,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym-suyu</t>
+          <t>https://blog.naver.com/blueskirt0704</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2869,13 +2845,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="R26" t="n">
-        <v>47</v>
+        <v>653</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,12 +2860,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2906,29 +2882,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>herricane@naver.com</t>
-        </is>
-      </c>
+          <t>휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/herricane</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2938,12 +2910,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2963,13 +2935,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>198</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>404</v>
+        <v>3</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,12 +2950,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3000,34 +2972,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ZWKxjn</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3037,7 +3009,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3048,7 +3020,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3057,13 +3029,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>821</v>
+        <v>1936</v>
       </c>
       <c r="Q28" t="n">
-        <v>559</v>
+        <v>828</v>
       </c>
       <c r="R28" t="n">
-        <v>1380</v>
+        <v>2764</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,12 +3044,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3094,25 +3066,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1340-7281</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45suyu/</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3127,7 +3103,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3138,7 +3114,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3147,13 +3123,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>91</v>
+        <v>4548</v>
       </c>
       <c r="Q29" t="n">
-        <v>161</v>
+        <v>1204</v>
       </c>
       <c r="R29" t="n">
-        <v>252</v>
+        <v>5752</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,12 +3138,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3184,34 +3160,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>rkdqnr7184@naver.com</t>
-        </is>
-      </c>
+          <t>프리원핏 수유점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QERxeG</t>
+          <t>https://www.instagram.com/freewantfit_suyu/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3232,7 +3204,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3241,13 +3213,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>462</v>
+        <v>114</v>
       </c>
       <c r="Q30" t="n">
-        <v>795</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>1257</v>
+        <v>119</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,12 +3228,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3278,29 +3250,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3315,7 +3287,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3335,13 +3307,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2659</v>
+        <v>1620</v>
       </c>
       <c r="Q31" t="n">
-        <v>4787</v>
+        <v>1195</v>
       </c>
       <c r="R31" t="n">
-        <v>7446</v>
+        <v>2815</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,12 +3322,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3372,29 +3344,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3409,7 +3381,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3429,13 +3401,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="Q32" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>343</v>
+        <v>51</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,12 +3416,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3466,29 +3438,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>io15io15@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/h9a1n94</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3498,12 +3470,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3519,17 +3491,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>335</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>450</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,12 +3510,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3645,25 +3617,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>uptfitness@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>070-4535-8515</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3703,13 +3675,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,12 +3690,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3740,29 +3712,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>blueskirt0704@naver.com</t>
-        </is>
-      </c>
+          <t>제이핏 여성전용피티샵</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blueskirt0704</t>
+          <t>https://www.instagram.com/jjfit_7707</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3777,7 +3745,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3797,13 +3765,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="n">
-        <v>507</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>649</v>
+        <v>10</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,12 +3780,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3834,25 +3802,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>스포애니 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>spoany87@naver.com</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany87</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3862,12 +3834,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3883,17 +3855,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>1463</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>1725</v>
       </c>
       <c r="R37" t="n">
-        <v>11</v>
+        <v>3188</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,12 +3874,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3924,29 +3896,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>junggyo777@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team_whale_mia</t>
+          <t>https://blog.naver.com/spoany52</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3961,7 +3933,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3981,13 +3953,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>114</v>
+        <v>2747</v>
       </c>
       <c r="Q38" t="n">
-        <v>125</v>
+        <v>2340</v>
       </c>
       <c r="R38" t="n">
-        <v>239</v>
+        <v>5087</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,12 +3968,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4018,29 +3990,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>junggyo777@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfitshark_jangwi</t>
+          <t>https://www.instagram.com/team_whale_mia</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4075,10 +4047,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="Q39" t="n">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="R39" t="n">
         <v>239</v>
@@ -4090,12 +4062,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4112,29 +4084,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>https://blog.naver.com/baekyuri802</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4169,13 +4141,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>175</v>
+        <v>623</v>
       </c>
       <c r="Q40" t="n">
-        <v>130</v>
+        <v>339</v>
       </c>
       <c r="R40" t="n">
-        <v>305</v>
+        <v>962</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4184,12 +4156,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4201,25 +4173,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4259,13 +4231,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,12 +4246,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4291,30 +4263,34 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>97_cosat@naver.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4324,12 +4300,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4345,17 +4321,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="R42" t="n">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,12 +4340,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4386,29 +4362,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>baekyuri802@naver.com</t>
-        </is>
-      </c>
+          <t>가인헬스클럽</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baekyuri802</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4418,12 +4390,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4439,17 +4411,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>622</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>339</v>
+        <v>10</v>
       </c>
       <c r="R43" t="n">
-        <v>961</v>
+        <v>10</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,12 +4430,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4480,29 +4452,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ablegym33@naver.com</t>
-        </is>
-      </c>
+          <t>미아동헬스장</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1340-7281</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4512,12 +4476,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4533,17 +4497,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4547</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>1204</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>5751</v>
+        <v>7</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,12 +4516,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4569,34 +4533,34 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4606,12 +4570,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4622,22 +4586,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,12 +4610,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4668,34 +4632,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trend_hd4</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4705,7 +4669,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4716,7 +4680,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4725,13 +4689,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2264</v>
+        <v>321</v>
       </c>
       <c r="Q46" t="n">
-        <v>1432</v>
+        <v>581</v>
       </c>
       <c r="R46" t="n">
-        <v>3696</v>
+        <v>902</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,12 +4704,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4762,25 +4726,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjfit_7707</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4790,7 +4754,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4811,17 +4775,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,12 +4794,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4852,29 +4816,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h9a1n94</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4889,7 +4853,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4909,13 +4873,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>115</v>
+        <v>426</v>
       </c>
       <c r="Q48" t="n">
-        <v>335</v>
+        <v>221</v>
       </c>
       <c r="R48" t="n">
-        <v>450</v>
+        <v>647</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4924,12 +4888,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4946,34 +4910,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5003,13 +4967,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1620</v>
+        <v>1717</v>
       </c>
       <c r="Q49" t="n">
-        <v>1195</v>
+        <v>393</v>
       </c>
       <c r="R49" t="n">
-        <v>2815</v>
+        <v>2110</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5018,12 +4982,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5035,34 +4999,30 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>070-4535-3463</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/f45suyu/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5072,7 +5032,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5088,22 +5048,22 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5112,12 +5072,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5134,29 +5094,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifeplus_bd/</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5171,7 +5131,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5191,13 +5151,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>694</v>
+        <v>1289</v>
       </c>
       <c r="Q51" t="n">
-        <v>144</v>
+        <v>1949</v>
       </c>
       <c r="R51" t="n">
-        <v>838</v>
+        <v>3238</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5206,12 +5166,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5228,44 +5188,48 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5276,22 +5240,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>8</v>
+        <v>1141</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R52" t="n">
-        <v>8</v>
+        <v>1182</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5300,12 +5264,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5322,25 +5286,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ask4554@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ask4554</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5350,12 +5318,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5375,13 +5343,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="R53" t="n">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,12 +5358,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5412,29 +5380,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ask4554</t>
+          <t>https://blog.naver.com/trend_hd4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5465,17 +5433,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>2263</v>
       </c>
       <c r="Q54" t="n">
-        <v>202</v>
+        <v>1432</v>
       </c>
       <c r="R54" t="n">
-        <v>212</v>
+        <v>3695</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,12 +5452,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5501,34 +5469,34 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5538,12 +5506,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5559,17 +5527,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5578,12 +5546,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5600,34 +5568,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>bodyfit_@naver.com</t>
-        </is>
-      </c>
+          <t>커브스 수유클럽</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+          <t>https://cafe.naver.com/curves</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5657,13 +5621,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="Q56" t="n">
-        <v>320</v>
+        <v>7</v>
       </c>
       <c r="R56" t="n">
-        <v>423</v>
+        <v>50</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,12 +5636,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5694,29 +5658,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>bum903@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/axis_pt</t>
+          <t>https://blog.naver.com/bum903</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5742,7 +5706,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5751,13 +5715,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="Q57" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="R57" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,12 +5730,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5783,34 +5747,30 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>osbum0224@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5820,7 +5780,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5841,17 +5801,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,12 +5820,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5882,29 +5842,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>sd670@naver.com</t>
-        </is>
-      </c>
+          <t>프리원핏 미아점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sd670</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5919,7 +5875,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5939,13 +5895,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="Q59" t="n">
-        <v>235</v>
+        <v>94</v>
       </c>
       <c r="R59" t="n">
-        <v>322</v>
+        <v>169</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,12 +5910,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5976,29 +5932,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>drawgym@naver.com</t>
-        </is>
-      </c>
+          <t>엘투휘트니스 수유번동점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6008,12 +5960,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6029,17 +5981,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1289</v>
+        <v>10</v>
       </c>
       <c r="Q60" t="n">
-        <v>1949</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>3238</v>
+        <v>11</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,12 +6000,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6070,29 +6022,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietmode-</t>
+          <t>https://blog.naver.com/ssdaw1234</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6123,17 +6075,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="Q61" t="n">
-        <v>211</v>
+        <v>93</v>
       </c>
       <c r="R61" t="n">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6142,12 +6094,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6164,29 +6116,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6201,7 +6153,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6221,13 +6173,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2747</v>
+        <v>125</v>
       </c>
       <c r="Q62" t="n">
-        <v>2339</v>
+        <v>218</v>
       </c>
       <c r="R62" t="n">
-        <v>5086</v>
+        <v>343</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6236,12 +6188,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6253,30 +6205,34 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>에너메카 휘트니스 미아점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nyh314@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>https://blog.naver.com/nyh314</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6307,17 +6263,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="Q63" t="n">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="R63" t="n">
-        <v>184</v>
+        <v>699</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,12 +6282,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6348,29 +6304,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssdaw1234</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6396,7 +6352,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6405,13 +6361,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q64" t="n">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="R64" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,12 +6376,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6442,29 +6398,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/enermeca2/</t>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6499,13 +6455,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1332</v>
+        <v>694</v>
       </c>
       <c r="Q65" t="n">
-        <v>885</v>
+        <v>144</v>
       </c>
       <c r="R65" t="n">
-        <v>2217</v>
+        <v>838</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,12 +6470,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6531,34 +6487,34 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://www.instagram.com/crossfitshark_jangwi</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6573,7 +6529,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6593,13 +6549,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q66" t="n">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="R66" t="n">
-        <v>181</v>
+        <v>239</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,12 +6564,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6630,40 +6586,44 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>크로스핏FA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>fa_sport@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6674,22 +6634,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="R67" t="n">
-        <v>10</v>
+        <v>345</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,12 +6658,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6720,29 +6680,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6757,7 +6717,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6777,13 +6737,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1717</v>
+        <v>175</v>
       </c>
       <c r="Q68" t="n">
-        <v>391</v>
+        <v>130</v>
       </c>
       <c r="R68" t="n">
-        <v>2108</v>
+        <v>305</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,12 +6752,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6814,29 +6774,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gungympt</t>
+          <t>https://blog.naver.com/dietmode-</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6851,7 +6811,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6867,17 +6827,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>426</v>
+        <v>99</v>
       </c>
       <c r="Q69" t="n">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="R69" t="n">
-        <v>647</v>
+        <v>310</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,12 +6846,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6903,34 +6863,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/curves</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6965,13 +6925,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="R70" t="n">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6980,12 +6940,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7002,38 +6962,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>codelegend@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>https://www.instagram.com/pressgym___</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7043,7 +6999,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7054,7 +7010,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7063,13 +7019,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1139</v>
+        <v>234</v>
       </c>
       <c r="Q71" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R71" t="n">
-        <v>1180</v>
+        <v>279</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7078,12 +7034,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7100,18 +7056,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -7122,7 +7078,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://blog.naver.com/wellcare093</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7137,7 +7093,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7153,17 +7109,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="Q72" t="n">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="R72" t="n">
-        <v>298</v>
+        <v>61</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7172,12 +7128,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7194,29 +7150,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1437-5900</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunghyunle2</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7231,7 +7187,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7251,13 +7207,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="Q73" t="n">
-        <v>29</v>
+        <v>548</v>
       </c>
       <c r="R73" t="n">
-        <v>61</v>
+        <v>710</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7266,12 +7222,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7288,7 +7244,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7301,7 +7257,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7341,13 +7297,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>247</v>
       </c>
       <c r="Q74" t="n">
-        <v>19</v>
+        <v>1343</v>
       </c>
       <c r="R74" t="n">
-        <v>21</v>
+        <v>1590</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7356,12 +7312,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7378,39 +7334,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7435,13 +7391,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="Q75" t="n">
-        <v>165</v>
+        <v>375</v>
       </c>
       <c r="R75" t="n">
-        <v>244</v>
+        <v>521</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7450,12 +7406,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7472,29 +7428,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>life_building_@naver.com</t>
-        </is>
-      </c>
+          <t>디와이비퍼포먼스트레이닝</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1404-1363</t>
+          <t>0507-1436-2922</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>https://www.instagram.com/dyb_performance</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7529,13 +7481,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>532</v>
+        <v>57</v>
       </c>
       <c r="Q76" t="n">
-        <v>2236</v>
+        <v>59</v>
       </c>
       <c r="R76" t="n">
-        <v>2768</v>
+        <v>116</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7544,12 +7496,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7566,29 +7518,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1404-1363</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymseungeun/</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7623,13 +7575,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>29</v>
+        <v>532</v>
       </c>
       <c r="Q77" t="n">
-        <v>47</v>
+        <v>2236</v>
       </c>
       <c r="R77" t="n">
-        <v>76</v>
+        <v>2768</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7638,12 +7590,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7660,34 +7612,34 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://pf.kakao.com/_ExmdAX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7697,7 +7649,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7708,7 +7660,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7717,13 +7669,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="Q78" t="n">
-        <v>547</v>
+        <v>55</v>
       </c>
       <c r="R78" t="n">
-        <v>709</v>
+        <v>77</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7732,12 +7684,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7754,29 +7706,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>https://smartstore.naver.com/runandlift</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7791,7 +7743,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7811,13 +7763,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="Q79" t="n">
-        <v>375</v>
+        <v>501</v>
       </c>
       <c r="R79" t="n">
-        <v>521</v>
+        <v>694</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7826,12 +7778,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7848,29 +7800,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/runandlift</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7905,13 +7857,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="Q80" t="n">
-        <v>501</v>
+        <v>64</v>
       </c>
       <c r="R80" t="n">
-        <v>694</v>
+        <v>107</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7920,12 +7872,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7942,29 +7894,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7995,17 +7947,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="Q81" t="n">
-        <v>53</v>
+        <v>1300</v>
       </c>
       <c r="R81" t="n">
-        <v>61</v>
+        <v>1378</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8014,12 +7966,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8036,12 +7988,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -8049,12 +8001,12 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8064,12 +8016,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8089,13 +8041,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Q82" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="R82" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8104,12 +8056,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8126,29 +8078,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8163,7 +8115,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8183,13 +8135,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="Q83" t="n">
-        <v>1300</v>
+        <v>47</v>
       </c>
       <c r="R83" t="n">
-        <v>1378</v>
+        <v>76</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8198,12 +8150,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8220,34 +8172,34 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8257,7 +8209,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8268,22 +8220,22 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>637</v>
+        <v>89</v>
       </c>
       <c r="Q84" t="n">
-        <v>699</v>
+        <v>180</v>
       </c>
       <c r="R84" t="n">
-        <v>1336</v>
+        <v>269</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8292,12 +8244,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8314,29 +8266,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1436-2922</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_performance</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8371,13 +8323,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="Q85" t="n">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="R85" t="n">
-        <v>116</v>
+        <v>298</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8386,12 +8338,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8408,25 +8360,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1437-5900</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>https://www.instagram.com/sunghyunle2</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8441,7 +8397,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8461,13 +8417,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>247</v>
+        <v>32</v>
       </c>
       <c r="Q86" t="n">
-        <v>1343</v>
+        <v>29</v>
       </c>
       <c r="R86" t="n">
-        <v>1590</v>
+        <v>61</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8476,12 +8432,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8498,29 +8454,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1301-9491</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hypedobby</t>
+          <t>https://blog.naver.com/xtmxjax</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8535,7 +8491,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8551,17 +8507,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R87" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8570,12 +8526,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8592,29 +8548,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0507-1366-4502</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8645,17 +8597,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="n">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="R88" t="n">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8664,12 +8616,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8686,44 +8638,44 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>hyomin_nase@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1385-0454</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.dailypt</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8743,13 +8695,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="Q89" t="n">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="R89" t="n">
-        <v>107</v>
+        <v>244</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8758,12 +8710,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8780,29 +8732,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xtmxjax</t>
+          <t>https://www.instagram.com/hypedobby</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8817,7 +8769,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8833,17 +8785,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8852,12 +8804,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8874,30 +8826,34 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1485-1323</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestgym24/223778254580</t>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8907,7 +8863,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8918,22 +8874,22 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>21</v>
+        <v>637</v>
       </c>
       <c r="Q91" t="n">
-        <v>7</v>
+        <v>699</v>
       </c>
       <c r="R91" t="n">
-        <v>28</v>
+        <v>1336</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8942,12 +8898,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8964,39 +8920,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0507-1377-5126</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ExmdAX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9012,22 +8964,22 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="R92" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9036,12 +8988,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9061,11 +9013,7 @@
           <t>DL 운동센터</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>gunwigun_official@naver.com</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,30 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>플로리다휘트니스 삼양동점</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sd670@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-5250-1469</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sd670</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -613,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1910693072</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910693072</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -654,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>https://blog.naver.com/dietmode-</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -707,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>351</v>
+        <v>99</v>
       </c>
       <c r="Q3" t="n">
-        <v>616</v>
+        <v>211</v>
       </c>
       <c r="R3" t="n">
-        <v>967</v>
+        <v>310</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,42 +730,46 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>osbum0224@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>070-4535-3463</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -801,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -838,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sd670</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -870,20 +878,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43knh</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -895,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>87</v>
+        <v>4548</v>
       </c>
       <c r="Q5" t="n">
-        <v>235</v>
+        <v>1205</v>
       </c>
       <c r="R5" t="n">
-        <v>322</v>
+        <v>5753</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,61 +922,61 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -974,10 +986,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc0yw3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -989,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>86</v>
+        <v>1936</v>
       </c>
       <c r="Q6" t="n">
-        <v>91</v>
+        <v>828</v>
       </c>
       <c r="R6" t="n">
-        <v>177</v>
+        <v>2764</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1045,11 @@
           <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1104,7 +1124,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1116,39 +1136,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1164,7 +1184,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1173,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1814</v>
+        <v>226</v>
       </c>
       <c r="Q8" t="n">
-        <v>1185</v>
+        <v>423</v>
       </c>
       <c r="R8" t="n">
-        <v>2999</v>
+        <v>649</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1210,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/herricane</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,17 +1283,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>206</v>
+        <v>1289</v>
       </c>
       <c r="Q9" t="n">
-        <v>198</v>
+        <v>1949</v>
       </c>
       <c r="R9" t="n">
-        <v>404</v>
+        <v>3238</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1304,29 +1324,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QERxeG</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1341,7 +1365,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1361,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>462</v>
+        <v>1141</v>
       </c>
       <c r="Q10" t="n">
-        <v>795</v>
+        <v>41</v>
       </c>
       <c r="R10" t="n">
-        <v>1257</v>
+        <v>1182</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,17 +1400,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1398,29 +1422,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>https://blog.naver.com/nyh314</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,17 +1475,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1086</v>
+        <v>334</v>
       </c>
       <c r="Q11" t="n">
-        <v>870</v>
+        <v>365</v>
       </c>
       <c r="R11" t="n">
-        <v>1956</v>
+        <v>699</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1494,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1516,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>419gym@naver.com</t>
+          <t>uckyfycmko336@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/419gym_official</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1549,13 +1573,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="Q12" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="R12" t="n">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1588,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1610,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>가인헬스클럽</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1618,12 +1642,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1639,17 +1663,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>347</v>
+        <v>10</v>
       </c>
       <c r="R13" t="n">
-        <v>694</v>
+        <v>10</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,61 +1682,61 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ZWKxjn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1728,22 +1752,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1381</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1776,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1774,29 +1798,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1370-7849</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://www.instagram.com/f45suyu/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1811,7 +1831,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1822,7 +1842,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1831,13 +1851,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2659</v>
+        <v>91</v>
       </c>
       <c r="Q15" t="n">
-        <v>4787</v>
+        <v>161</v>
       </c>
       <c r="R15" t="n">
-        <v>7446</v>
+        <v>252</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1866,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1868,25 +1888,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ready4gymsuyu@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1896,12 +1920,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1917,17 +1941,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>1086</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="R16" t="n">
-        <v>8</v>
+        <v>1956</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,51 +1960,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>https://www.instagram.com/uphoria_mia_1/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2006,7 +2030,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2015,13 +2039,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="Q17" t="n">
-        <v>243</v>
+        <v>584</v>
       </c>
       <c r="R17" t="n">
-        <v>359</v>
+        <v>814</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2030,17 +2054,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2052,29 +2076,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2109,13 +2133,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>689</v>
+        <v>2659</v>
       </c>
       <c r="Q18" t="n">
-        <v>728</v>
+        <v>4787</v>
       </c>
       <c r="R18" t="n">
-        <v>1417</v>
+        <v>7446</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2148,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2146,44 +2170,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2203,13 +2227,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>103</v>
+        <v>1814</v>
       </c>
       <c r="Q19" t="n">
-        <v>320</v>
+        <v>1185</v>
       </c>
       <c r="R19" t="n">
-        <v>423</v>
+        <v>2999</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,51 +2242,55 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>myeonghui5402@gmail.com</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2277,7 +2305,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2297,13 +2325,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="Q20" t="n">
-        <v>297</v>
+        <v>91</v>
       </c>
       <c r="R20" t="n">
-        <v>392</v>
+        <v>177</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2340,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2334,21 +2362,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>419gym</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>419gym@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1433-5131</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/419gym_official</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2358,7 +2394,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2379,17 +2415,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="R21" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2434,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2420,29 +2456,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/enermeca2/</t>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,13 +2513,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1333</v>
+        <v>103</v>
       </c>
       <c r="Q22" t="n">
-        <v>885</v>
+        <v>320</v>
       </c>
       <c r="R22" t="n">
-        <v>2218</v>
+        <v>423</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2528,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2514,35 +2550,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rkdqnr7184@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_QERxeG</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2558,22 +2598,22 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>795</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>1257</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,17 +2622,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2604,25 +2644,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ask4554@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ask4554</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2632,12 +2676,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2657,13 +2701,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="R24" t="n">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2672,51 +2716,51 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2742,7 +2786,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2751,13 +2795,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>230</v>
+        <v>1333</v>
       </c>
       <c r="Q25" t="n">
-        <v>584</v>
+        <v>884</v>
       </c>
       <c r="R25" t="n">
-        <v>814</v>
+        <v>2217</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2766,17 +2810,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2788,29 +2832,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blueskirt0704</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2845,13 +2889,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="Q26" t="n">
-        <v>511</v>
+        <v>297</v>
       </c>
       <c r="R26" t="n">
-        <v>653</v>
+        <v>392</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2860,17 +2904,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2882,25 +2926,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>범휘트니스  수유점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bum903@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bum903</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2910,12 +2958,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2931,17 +2979,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2950,51 +2998,47 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>acrogym1@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acrogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3004,12 +3048,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3025,17 +3069,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1936</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>828</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2764</v>
+        <v>0</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3044,51 +3088,51 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3098,12 +3142,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3119,17 +3163,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4548</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1204</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5752</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3138,47 +3182,51 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3188,7 +3236,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3209,17 +3257,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3228,17 +3276,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3250,29 +3298,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3282,7 +3330,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3307,13 +3355,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1620</v>
+        <v>115</v>
       </c>
       <c r="Q31" t="n">
-        <v>1195</v>
+        <v>335</v>
       </c>
       <c r="R31" t="n">
-        <v>2815</v>
+        <v>450</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3322,17 +3370,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3344,29 +3392,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym-suyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3376,20 +3424,24 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40kte</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3401,13 +3453,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>51</v>
+        <v>2747</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2344</v>
       </c>
       <c r="R32" t="n">
-        <v>51</v>
+        <v>5091</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3416,17 +3468,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3438,29 +3490,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>h9a1n94@naver.com</t>
-        </is>
-      </c>
+          <t>휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h9a1n94</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3470,12 +3518,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3491,17 +3539,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>335</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>450</v>
+        <v>3</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3510,17 +3558,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3532,30 +3580,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1338-1501</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>https://blog.naver.com/blueskirt0704</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3585,13 +3637,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="Q34" t="n">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="R34" t="n">
-        <v>280</v>
+        <v>654</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3600,57 +3652,61 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>woojoogym@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3671,17 +3727,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3690,17 +3746,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3712,25 +3768,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>피트니스 베네핏 수유역점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>baekyuri802@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjfit_7707</t>
+          <t>https://blog.naver.com/baekyuri802</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3745,7 +3805,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3765,13 +3825,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>623</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="R36" t="n">
-        <v>10</v>
+        <v>962</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3780,17 +3840,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3802,29 +3862,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany87</t>
+          <t>http://blog.naver.com/herricane</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3855,17 +3915,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1463</v>
+        <v>206</v>
       </c>
       <c r="Q37" t="n">
-        <v>1725</v>
+        <v>198</v>
       </c>
       <c r="R37" t="n">
-        <v>3188</v>
+        <v>404</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3874,17 +3934,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3896,29 +3956,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>https://blog.naver.com/trend_hd4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3953,13 +4013,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2747</v>
+        <v>2263</v>
       </c>
       <c r="Q38" t="n">
-        <v>2340</v>
+        <v>1432</v>
       </c>
       <c r="R38" t="n">
-        <v>5087</v>
+        <v>3695</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3968,17 +4028,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3990,29 +4050,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>배용덕헬스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>junggyo777@naver.com</t>
+          <t>nicenet@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team_whale_mia</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4022,7 +4082,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4043,17 +4103,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="R39" t="n">
-        <v>239</v>
+        <v>13</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4062,17 +4122,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4084,29 +4144,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baekyuri802</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4116,20 +4176,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mfvy</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4141,13 +4205,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>623</v>
+        <v>1620</v>
       </c>
       <c r="Q40" t="n">
-        <v>339</v>
+        <v>1195</v>
       </c>
       <c r="R40" t="n">
-        <v>962</v>
+        <v>2815</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4156,17 +4220,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4178,25 +4242,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>woojoogym2@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4206,7 +4274,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4227,17 +4295,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="R41" t="n">
-        <v>54</v>
+        <v>343</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4246,17 +4314,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4418,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4362,25 +4430,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gymchoi@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymchoi</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4390,12 +4462,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4411,17 +4483,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="R43" t="n">
-        <v>10</v>
+        <v>694</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4430,17 +4502,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4452,16 +4524,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>더 퍼스트짐</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ssdaw1234@naver.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1353-7541</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4486,10 +4566,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47wce</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>X</t>
@@ -4497,17 +4581,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="R44" t="n">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4516,17 +4600,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4538,29 +4622,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4570,23 +4654,27 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4egpq</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4595,13 +4683,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="Q45" t="n">
-        <v>423</v>
+        <v>7</v>
       </c>
       <c r="R45" t="n">
-        <v>649</v>
+        <v>50</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4610,17 +4698,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4632,29 +4720,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1332-1672</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4669,7 +4753,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4680,7 +4764,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4689,13 +4773,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="Q46" t="n">
-        <v>581</v>
+        <v>193</v>
       </c>
       <c r="R46" t="n">
-        <v>902</v>
+        <v>280</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4704,17 +4788,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4726,20 +4810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>엘투휘트니스 수유번동점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4779,13 +4867,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4794,51 +4882,51 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gungympt</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4853,7 +4941,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4873,13 +4961,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>426</v>
+        <v>80</v>
       </c>
       <c r="Q48" t="n">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="R48" t="n">
-        <v>647</v>
+        <v>184</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4888,17 +4976,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4910,34 +4998,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4947,7 +5035,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4967,13 +5055,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1717</v>
+        <v>689</v>
       </c>
       <c r="Q49" t="n">
-        <v>393</v>
+        <v>728</v>
       </c>
       <c r="R49" t="n">
-        <v>2110</v>
+        <v>1417</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4982,17 +5070,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5004,25 +5092,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1393-8101</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45suyu/</t>
+          <t>https://www.instagram.com/kdhonepick</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5048,7 +5140,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5057,13 +5149,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="Q50" t="n">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="R50" t="n">
-        <v>252</v>
+        <v>359</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5072,17 +5164,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5094,34 +5186,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5131,7 +5223,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5142,7 +5234,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5151,13 +5243,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1289</v>
+        <v>321</v>
       </c>
       <c r="Q51" t="n">
-        <v>1949</v>
+        <v>581</v>
       </c>
       <c r="R51" t="n">
-        <v>3238</v>
+        <v>902</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5166,17 +5258,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5188,38 +5280,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5229,7 +5317,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5240,7 +5328,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5249,13 +5337,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1141</v>
+        <v>1717</v>
       </c>
       <c r="Q52" t="n">
-        <v>41</v>
+        <v>395</v>
       </c>
       <c r="R52" t="n">
-        <v>1182</v>
+        <v>2112</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5264,17 +5352,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5286,29 +5374,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ask4554</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5339,17 +5427,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="Q53" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>212</v>
+        <v>51</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5358,51 +5446,51 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trend_hd4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5412,12 +5500,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5433,17 +5521,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2263</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3695</v>
+        <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5452,51 +5540,51 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5506,7 +5594,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5527,17 +5615,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5546,17 +5634,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5568,30 +5656,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>노블휘트니스</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>noble_fitness@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/curves</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5601,7 +5693,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5621,13 +5713,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="R56" t="n">
-        <v>50</v>
+        <v>305</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5636,17 +5728,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5658,29 +5750,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>hanwnsdn@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1409-0851</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5690,12 +5778,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5711,17 +5799,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="R57" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5730,47 +5818,51 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>엑시스피티</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>axis_pt@naver.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>070-4535-0883</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5780,12 +5872,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5796,22 +5888,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5820,17 +5912,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1476244634</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476244634</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5842,25 +5934,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5870,7 +5962,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5891,17 +5983,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="Q59" t="n">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="R59" t="n">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5910,17 +6002,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5932,20 +6024,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>NH FITNESS CLUB</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jjoseohyun@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5985,13 +6081,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6000,17 +6096,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6022,29 +6118,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssdaw1234</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6054,20 +6150,24 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sak0</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>X</t>
@@ -6079,13 +6179,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>24</v>
+        <v>1464</v>
       </c>
       <c r="Q61" t="n">
-        <v>93</v>
+        <v>1725</v>
       </c>
       <c r="R61" t="n">
-        <v>117</v>
+        <v>3189</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6094,17 +6194,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6116,29 +6216,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>woojoogym2@naver.com</t>
-        </is>
-      </c>
+          <t>제이핏 여성전용피티샵</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6148,7 +6244,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6173,13 +6269,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="Q62" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>343</v>
+        <v>10</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6188,17 +6284,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6210,29 +6306,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nyh314</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6242,12 +6338,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6267,13 +6363,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>334</v>
+        <v>40</v>
       </c>
       <c r="Q63" t="n">
-        <v>365</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>699</v>
+        <v>44</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6282,17 +6378,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6304,34 +6400,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>fa_sport@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/axis_pt</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6361,13 +6457,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="Q64" t="n">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="R64" t="n">
-        <v>69</v>
+        <v>345</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6376,17 +6472,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6516,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifeplus_bd/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6430,7 +6526,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6440,10 +6536,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48ak4</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>X</t>
@@ -6480,7 +6580,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6492,29 +6592,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>hsyqz13@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfitshark_jangwi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6524,7 +6624,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6549,10 +6649,10 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="Q66" t="n">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="R66" t="n">
         <v>239</v>
@@ -6564,17 +6664,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6586,55 +6686,59 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9qn</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6643,13 +6747,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>239</v>
+        <v>114</v>
       </c>
       <c r="Q67" t="n">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="R67" t="n">
-        <v>345</v>
+        <v>119</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6658,17 +6762,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6680,29 +6784,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>uptfitness@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1421-2221</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6712,12 +6812,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6733,17 +6833,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="Q68" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>305</v>
+        <v>7</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6752,17 +6852,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6774,29 +6874,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietmode-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6806,20 +6906,24 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wqdd</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>X</t>
@@ -6827,17 +6931,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="Q69" t="n">
         <v>211</v>
       </c>
       <c r="R69" t="n">
-        <v>310</v>
+        <v>239</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6846,51 +6950,51 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6900,23 +7004,27 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wellmvw</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6925,13 +7033,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>80</v>
+        <v>823</v>
       </c>
       <c r="Q70" t="n">
-        <v>104</v>
+        <v>559</v>
       </c>
       <c r="R70" t="n">
-        <v>184</v>
+        <v>1382</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6940,17 +7048,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6967,7 +7075,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>codelegend@naver.com</t>
+          <t>pressgym@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -6984,7 +7092,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pressgym___</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6994,7 +7102,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7004,10 +7112,14 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8bi</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7044,7 +7156,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7056,29 +7168,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7109,17 +7221,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="Q72" t="n">
-        <v>53</v>
+        <v>548</v>
       </c>
       <c r="R72" t="n">
-        <v>61</v>
+        <v>710</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7128,17 +7240,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7150,29 +7262,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7203,17 +7315,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="Q73" t="n">
-        <v>548</v>
+        <v>180</v>
       </c>
       <c r="R73" t="n">
-        <v>710</v>
+        <v>269</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7222,17 +7334,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7244,25 +7356,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1385-0454</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7277,7 +7393,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7297,13 +7413,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="Q74" t="n">
-        <v>1343</v>
+        <v>64</v>
       </c>
       <c r="R74" t="n">
-        <v>1590</v>
+        <v>107</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7312,17 +7428,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7334,39 +7450,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>hyomin_nase@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7391,13 +7507,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="Q75" t="n">
-        <v>375</v>
+        <v>165</v>
       </c>
       <c r="R75" t="n">
-        <v>521</v>
+        <v>244</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7406,17 +7522,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7428,25 +7544,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>통증&amp;교정연구소</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>xtmxjax@naver.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1436-2922</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_performance</t>
+          <t>https://blog.naver.com/xtmxjax</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7461,7 +7581,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7477,17 +7597,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="Q76" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="R76" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7496,17 +7616,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7518,29 +7638,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0507-1404-1363</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7555,7 +7671,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7571,17 +7687,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>532</v>
+        <v>21</v>
       </c>
       <c r="Q77" t="n">
-        <v>2236</v>
+        <v>7</v>
       </c>
       <c r="R77" t="n">
-        <v>2768</v>
+        <v>28</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7590,17 +7706,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7810,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7706,29 +7822,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/runandlift</t>
+          <t>https://blog.naver.com/wellcare093</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7743,7 +7859,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7759,17 +7875,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="Q79" t="n">
-        <v>501</v>
+        <v>54</v>
       </c>
       <c r="R79" t="n">
-        <v>694</v>
+        <v>62</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7778,17 +7894,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7800,29 +7916,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1385-0454</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.dailypt</t>
+          <t>https://www.instagram.com/hypedobby</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7857,13 +7973,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q80" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7872,17 +7988,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7894,29 +8010,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://www.instagram.com/sunghyunle2</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7931,7 +8047,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7951,13 +8067,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="Q81" t="n">
-        <v>1300</v>
+        <v>29</v>
       </c>
       <c r="R81" t="n">
-        <v>1378</v>
+        <v>61</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7966,17 +8082,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7988,12 +8104,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -8001,12 +8117,12 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestgym24/223778254580</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8037,18 +8153,18 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>19</v>
+      </c>
+      <c r="R82" t="n">
         <v>21</v>
       </c>
-      <c r="Q82" t="n">
-        <v>7</v>
-      </c>
-      <c r="R82" t="n">
-        <v>28</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>X</t>
@@ -8056,17 +8172,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8078,29 +8194,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymseungeun/</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8115,7 +8231,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8135,13 +8251,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="Q83" t="n">
-        <v>47</v>
+        <v>375</v>
       </c>
       <c r="R83" t="n">
-        <v>76</v>
+        <v>521</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8150,17 +8266,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8172,29 +8288,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8209,7 +8325,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8225,17 +8341,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="Q84" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="R84" t="n">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8244,17 +8360,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8266,29 +8382,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0507-1368-4511</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8303,7 +8415,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8323,13 +8435,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="Q85" t="n">
-        <v>220</v>
+        <v>1343</v>
       </c>
       <c r="R85" t="n">
-        <v>298</v>
+        <v>1590</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8338,17 +8450,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8360,29 +8472,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1437-5900</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunghyunle2</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8397,7 +8509,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8417,13 +8529,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="Q86" t="n">
-        <v>29</v>
+        <v>1302</v>
       </c>
       <c r="R86" t="n">
-        <v>61</v>
+        <v>1380</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8432,17 +8544,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8454,34 +8566,34 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xtmxjax</t>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8491,7 +8603,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8502,22 +8614,22 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>33</v>
+        <v>637</v>
       </c>
       <c r="Q87" t="n">
-        <v>10</v>
+        <v>699</v>
       </c>
       <c r="R87" t="n">
-        <v>43</v>
+        <v>1336</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8526,17 +8638,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8548,25 +8660,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1404-1363</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8581,7 +8697,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8601,13 +8717,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>532</v>
       </c>
       <c r="Q88" t="n">
-        <v>19</v>
+        <v>2236</v>
       </c>
       <c r="R88" t="n">
-        <v>21</v>
+        <v>2768</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8616,17 +8732,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8638,34 +8754,34 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8675,15 +8791,19 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu8v0g9</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>X</t>
@@ -8695,13 +8815,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="Q89" t="n">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="R89" t="n">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8710,17 +8830,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8732,29 +8852,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0507-1301-9491</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hypedobby</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8764,7 +8880,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8785,17 +8901,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R90" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8804,17 +8920,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8826,39 +8942,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>디와이비퍼포먼스트레이닝</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1436-2922</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8874,7 +8990,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8883,13 +8999,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>637</v>
+        <v>57</v>
       </c>
       <c r="Q91" t="n">
-        <v>699</v>
+        <v>59</v>
       </c>
       <c r="R91" t="n">
-        <v>1336</v>
+        <v>116</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8898,17 +9014,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -8920,20 +9036,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1382-4849</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8958,10 +9078,14 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zmep</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr">
         <is>
           <t>X</t>
@@ -8969,17 +9093,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="Q92" t="n">
-        <v>41</v>
+        <v>501</v>
       </c>
       <c r="R92" t="n">
-        <v>42</v>
+        <v>694</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8988,17 +9112,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9137,11 @@
           <t>DL 운동센터</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>gunwigun_official@naver.com</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
@@ -9084,7 +9212,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sd670</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>235</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>322</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietmode-</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>99</v>
+        <v>1936</v>
       </c>
       <c r="Q3" t="n">
-        <v>211</v>
+        <v>828</v>
       </c>
       <c r="R3" t="n">
-        <v>310</v>
+        <v>2764</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43knh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4548</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>1205</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5753</v>
+        <v>11</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>acrogym1@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -986,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc0yw3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1005,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1936</v>
+        <v>426</v>
       </c>
       <c r="Q6" t="n">
-        <v>828</v>
+        <v>221</v>
       </c>
       <c r="R6" t="n">
-        <v>2764</v>
+        <v>647</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1037,29 +1029,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>070-5250-6614</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1084,10 +1076,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdf2zxw</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1099,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1349373253</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349373253</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1136,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>배용덕헬스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>nicenet@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1184,22 +1180,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>423</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>649</v>
+        <v>13</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>https://www.instagram.com/jjfit_7707</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1287,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1289</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>1949</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3238</v>
+        <v>10</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,59 +1320,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>drawgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ham5</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1385,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1141</v>
+        <v>1289</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>1949</v>
       </c>
       <c r="R10" t="n">
-        <v>1182</v>
+        <v>3238</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1422,29 +1418,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>nyh314@naver.com</t>
-        </is>
-      </c>
+          <t>가인헬스클럽</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nyh314</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,12 +1446,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1479,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>365</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>699</v>
+        <v>10</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1516,29 +1508,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uckyfycmko336@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1548,7 +1540,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1558,10 +1550,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43zk4</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1573,13 +1569,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="Q12" t="n">
-        <v>94</v>
+        <v>346</v>
       </c>
       <c r="R12" t="n">
-        <v>169</v>
+        <v>694</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1588,12 +1584,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1610,24 +1606,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1652,10 +1648,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40kte</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1663,17 +1663,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2747</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>2344</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>5091</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1699,49 +1699,49 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>fa_sport@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1752,22 +1752,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1798,25 +1798,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02-987-0111</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1826,7 +1830,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1842,22 +1846,22 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="Q15" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>252</v>
+        <v>44</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1866,12 +1870,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1888,34 +1892,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1930,13 +1938,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1945,13 +1957,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1086</v>
+        <v>1141</v>
       </c>
       <c r="Q16" t="n">
-        <v>870</v>
+        <v>41</v>
       </c>
       <c r="R16" t="n">
-        <v>1956</v>
+        <v>1182</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1960,12 +1972,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1977,34 +1989,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2030,7 +2042,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2039,13 +2051,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="Q17" t="n">
-        <v>584</v>
+        <v>218</v>
       </c>
       <c r="R17" t="n">
-        <v>814</v>
+        <v>343</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2054,12 +2066,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2076,29 +2088,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>uptfitness@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1370-7849</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2108,12 +2116,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2129,17 +2137,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2659</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4787</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>7446</v>
+        <v>7</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2148,12 +2156,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2170,34 +2178,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2207,7 +2215,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2227,13 +2235,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1814</v>
+        <v>175</v>
       </c>
       <c r="Q19" t="n">
-        <v>1185</v>
+        <v>130</v>
       </c>
       <c r="R19" t="n">
-        <v>2999</v>
+        <v>305</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2242,12 +2250,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2259,38 +2267,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>myeonghui5402@gmail.com</t>
-        </is>
-      </c>
+          <t>ablegym33@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2305,7 +2309,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2325,13 +2329,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>86</v>
+        <v>4548</v>
       </c>
       <c r="Q20" t="n">
-        <v>91</v>
+        <v>1205</v>
       </c>
       <c r="R20" t="n">
-        <v>177</v>
+        <v>5753</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2340,12 +2344,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2362,29 +2366,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>419gym@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/419gym_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2394,7 +2398,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2404,10 +2408,14 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4csg5</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>X</t>
@@ -2419,13 +2427,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>297</v>
       </c>
       <c r="R21" t="n">
-        <v>93</v>
+        <v>392</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2434,12 +2442,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2456,29 +2464,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2498,13 +2506,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yudn</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2513,13 +2525,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>103</v>
+        <v>462</v>
       </c>
       <c r="Q22" t="n">
-        <v>320</v>
+        <v>795</v>
       </c>
       <c r="R22" t="n">
-        <v>423</v>
+        <v>1257</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2528,12 +2540,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2550,39 +2562,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>hegardengym_suyu-@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QERxeG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2592,13 +2604,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49479</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2607,13 +2623,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>462</v>
+        <v>37</v>
       </c>
       <c r="Q23" t="n">
-        <v>795</v>
+        <v>56</v>
       </c>
       <c r="R23" t="n">
-        <v>1257</v>
+        <v>93</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2622,12 +2638,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2644,29 +2660,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ask4554</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2676,20 +2692,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfi5my</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>X</t>
@@ -2697,17 +2717,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>2263</v>
       </c>
       <c r="Q24" t="n">
-        <v>202</v>
+        <v>1432</v>
       </c>
       <c r="R24" t="n">
-        <v>212</v>
+        <v>3695</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2716,12 +2736,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2738,29 +2758,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/enermeca2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2770,7 +2790,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2780,10 +2800,14 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5j3</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2795,13 +2819,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1333</v>
+        <v>1717</v>
       </c>
       <c r="Q25" t="n">
-        <v>884</v>
+        <v>395</v>
       </c>
       <c r="R25" t="n">
-        <v>2217</v>
+        <v>2112</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2810,12 +2834,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2832,29 +2856,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>linegym_@naver.com</t>
-        </is>
-      </c>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2864,12 +2884,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2885,17 +2905,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="n">
-        <v>297</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
-        <v>392</v>
+        <v>13</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2904,12 +2924,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2926,29 +2946,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>https://www.instagram.com/freewantfit_suyu/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2963,7 +2983,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2983,13 +3003,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2998,12 +3018,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3015,30 +3035,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>제이짐 휘트니스 4.19점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>herricane@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>070-5250-1469</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://blog.naver.com/herricane</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3048,12 +3072,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3073,13 +3097,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3088,12 +3112,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1910693072</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910693072</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3113,11 +3137,7 @@
           <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>bizhows@naver.com</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
@@ -3199,29 +3219,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>somedayday00@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3246,10 +3266,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpw1lb4</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3261,13 +3285,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3276,12 +3300,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3298,24 +3322,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3340,10 +3364,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqzk</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3355,13 +3383,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="Q31" t="n">
-        <v>335</v>
+        <v>512</v>
       </c>
       <c r="R31" t="n">
-        <v>450</v>
+        <v>654</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3370,12 +3398,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3387,34 +3415,34 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3424,24 +3452,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40kte</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3453,13 +3477,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2747</v>
+        <v>24</v>
       </c>
       <c r="Q32" t="n">
-        <v>2344</v>
+        <v>157</v>
       </c>
       <c r="R32" t="n">
-        <v>5091</v>
+        <v>181</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3468,12 +3492,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3490,35 +3514,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>woojoogym@naver.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3539,17 +3567,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>616</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>967</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3558,12 +3586,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3580,29 +3608,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>NH FITNESS CLUB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blueskirt0704</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3612,12 +3640,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3633,17 +3661,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="Q34" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>654</v>
+        <v>8</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3652,12 +3680,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3674,29 +3702,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3722,7 +3750,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3731,13 +3759,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>351</v>
+        <v>823</v>
       </c>
       <c r="Q35" t="n">
-        <v>616</v>
+        <v>559</v>
       </c>
       <c r="R35" t="n">
-        <v>967</v>
+        <v>1382</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3746,12 +3774,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3768,29 +3796,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baekyuri802</t>
+          <t>https://blog.naver.com/spoany87</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3825,13 +3853,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>623</v>
+        <v>1464</v>
       </c>
       <c r="Q36" t="n">
-        <v>339</v>
+        <v>1725</v>
       </c>
       <c r="R36" t="n">
-        <v>962</v>
+        <v>3189</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3840,12 +3868,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3862,29 +3890,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>02-999-9905</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/herricane</t>
+          <t>https://www.instagram.com/f45suyu/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3899,7 +3923,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3910,22 +3934,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="Q37" t="n">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="R37" t="n">
-        <v>404</v>
+        <v>252</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3934,12 +3958,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3951,34 +3975,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>trend_hd4@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trend_hd4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3988,12 +4008,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4009,17 +4029,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2263</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3695</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4028,12 +4048,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4050,24 +4070,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nicenet@naver.com</t>
+          <t>ddt341@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4103,17 +4123,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R39" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4122,12 +4142,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4144,24 +4164,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4191,12 +4211,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mfvy</t>
+          <t>https://talk.naver.com/ct/wwrhsu4</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4205,13 +4225,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1620</v>
+        <v>25</v>
       </c>
       <c r="Q40" t="n">
-        <v>1195</v>
+        <v>44</v>
       </c>
       <c r="R40" t="n">
-        <v>2815</v>
+        <v>69</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4220,12 +4240,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4242,29 +4262,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4274,7 +4294,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4284,10 +4304,14 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rzh6</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4299,13 +4323,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>125</v>
+        <v>623</v>
       </c>
       <c r="Q41" t="n">
-        <v>218</v>
+        <v>339</v>
       </c>
       <c r="R41" t="n">
-        <v>343</v>
+        <v>962</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4314,12 +4338,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4331,34 +4355,34 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4368,12 +4392,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4389,17 +4413,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="Q42" t="n">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="R42" t="n">
-        <v>181</v>
+        <v>54</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4408,12 +4432,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4430,29 +4454,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4487,13 +4511,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>348</v>
+        <v>1085</v>
       </c>
       <c r="Q43" t="n">
-        <v>346</v>
+        <v>870</v>
       </c>
       <c r="R43" t="n">
-        <v>694</v>
+        <v>1955</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4502,12 +4526,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4519,34 +4543,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>myeonghui5402@gmail.com</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4556,7 +4584,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4566,14 +4594,10 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47wce</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>X</t>
@@ -4585,13 +4609,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="Q44" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R44" t="n">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4600,12 +4624,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4617,29 +4641,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4664,14 +4688,10 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egpq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4679,17 +4699,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4698,12 +4718,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4720,30 +4740,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1393-8101</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>https://www.instagram.com/kdhonepick</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4753,7 +4777,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4773,13 +4797,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="Q46" t="n">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="R46" t="n">
-        <v>280</v>
+        <v>359</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4788,12 +4812,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4810,29 +4834,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>uckyfycmko336@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4842,7 +4866,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4863,17 +4887,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="R47" t="n">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4882,12 +4906,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4899,44 +4923,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4961,13 +4985,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>80</v>
+        <v>1814</v>
       </c>
       <c r="Q48" t="n">
-        <v>104</v>
+        <v>1185</v>
       </c>
       <c r="R48" t="n">
-        <v>184</v>
+        <v>2999</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4976,12 +5000,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4993,34 +5017,30 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>gorillagym5@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>070-5250-6614</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5030,12 +5050,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5051,17 +5071,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1417</v>
+        <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5070,12 +5090,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5092,29 +5112,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>hanwnsdn@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1393-8101</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5124,7 +5140,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5145,17 +5161,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="Q50" t="n">
-        <v>243</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
-        <v>359</v>
+        <v>14</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5164,12 +5180,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5181,39 +5197,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>lifebuildingmia@naver.com</t>
-        </is>
-      </c>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5223,7 +5235,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5234,7 +5246,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5243,13 +5255,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="Q51" t="n">
-        <v>581</v>
+        <v>104</v>
       </c>
       <c r="R51" t="n">
-        <v>902</v>
+        <v>184</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5258,12 +5270,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5280,29 +5292,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5337,13 +5349,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1717</v>
+        <v>1333</v>
       </c>
       <c r="Q52" t="n">
-        <v>395</v>
+        <v>884</v>
       </c>
       <c r="R52" t="n">
-        <v>2112</v>
+        <v>2217</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5352,12 +5364,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5374,29 +5386,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym-suyu</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5431,13 +5443,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>51</v>
+        <v>2659</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4787</v>
       </c>
       <c r="R53" t="n">
-        <v>51</v>
+        <v>7446</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5446,12 +5458,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5463,49 +5475,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>070-4535-3463</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5521,17 +5529,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5540,12 +5548,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5562,29 +5570,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gungympt</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5619,13 +5627,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>426</v>
+        <v>1620</v>
       </c>
       <c r="Q55" t="n">
-        <v>221</v>
+        <v>1195</v>
       </c>
       <c r="R55" t="n">
-        <v>647</v>
+        <v>2815</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5634,12 +5642,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5656,34 +5664,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5693,7 +5701,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5704,7 +5712,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5713,13 +5721,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>175</v>
+        <v>321</v>
       </c>
       <c r="Q56" t="n">
-        <v>130</v>
+        <v>581</v>
       </c>
       <c r="R56" t="n">
-        <v>305</v>
+        <v>902</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5728,12 +5736,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5745,25 +5753,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>070-4535-0870</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5803,13 +5815,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5818,12 +5830,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5840,29 +5852,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/axis_pt</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5897,13 +5909,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="Q58" t="n">
-        <v>44</v>
+        <v>423</v>
       </c>
       <c r="R58" t="n">
-        <v>69</v>
+        <v>649</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5912,12 +5924,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5929,25 +5941,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5987,13 +5999,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6002,12 +6014,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6024,29 +6036,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6056,7 +6068,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6077,17 +6089,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>8</v>
+        <v>694</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="R60" t="n">
-        <v>8</v>
+        <v>838</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6096,12 +6108,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6118,29 +6130,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>junggyo777@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/team_whale_mia</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6150,7 +6162,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6160,14 +6172,10 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sak0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>X</t>
@@ -6179,13 +6187,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1464</v>
+        <v>114</v>
       </c>
       <c r="Q61" t="n">
-        <v>1725</v>
+        <v>125</v>
       </c>
       <c r="R61" t="n">
-        <v>3189</v>
+        <v>239</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6194,12 +6202,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6216,20 +6224,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>바디채널 광산사거리점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>bodyfit_@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6254,10 +6266,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sncb</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6269,13 +6285,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="R62" t="n">
-        <v>10</v>
+        <v>423</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6284,12 +6300,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6306,29 +6322,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6338,12 +6354,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6359,17 +6375,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>40</v>
+        <v>689</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>728</v>
       </c>
       <c r="R63" t="n">
-        <v>44</v>
+        <v>1417</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6378,12 +6394,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6400,34 +6416,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>https://cafe.naver.com/curves</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6448,7 +6464,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6457,13 +6473,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>239</v>
+        <v>43</v>
       </c>
       <c r="Q64" t="n">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>345</v>
+        <v>50</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6472,12 +6488,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6494,24 +6510,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6541,7 +6557,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48ak4</t>
+          <t>https://talk.naver.com/ct/w47wce</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6555,13 +6571,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>694</v>
+        <v>24</v>
       </c>
       <c r="Q65" t="n">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="R65" t="n">
-        <v>838</v>
+        <v>117</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6570,12 +6586,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6587,29 +6603,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hsyqz13@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6634,13 +6650,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405s2</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6649,13 +6669,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>114</v>
+        <v>230</v>
       </c>
       <c r="Q66" t="n">
-        <v>125</v>
+        <v>584</v>
       </c>
       <c r="R66" t="n">
-        <v>239</v>
+        <v>814</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6664,12 +6684,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6686,24 +6706,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>pressgym@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6733,7 +6753,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f9qn</t>
+          <t>https://talk.naver.com/ct/w5i8bi</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6747,13 +6767,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="R67" t="n">
-        <v>119</v>
+        <v>279</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6762,12 +6782,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6784,20 +6804,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1417-9917</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6822,10 +6846,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jggy</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6833,17 +6861,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="R68" t="n">
-        <v>7</v>
+        <v>322</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6852,12 +6880,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6896,7 +6924,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/crossfitshark_jangwi</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6906,7 +6934,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6916,14 +6944,10 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wqdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>X</t>
@@ -6972,29 +6996,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ask4554</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7004,42 +7028,38 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wellmvw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>823</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
-        <v>559</v>
+        <v>202</v>
       </c>
       <c r="R70" t="n">
-        <v>1382</v>
+        <v>212</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7048,12 +7068,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7070,29 +7090,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>pressgym@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/h9a1n94</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7102,24 +7122,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5i8bi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7131,13 +7147,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>234</v>
+        <v>115</v>
       </c>
       <c r="Q71" t="n">
-        <v>45</v>
+        <v>335</v>
       </c>
       <c r="R71" t="n">
-        <v>279</v>
+        <v>450</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7146,12 +7162,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7168,29 +7184,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7200,23 +7216,27 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4utrl</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7225,13 +7245,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>162</v>
+        <v>637</v>
       </c>
       <c r="Q72" t="n">
-        <v>548</v>
+        <v>699</v>
       </c>
       <c r="R72" t="n">
-        <v>710</v>
+        <v>1336</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7240,12 +7260,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7262,29 +7282,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7294,20 +7314,24 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxl9x94</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
@@ -7315,17 +7339,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="Q73" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>269</v>
+        <v>40</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7334,12 +7358,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7356,29 +7380,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1385-0454</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.dailypt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7388,7 +7408,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7398,10 +7418,14 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9vb</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7413,13 +7437,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="Q74" t="n">
-        <v>64</v>
+        <v>1343</v>
       </c>
       <c r="R74" t="n">
-        <v>107</v>
+        <v>1590</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7428,12 +7452,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7450,34 +7474,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7487,7 +7511,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7503,17 +7527,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="Q75" t="n">
-        <v>165</v>
+        <v>10</v>
       </c>
       <c r="R75" t="n">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7522,12 +7546,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7544,29 +7568,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xtmxjax</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7576,20 +7600,24 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zcrh</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7597,17 +7625,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="R76" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7616,12 +7644,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7656,7 +7684,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestgym24/223778254580</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7666,12 +7694,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7728,39 +7756,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>디와이비퍼포먼스트레이닝</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1436-2922</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ExmdAX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7776,7 +7804,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7785,13 +7813,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="Q78" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="R78" t="n">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7800,12 +7828,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7822,29 +7850,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1404-1390</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7854,12 +7878,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7879,13 +7903,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="R79" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7894,12 +7918,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7916,29 +7940,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1301-9491</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hypedobby</t>
+          <t>https://smartstore.naver.com/runandlift</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7973,13 +7997,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="R80" t="n">
-        <v>40</v>
+        <v>694</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7988,12 +8012,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8010,44 +8034,44 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>hyomin_nase@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1437-5900</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunghyunle2</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8067,13 +8091,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="Q81" t="n">
-        <v>29</v>
+        <v>165</v>
       </c>
       <c r="R81" t="n">
-        <v>61</v>
+        <v>244</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8082,12 +8106,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8104,25 +8128,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1366-4502</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8153,17 +8181,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="Q82" t="n">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="R82" t="n">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8172,12 +8200,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8194,34 +8222,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>https://pf.kakao.com/_ExmdAX</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8231,7 +8259,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8242,7 +8270,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8251,13 +8279,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="Q83" t="n">
-        <v>375</v>
+        <v>55</v>
       </c>
       <c r="R83" t="n">
-        <v>521</v>
+        <v>77</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8266,12 +8294,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8288,18 +8316,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -8310,7 +8338,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://blog.naver.com/wellcare093</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8325,7 +8353,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8341,17 +8369,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="Q84" t="n">
-        <v>220</v>
+        <v>54</v>
       </c>
       <c r="R84" t="n">
-        <v>298</v>
+        <v>62</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8360,12 +8388,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8382,25 +8410,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1467-8213</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8435,13 +8467,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>247</v>
+        <v>162</v>
       </c>
       <c r="Q85" t="n">
-        <v>1343</v>
+        <v>548</v>
       </c>
       <c r="R85" t="n">
-        <v>1590</v>
+        <v>710</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8450,12 +8482,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8472,29 +8504,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8509,7 +8541,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8529,13 +8561,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="Q86" t="n">
-        <v>1302</v>
+        <v>47</v>
       </c>
       <c r="R86" t="n">
-        <v>1380</v>
+        <v>76</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8544,12 +8576,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8566,34 +8598,34 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8603,7 +8635,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8614,7 +8646,7 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -8623,13 +8655,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>637</v>
+        <v>146</v>
       </c>
       <c r="Q87" t="n">
-        <v>699</v>
+        <v>375</v>
       </c>
       <c r="R87" t="n">
-        <v>1336</v>
+        <v>521</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8638,12 +8670,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8754,24 +8786,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8801,7 +8833,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wu8v0g9</t>
+          <t>https://talk.naver.com/ct/w45d9r</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8815,13 +8847,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="Q89" t="n">
-        <v>47</v>
+        <v>1302</v>
       </c>
       <c r="R89" t="n">
-        <v>76</v>
+        <v>1380</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8830,12 +8862,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8852,12 +8884,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -8865,12 +8897,12 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8880,12 +8912,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8901,17 +8933,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="R90" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8920,12 +8952,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8942,29 +8974,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1436-2922</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8974,7 +9006,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8999,13 +9031,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="Q91" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="R91" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9014,12 +9046,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9036,29 +9068,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9068,7 +9100,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9078,14 +9110,10 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zmep</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>X</t>
@@ -9097,13 +9125,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="Q92" t="n">
-        <v>501</v>
+        <v>220</v>
       </c>
       <c r="R92" t="n">
-        <v>694</v>
+        <v>298</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9112,12 +9140,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>io15io15@naver.com</t>
+          <t>codelegend@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/pressgym___</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>279</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>acrogym1@naver.com</t>
-        </is>
-      </c>
+          <t>프리원핏 수유점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acrogym1</t>
+          <t>https://www.instagram.com/freewantfit_suyu/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1936</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="n">
-        <v>828</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>2764</v>
+        <v>119</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym-suyu</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>51</v>
+        <v>175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="R4" t="n">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,29 +837,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>lhj0709_@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +932,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>gungympt@naver.com</t>
-        </is>
-      </c>
+          <t>NH FITNESS CLUB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gungympt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +960,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,17 +981,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>426</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>647</v>
+        <v>8</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1000,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1022,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>dietmode-@naver.com</t>
-        </is>
-      </c>
+          <t>프리원핏 미아점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1076,14 +1060,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdf2zxw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,17 +1071,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="Q7" t="n">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="R7" t="n">
-        <v>310</v>
+        <v>169</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1090,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,24 +1112,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>nicenet@naver.com</t>
-        </is>
-      </c>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1189,10 +1165,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
         <v>13</v>
@@ -1204,12 +1180,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1197,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>lhj0709_@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjfit_7707</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,7 +1230,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1279,17 +1251,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1292,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,27 +1324,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ham5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1381,13 +1349,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1289</v>
+        <v>226</v>
       </c>
       <c r="Q10" t="n">
-        <v>1949</v>
+        <v>423</v>
       </c>
       <c r="R10" t="n">
-        <v>3238</v>
+        <v>649</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1364,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,25 +1386,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>피트니스 베네핏 수유역점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>baekyuri802@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/baekyuri802</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1446,12 +1418,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,17 +1439,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>339</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>962</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1458,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1508,29 +1480,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>gymchoi@naver.com</t>
-        </is>
-      </c>
+          <t>제이핏 여성전용피티샵</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jjfit_7707</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1540,7 +1508,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1550,14 +1518,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43zk4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1569,13 +1533,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>348</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>694</v>
+        <v>10</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,12 +1548,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1606,24 +1570,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>spoany52@naver.com</t>
-        </is>
-      </c>
+          <t>가인헬스클럽</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1648,14 +1608,10 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40kte</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1663,17 +1619,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2747</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2344</v>
+        <v>10</v>
       </c>
       <c r="R13" t="n">
-        <v>5091</v>
+        <v>10</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1682,12 +1638,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1704,34 +1660,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>https://blog.naver.com/blueskirt0704</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1752,7 +1708,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1761,13 +1717,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>239</v>
+        <v>142</v>
       </c>
       <c r="Q14" t="n">
-        <v>106</v>
+        <v>514</v>
       </c>
       <c r="R14" t="n">
-        <v>345</v>
+        <v>656</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1776,12 +1732,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1798,29 +1754,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>건짐 수유역점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1830,7 +1786,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1851,17 +1807,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>40</v>
+        <v>426</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>221</v>
       </c>
       <c r="R15" t="n">
-        <v>44</v>
+        <v>647</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1870,12 +1826,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1892,33 +1848,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>wefit100@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1933,19 +1885,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>O</t>
@@ -1957,13 +1905,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1141</v>
+        <v>823</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>559</v>
       </c>
       <c r="R16" t="n">
-        <v>1182</v>
+        <v>1382</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1972,12 +1920,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1994,29 +1942,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>junggyo777@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>https://www.instagram.com/team_whale_mia</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2051,13 +1999,13 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q17" t="n">
         <v>125</v>
       </c>
-      <c r="Q17" t="n">
-        <v>218</v>
-      </c>
       <c r="R17" t="n">
-        <v>343</v>
+        <v>239</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2066,12 +2014,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2088,30 +2036,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1417-2362</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2121,7 +2073,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2137,17 +2089,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>1814</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1185</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>2999</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2156,12 +2108,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2178,39 +2130,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2226,7 +2178,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2235,13 +2187,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>175</v>
+        <v>321</v>
       </c>
       <c r="Q19" t="n">
-        <v>130</v>
+        <v>581</v>
       </c>
       <c r="R19" t="n">
-        <v>305</v>
+        <v>902</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2250,12 +2202,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2272,29 +2224,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>https://blog.naver.com/ssdaw1234</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2329,13 +2281,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4548</v>
+        <v>24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1205</v>
+        <v>93</v>
       </c>
       <c r="R20" t="n">
-        <v>5753</v>
+        <v>117</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2344,12 +2296,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2366,56 +2318,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1418-7007</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4csg5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>X</t>
@@ -2427,13 +2371,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="Q21" t="n">
-        <v>297</v>
+        <v>193</v>
       </c>
       <c r="R21" t="n">
-        <v>392</v>
+        <v>280</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2442,12 +2386,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2464,29 +2408,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2496,27 +2440,23 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yudn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2525,13 +2465,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>462</v>
+        <v>689</v>
       </c>
       <c r="Q22" t="n">
-        <v>795</v>
+        <v>728</v>
       </c>
       <c r="R22" t="n">
-        <v>1257</v>
+        <v>1417</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2540,12 +2480,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2557,34 +2497,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hegardengym_suyu-@naver.com</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>myeonghui5402@gmail.com</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2594,7 +2538,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2604,14 +2548,10 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49479</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2623,13 +2563,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="Q23" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="R23" t="n">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2638,12 +2578,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2660,24 +2600,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2702,14 +2642,10 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfi5my</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>X</t>
@@ -2717,17 +2653,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2263</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1432</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>3695</v>
+        <v>3</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2736,12 +2672,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2758,29 +2694,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/trend_hd4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2790,24 +2726,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r5j3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2819,13 +2751,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1717</v>
+        <v>2263</v>
       </c>
       <c r="Q25" t="n">
-        <v>395</v>
+        <v>1434</v>
       </c>
       <c r="R25" t="n">
-        <v>2112</v>
+        <v>3697</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2834,12 +2766,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2851,30 +2783,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>osbum0224@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2884,12 +2820,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2905,17 +2841,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2924,12 +2860,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2946,29 +2882,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit_suyu/</t>
+          <t>https://cafe.naver.com/curves</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2983,7 +2919,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3003,13 +2939,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3018,12 +2954,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3040,29 +2976,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>419gym@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/herricane</t>
+          <t>http://www.instagram.com/419gym_official</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3077,7 +3013,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3093,17 +3029,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="Q28" t="n">
-        <v>198</v>
+        <v>56</v>
       </c>
       <c r="R28" t="n">
-        <v>404</v>
+        <v>93</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3112,12 +3048,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3129,45 +3065,53 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>짐박스피트니스 미아사거리역점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>070-4535-0883</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3178,22 +3122,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1141</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1182</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3202,12 +3146,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1476244634</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476244634</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3224,29 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>somedayday00@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3256,24 +3200,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpw1lb4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3281,17 +3221,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>334</v>
+        <v>1936</v>
       </c>
       <c r="Q30" t="n">
-        <v>365</v>
+        <v>828</v>
       </c>
       <c r="R30" t="n">
-        <v>699</v>
+        <v>2764</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3300,12 +3240,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3322,29 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3354,7 +3294,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3364,14 +3304,10 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqzk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3383,13 +3319,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>142</v>
+        <v>1717</v>
       </c>
       <c r="Q31" t="n">
-        <v>512</v>
+        <v>398</v>
       </c>
       <c r="R31" t="n">
-        <v>654</v>
+        <v>2115</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3398,12 +3334,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3415,34 +3351,34 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3477,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="Q32" t="n">
-        <v>157</v>
+        <v>297</v>
       </c>
       <c r="R32" t="n">
-        <v>181</v>
+        <v>392</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3492,12 +3428,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3514,34 +3450,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3551,7 +3487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3571,13 +3507,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>351</v>
+        <v>1289</v>
       </c>
       <c r="Q33" t="n">
-        <v>616</v>
+        <v>1950</v>
       </c>
       <c r="R33" t="n">
-        <v>967</v>
+        <v>3239</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3586,12 +3522,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3608,29 +3544,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymchoi</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3640,12 +3576,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3661,17 +3597,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>8</v>
+        <v>348</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="R34" t="n">
-        <v>8</v>
+        <v>694</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3680,12 +3616,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3702,34 +3638,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ZWKxjn</t>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3750,7 +3686,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3759,13 +3695,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>823</v>
+        <v>103</v>
       </c>
       <c r="Q35" t="n">
-        <v>559</v>
+        <v>320</v>
       </c>
       <c r="R35" t="n">
-        <v>1382</v>
+        <v>423</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3774,12 +3710,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3796,29 +3732,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany87</t>
+          <t>https://blog.naver.com/nyh314</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3849,17 +3785,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1464</v>
+        <v>334</v>
       </c>
       <c r="Q36" t="n">
-        <v>1725</v>
+        <v>365</v>
       </c>
       <c r="R36" t="n">
-        <v>3189</v>
+        <v>699</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3868,12 +3804,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3890,25 +3826,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1369-2202</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3918,7 +3858,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3934,22 +3874,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>252</v>
+        <v>11</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3958,12 +3898,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3975,30 +3915,34 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>woojoogym2@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>070-4535-3463</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4008,7 +3952,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4029,17 +3973,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4048,12 +3992,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4070,29 +4014,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ddt341@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4102,7 +4046,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4127,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>37</v>
+        <v>1620</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>1195</v>
       </c>
       <c r="R39" t="n">
-        <v>57</v>
+        <v>2815</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4142,12 +4086,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4164,29 +4108,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4196,27 +4140,23 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwrhsu4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4225,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>25</v>
+        <v>4548</v>
       </c>
       <c r="Q40" t="n">
-        <v>44</v>
+        <v>1205</v>
       </c>
       <c r="R40" t="n">
-        <v>69</v>
+        <v>5753</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4240,12 +4180,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4262,29 +4202,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sd670</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4294,24 +4234,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rzh6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4323,13 +4259,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>623</v>
+        <v>87</v>
       </c>
       <c r="Q41" t="n">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c r="R41" t="n">
-        <v>962</v>
+        <v>322</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4338,12 +4274,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4360,29 +4296,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany52</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4392,12 +4328,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4413,17 +4349,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>38</v>
+        <v>2747</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>2344</v>
       </c>
       <c r="R42" t="n">
-        <v>54</v>
+        <v>5091</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4432,12 +4368,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4454,29 +4390,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>배용덕헬스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>nicenet@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4486,12 +4422,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4507,17 +4443,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1085</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>870</v>
+        <v>13</v>
       </c>
       <c r="R43" t="n">
-        <v>1955</v>
+        <v>13</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4526,12 +4462,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4543,38 +4479,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>myeonghui5402@gmail.com</t>
-        </is>
-      </c>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4584,7 +4516,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4605,17 +4537,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4624,12 +4556,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4641,34 +4573,34 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4678,7 +4610,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4699,17 +4631,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>838</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4718,12 +4650,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4740,29 +4672,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1393-8101</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>https://www.instagram.com/f45suyu/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4788,7 +4716,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4797,13 +4725,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="Q46" t="n">
-        <v>243</v>
+        <v>161</v>
       </c>
       <c r="R46" t="n">
-        <v>359</v>
+        <v>252</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4812,12 +4740,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4834,34 +4762,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>uckyfycmko336@naver.com</t>
+          <t>fa_sport@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4871,7 +4799,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4882,7 +4810,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4891,13 +4819,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="Q47" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="R47" t="n">
-        <v>169</v>
+        <v>345</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4906,12 +4834,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4928,39 +4856,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4976,7 +4904,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4985,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1814</v>
+        <v>25</v>
       </c>
       <c r="Q48" t="n">
-        <v>1185</v>
+        <v>45</v>
       </c>
       <c r="R48" t="n">
-        <v>2999</v>
+        <v>70</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5000,12 +4928,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5017,30 +4945,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>크로스핏샤크</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>fatdogxp@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>070-5250-6614</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/crossfitshark_jangwi</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5050,7 +4982,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5071,17 +5003,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5090,12 +5022,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1349373253</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349373253</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5107,30 +5039,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1334-6825</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/uphoria_mia_1/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5140,7 +5076,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5156,22 +5092,22 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>584</v>
       </c>
       <c r="R50" t="n">
-        <v>14</v>
+        <v>814</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5180,12 +5116,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5197,30 +5133,30 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>미아동헬스장</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>uptfitness@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>02-986-2534</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5230,12 +5166,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5251,17 +5187,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="Q51" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5270,12 +5206,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5386,29 +5322,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://blog.naver.com/spoany87</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5443,13 +5379,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2659</v>
+        <v>1464</v>
       </c>
       <c r="Q53" t="n">
-        <v>4787</v>
+        <v>1727</v>
       </c>
       <c r="R53" t="n">
-        <v>7446</v>
+        <v>3191</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5458,12 +5394,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5480,30 +5416,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1357-9092</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5533,13 +5473,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="Q54" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>280</v>
+        <v>51</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5548,12 +5488,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5570,29 +5510,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5602,7 +5542,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5623,17 +5563,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1620</v>
+        <v>38</v>
       </c>
       <c r="Q55" t="n">
-        <v>1195</v>
+        <v>16</v>
       </c>
       <c r="R55" t="n">
-        <v>2815</v>
+        <v>54</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5642,12 +5582,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5659,44 +5599,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5712,22 +5652,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>581</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>902</v>
+        <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5736,12 +5676,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5753,29 +5693,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>hanwnsdn@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>070-4535-0870</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5815,13 +5751,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5830,12 +5766,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5852,29 +5788,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>https://blog.naver.com/h9a1n94</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5900,7 +5836,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5909,13 +5845,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="Q58" t="n">
-        <v>423</v>
+        <v>335</v>
       </c>
       <c r="R58" t="n">
-        <v>649</v>
+        <v>450</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5924,12 +5860,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5941,40 +5877,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>woojoogym@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>070-5250-1469</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5995,17 +5935,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6014,12 +5954,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1910693072</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910693072</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6036,29 +5976,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>bum903@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifeplus_bd/</t>
+          <t>https://blog.naver.com/bum903</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6073,7 +6013,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6093,13 +6033,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>694</v>
+        <v>37</v>
       </c>
       <c r="Q60" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="R60" t="n">
-        <v>838</v>
+        <v>57</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6108,12 +6048,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6125,34 +6065,34 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>junggyo777@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>070-5250-6614</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team_whale_mia</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6162,7 +6102,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6183,17 +6123,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6202,12 +6142,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6224,29 +6164,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6256,24 +6196,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sncb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6285,13 +6221,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>103</v>
+        <v>1085</v>
       </c>
       <c r="Q62" t="n">
-        <v>320</v>
+        <v>871</v>
       </c>
       <c r="R62" t="n">
-        <v>423</v>
+        <v>1956</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6300,12 +6236,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6322,29 +6258,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6354,12 +6290,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6375,17 +6311,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>689</v>
+        <v>40</v>
       </c>
       <c r="Q63" t="n">
-        <v>728</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>1417</v>
+        <v>44</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6394,12 +6330,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6416,29 +6352,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/curves</t>
+          <t>https://blog.naver.com/dietmode-</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6469,17 +6405,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="R64" t="n">
-        <v>50</v>
+        <v>310</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6488,12 +6424,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6510,29 +6446,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kdhonepick</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6542,7 +6478,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6552,14 +6488,10 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47wce</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>X</t>
@@ -6571,13 +6503,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="Q65" t="n">
-        <v>93</v>
+        <v>243</v>
       </c>
       <c r="R65" t="n">
-        <v>117</v>
+        <v>359</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6586,12 +6518,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6603,44 +6535,44 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_QERxeG</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6650,14 +6582,10 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w405s2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>O</t>
@@ -6669,13 +6597,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>230</v>
+        <v>462</v>
       </c>
       <c r="Q66" t="n">
-        <v>584</v>
+        <v>795</v>
       </c>
       <c r="R66" t="n">
-        <v>814</v>
+        <v>1257</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6684,12 +6612,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6701,29 +6629,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>pressgym@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6748,14 +6676,10 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5i8bi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6763,17 +6687,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6782,12 +6706,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6804,29 +6728,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6836,24 +6760,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jggy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6865,13 +6785,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>87</v>
+        <v>2659</v>
       </c>
       <c r="Q68" t="n">
-        <v>235</v>
+        <v>4787</v>
       </c>
       <c r="R68" t="n">
-        <v>322</v>
+        <v>7446</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6880,12 +6800,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6897,34 +6817,34 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfitshark_jangwi</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6939,7 +6859,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6959,13 +6879,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="n">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="R69" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6974,12 +6894,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7090,29 +7010,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h9a1n94</t>
+          <t>http://blog.naver.com/herricane</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7143,17 +7063,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="Q71" t="n">
-        <v>335</v>
+        <v>198</v>
       </c>
       <c r="R71" t="n">
-        <v>450</v>
+        <v>404</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7162,12 +7082,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7184,29 +7104,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7216,27 +7136,23 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4utrl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7245,13 +7161,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>637</v>
+        <v>162</v>
       </c>
       <c r="Q72" t="n">
-        <v>699</v>
+        <v>548</v>
       </c>
       <c r="R72" t="n">
-        <v>1336</v>
+        <v>710</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7260,12 +7176,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7282,29 +7198,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1301-9491</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wellcare093</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7314,24 +7230,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxl9x94</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
@@ -7339,17 +7251,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R73" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7358,12 +7270,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7380,25 +7292,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1318-2087</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/xtmxjax</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7408,24 +7324,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u9vb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7433,17 +7345,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>247</v>
+        <v>33</v>
       </c>
       <c r="Q74" t="n">
-        <v>1343</v>
+        <v>10</v>
       </c>
       <c r="R74" t="n">
-        <v>1590</v>
+        <v>43</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7452,12 +7364,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7474,29 +7386,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hypedobby</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7506,7 +7418,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7527,17 +7439,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7546,12 +7458,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7568,29 +7480,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1437-5900</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7600,24 +7508,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zcrh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7629,13 +7533,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Q76" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="R76" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7644,12 +7548,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7666,25 +7570,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>forestgym24@naver.com</t>
-        </is>
-      </c>
+          <t>디와이비퍼포먼스트레이닝</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1436-2922</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dyb_performance</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7694,7 +7598,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7715,17 +7619,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="R77" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7734,12 +7638,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7756,29 +7660,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1436-2922</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7788,7 +7692,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7813,13 +7717,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="Q78" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="R78" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7828,12 +7732,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7850,25 +7754,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1362-0934</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7878,12 +7786,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7899,17 +7807,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="Q79" t="n">
-        <v>41</v>
+        <v>1303</v>
       </c>
       <c r="R79" t="n">
-        <v>42</v>
+        <v>1381</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7918,12 +7826,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7940,29 +7848,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/runandlift</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7997,13 +7905,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="Q80" t="n">
-        <v>501</v>
+        <v>47</v>
       </c>
       <c r="R80" t="n">
-        <v>694</v>
+        <v>76</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8012,12 +7920,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8034,39 +7942,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8091,13 +7999,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="Q81" t="n">
-        <v>165</v>
+        <v>375</v>
       </c>
       <c r="R81" t="n">
-        <v>244</v>
+        <v>521</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8106,12 +8014,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8128,34 +8036,34 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8165,7 +8073,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8176,22 +8084,22 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>89</v>
+        <v>637</v>
       </c>
       <c r="Q82" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="R82" t="n">
-        <v>269</v>
+        <v>1337</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8200,12 +8108,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8222,34 +8130,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ExmdAX</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8270,7 +8178,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8279,13 +8187,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="Q83" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="R83" t="n">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8294,12 +8202,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8316,29 +8224,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>https://www.instagram.com/sunghyunle2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8353,7 +8261,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8369,17 +8277,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q84" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="R84" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8388,12 +8296,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8410,29 +8318,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1404-1363</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8447,7 +8355,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8467,13 +8375,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>162</v>
+        <v>532</v>
       </c>
       <c r="Q85" t="n">
-        <v>548</v>
+        <v>2236</v>
       </c>
       <c r="R85" t="n">
-        <v>710</v>
+        <v>2768</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8482,12 +8390,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8504,29 +8412,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymseungeun/</t>
+          <t>https://smartstore.naver.com/runandlift</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8561,13 +8469,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>29</v>
+        <v>193</v>
       </c>
       <c r="Q86" t="n">
-        <v>47</v>
+        <v>501</v>
       </c>
       <c r="R86" t="n">
-        <v>76</v>
+        <v>694</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8576,12 +8484,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8598,29 +8506,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8651,17 +8559,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="Q87" t="n">
-        <v>375</v>
+        <v>180</v>
       </c>
       <c r="R87" t="n">
-        <v>521</v>
+        <v>269</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8670,12 +8578,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8692,44 +8600,44 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>hyomin_nase@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1404-1363</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8749,13 +8657,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>532</v>
+        <v>79</v>
       </c>
       <c r="Q88" t="n">
-        <v>2236</v>
+        <v>165</v>
       </c>
       <c r="R88" t="n">
-        <v>2768</v>
+        <v>244</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8764,12 +8672,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8786,39 +8694,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_ExmdAX</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8828,17 +8736,13 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45d9r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8847,13 +8751,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="Q89" t="n">
-        <v>1302</v>
+        <v>55</v>
       </c>
       <c r="R89" t="n">
-        <v>1380</v>
+        <v>77</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8862,12 +8766,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8884,12 +8788,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -8897,12 +8801,12 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8912,12 +8816,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8933,17 +8837,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="R90" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8952,12 +8856,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8974,29 +8878,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0507-1385-0454</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.dailypt</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9011,7 +8911,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9031,13 +8931,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="Q91" t="n">
-        <v>64</v>
+        <v>1343</v>
       </c>
       <c r="R91" t="n">
-        <v>107</v>
+        <v>1590</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9046,12 +8946,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9068,29 +8968,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0507-1368-4511</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9105,7 +9001,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9121,17 +9017,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="Q92" t="n">
-        <v>220</v>
+        <v>7</v>
       </c>
       <c r="R92" t="n">
-        <v>298</v>
+        <v>28</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9140,12 +9036,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>codelegend@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pressgym___</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>플로리다휘트니스 삼양동점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sd670@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -696,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jggy</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>235</v>
       </c>
       <c r="R3" t="n">
-        <v>119</v>
+        <v>322</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>junggyo777@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>https://www.instagram.com/team_whale_mia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -785,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="Q4" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="R4" t="n">
-        <v>305</v>
+        <v>239</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -837,25 +845,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>에이블짐 수유점</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ablegym33@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -880,10 +892,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43knh</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -891,17 +907,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4549</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1205</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>5754</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -932,30 +948,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>highend_fit@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -965,15 +985,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v4ny</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -981,17 +1005,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>1814</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>2999</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1022,30 +1046,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>M스피닝 강사 교육</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>m_spinning@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1380-1962</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1055,15 +1079,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc215t</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1075,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="Q7" t="n">
-        <v>94</v>
+        <v>193</v>
       </c>
       <c r="R7" t="n">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1090,12 +1118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1112,20 +1140,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>F45 수유</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>f45_suyu@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1306-3451</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1150,28 +1178,32 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy43x6v</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="R8" t="n">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1180,12 +1212,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1197,25 +1229,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>배용덕헬스</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>nicenet@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>070-4535-0883</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1258,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1270,12 +1306,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1476244634</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476244634</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1292,29 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1324,23 +1360,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqzk</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1349,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>226</v>
+        <v>142</v>
       </c>
       <c r="Q10" t="n">
-        <v>423</v>
+        <v>518</v>
       </c>
       <c r="R10" t="n">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1364,12 +1404,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1386,29 +1426,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baekyuri802</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1418,12 +1458,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1439,17 +1479,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>623</v>
+        <v>38</v>
       </c>
       <c r="Q11" t="n">
-        <v>339</v>
+        <v>16</v>
       </c>
       <c r="R11" t="n">
-        <v>962</v>
+        <v>54</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1458,12 +1498,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1475,30 +1515,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>97_cosat@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjfit_7707</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1508,7 +1552,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1518,10 +1562,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa2rxwt</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1533,13 +1581,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1548,12 +1596,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1570,20 +1618,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>커브스 수유클럽</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>haon8312@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1608,10 +1660,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4egpq</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1619,17 +1675,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1638,12 +1694,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1660,34 +1716,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blueskirt0704</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1697,7 +1753,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1708,7 +1764,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1717,13 +1773,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>142</v>
+        <v>321</v>
       </c>
       <c r="Q14" t="n">
-        <v>514</v>
+        <v>581</v>
       </c>
       <c r="R14" t="n">
-        <v>656</v>
+        <v>902</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1732,12 +1788,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1754,29 +1810,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>건짐 수유역점</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gungympt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1786,7 +1842,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1796,13 +1852,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41vr7</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1811,13 +1871,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="Q15" t="n">
-        <v>221</v>
+        <v>423</v>
       </c>
       <c r="R15" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1826,12 +1886,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1848,29 +1908,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ZWKxjn</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1885,7 +1949,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1905,13 +1969,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>823</v>
+        <v>1145</v>
       </c>
       <c r="Q16" t="n">
-        <v>559</v>
+        <v>41</v>
       </c>
       <c r="R16" t="n">
-        <v>1382</v>
+        <v>1186</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1920,12 +1984,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1942,29 +2006,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>junggyo777@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team_whale_mia</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1974,7 +2038,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1995,17 +2059,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="R17" t="n">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2014,12 +2078,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2036,39 +2100,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2093,13 +2157,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1814</v>
+        <v>51</v>
       </c>
       <c r="Q18" t="n">
-        <v>1185</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2999</v>
+        <v>51</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2108,12 +2172,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2130,39 +2194,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2172,13 +2236,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sncb</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2187,13 +2255,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>321</v>
+        <v>103</v>
       </c>
       <c r="Q19" t="n">
-        <v>581</v>
+        <v>320</v>
       </c>
       <c r="R19" t="n">
-        <v>902</v>
+        <v>423</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2202,12 +2270,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2224,29 +2292,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>uckyfycmko336@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssdaw1234</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2261,7 +2329,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2281,13 +2349,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="Q20" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R20" t="n">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2296,12 +2364,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2318,40 +2386,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>ddt341@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1409-0851</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2371,13 +2443,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="Q21" t="n">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
-        <v>280</v>
+        <v>57</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2386,12 +2458,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2408,29 +2480,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2440,12 +2512,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2465,13 +2537,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>689</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1417</v>
+        <v>10</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2480,12 +2552,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2497,38 +2569,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>myeonghui5402@gmail.com</t>
-        </is>
-      </c>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2538,7 +2606,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2559,17 +2627,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2578,12 +2646,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2600,39 +2668,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>io15io15@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2653,17 +2721,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1718</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>398</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>2116</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2672,12 +2740,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2694,29 +2762,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trend_hd4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2726,20 +2794,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40kte</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2751,13 +2823,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2263</v>
+        <v>2749</v>
       </c>
       <c r="Q25" t="n">
-        <v>1434</v>
+        <v>2345</v>
       </c>
       <c r="R25" t="n">
-        <v>3697</v>
+        <v>5094</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2766,12 +2838,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2783,34 +2855,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2820,20 +2892,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rzh6</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2845,13 +2921,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>80</v>
+        <v>623</v>
       </c>
       <c r="Q26" t="n">
-        <v>104</v>
+        <v>339</v>
       </c>
       <c r="R26" t="n">
-        <v>184</v>
+        <v>962</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2860,12 +2936,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2882,29 +2958,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/curves</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2914,23 +2990,27 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwrhsu4</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2939,13 +3019,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="R27" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2954,12 +3034,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2976,29 +3056,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>419gym@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/419gym_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3008,7 +3088,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3018,10 +3098,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w481k9</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3029,17 +3113,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>37</v>
+        <v>206</v>
       </c>
       <c r="Q28" t="n">
-        <v>56</v>
+        <v>198</v>
       </c>
       <c r="R28" t="n">
-        <v>93</v>
+        <v>404</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3048,12 +3132,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3070,59 +3154,59 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>dwgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e814</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3131,13 +3215,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1141</v>
+        <v>2659</v>
       </c>
       <c r="Q29" t="n">
-        <v>41</v>
+        <v>4787</v>
       </c>
       <c r="R29" t="n">
-        <v>1182</v>
+        <v>7446</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,12 +3230,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3163,34 +3247,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>acrogym1@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acrogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3200,23 +3284,27 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405s2</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3225,13 +3313,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1936</v>
+        <v>230</v>
       </c>
       <c r="Q30" t="n">
-        <v>828</v>
+        <v>584</v>
       </c>
       <c r="R30" t="n">
-        <v>2764</v>
+        <v>814</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,12 +3328,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3262,29 +3350,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>pressgym@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3294,7 +3382,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3304,10 +3392,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8bi</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3319,13 +3411,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1717</v>
+        <v>236</v>
       </c>
       <c r="Q31" t="n">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="R31" t="n">
-        <v>2115</v>
+        <v>281</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3334,12 +3426,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3356,29 +3448,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>더블플러스휘트니스클럽</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3388,12 +3480,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3409,17 +3501,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="Q32" t="n">
-        <v>297</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>392</v>
+        <v>13</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,12 +3520,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3450,29 +3542,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3482,20 +3574,24 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43zk4</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>X</t>
@@ -3507,13 +3603,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1289</v>
+        <v>348</v>
       </c>
       <c r="Q33" t="n">
-        <v>1950</v>
+        <v>346</v>
       </c>
       <c r="R33" t="n">
-        <v>3239</v>
+        <v>694</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,12 +3618,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3544,29 +3640,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3576,12 +3672,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3597,17 +3693,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>346</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>694</v>
+        <v>3</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,12 +3712,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3638,29 +3734,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3670,7 +3766,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3680,10 +3776,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy486uk</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3695,13 +3795,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>103</v>
+        <v>689</v>
       </c>
       <c r="Q35" t="n">
-        <v>320</v>
+        <v>728</v>
       </c>
       <c r="R35" t="n">
-        <v>423</v>
+        <v>1417</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,12 +3810,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3732,29 +3832,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nyh314</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3769,7 +3869,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3785,17 +3885,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>334</v>
+        <v>125</v>
       </c>
       <c r="Q36" t="n">
-        <v>365</v>
+        <v>219</v>
       </c>
       <c r="R36" t="n">
-        <v>699</v>
+        <v>344</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,12 +3904,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3826,29 +3926,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ssdaw1234</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3858,12 +3958,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3879,17 +3979,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="R37" t="n">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,12 +3998,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3920,29 +4020,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>hegardengym_suyu-@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1433-5131</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3952,7 +4052,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3962,10 +4062,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49479</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -3977,13 +4081,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="Q38" t="n">
-        <v>218</v>
+        <v>56</v>
       </c>
       <c r="R38" t="n">
-        <v>343</v>
+        <v>93</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,12 +4096,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4014,34 +4118,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>fa_sport@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4051,7 +4155,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4062,7 +4166,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4071,13 +4175,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1620</v>
+        <v>239</v>
       </c>
       <c r="Q39" t="n">
-        <v>1195</v>
+        <v>106</v>
       </c>
       <c r="R39" t="n">
-        <v>2815</v>
+        <v>345</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,12 +4190,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4108,29 +4212,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4140,23 +4244,27 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yudn</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4165,13 +4273,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4548</v>
+        <v>462</v>
       </c>
       <c r="Q40" t="n">
-        <v>1205</v>
+        <v>795</v>
       </c>
       <c r="R40" t="n">
-        <v>5753</v>
+        <v>1257</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,12 +4288,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4202,29 +4310,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>uptfitness@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1417-9917</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sd670</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4234,12 +4338,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4255,17 +4359,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>322</v>
+        <v>7</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,12 +4378,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4296,29 +4400,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4328,20 +4432,24 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfi5my</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>X</t>
@@ -4353,13 +4461,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2747</v>
+        <v>2264</v>
       </c>
       <c r="Q42" t="n">
-        <v>2344</v>
+        <v>1435</v>
       </c>
       <c r="R42" t="n">
-        <v>5091</v>
+        <v>3699</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,12 +4476,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4390,24 +4498,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nicenet@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4432,28 +4540,32 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wellmvw</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>559</v>
       </c>
       <c r="R43" t="n">
-        <v>13</v>
+        <v>1382</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,12 +4574,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4479,7 +4591,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4495,7 +4607,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070-5250-1469</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4556,12 +4668,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1910693072</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910693072</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4578,29 +4690,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifeplus_bd/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4610,7 +4722,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4620,10 +4732,14 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdf2zxw</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4631,17 +4747,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>694</v>
+        <v>99</v>
       </c>
       <c r="Q45" t="n">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="R45" t="n">
-        <v>838</v>
+        <v>310</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,12 +4766,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4672,25 +4788,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1369-2202</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4700,7 +4820,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4716,22 +4836,22 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="Q46" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>252</v>
+        <v>11</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,12 +4860,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4762,34 +4882,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4810,7 +4930,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4819,13 +4939,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>239</v>
+        <v>1085</v>
       </c>
       <c r="Q47" t="n">
-        <v>106</v>
+        <v>874</v>
       </c>
       <c r="R47" t="n">
-        <v>345</v>
+        <v>1959</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,12 +4954,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4856,29 +4976,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/axis_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4888,23 +5008,27 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mfvy</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4913,13 +5037,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>25</v>
+        <v>1620</v>
       </c>
       <c r="Q48" t="n">
-        <v>45</v>
+        <v>1196</v>
       </c>
       <c r="R48" t="n">
-        <v>70</v>
+        <v>2816</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,12 +5052,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4950,29 +5074,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfitshark_jangwi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4982,7 +5106,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5007,13 +5131,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="Q49" t="n">
-        <v>210</v>
+        <v>335</v>
       </c>
       <c r="R49" t="n">
-        <v>238</v>
+        <v>450</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,12 +5146,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5039,34 +5163,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5076,7 +5200,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5086,13 +5210,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wqdd</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5101,13 +5229,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>230</v>
+        <v>28</v>
       </c>
       <c r="Q50" t="n">
-        <v>584</v>
+        <v>211</v>
       </c>
       <c r="R50" t="n">
-        <v>814</v>
+        <v>239</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,12 +5244,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5138,25 +5266,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1418-7007</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5166,12 +5298,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5187,17 +5319,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>297</v>
       </c>
       <c r="R51" t="n">
-        <v>7</v>
+        <v>392</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5206,12 +5338,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5228,29 +5360,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/enermeca2/</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5265,7 +5397,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5285,13 +5417,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1333</v>
+        <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>884</v>
+        <v>130</v>
       </c>
       <c r="R52" t="n">
-        <v>2217</v>
+        <v>305</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5300,12 +5432,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5322,29 +5454,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany87</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5354,20 +5486,24 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48ak4</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5379,13 +5515,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1464</v>
+        <v>694</v>
       </c>
       <c r="Q53" t="n">
-        <v>1727</v>
+        <v>145</v>
       </c>
       <c r="R53" t="n">
-        <v>3191</v>
+        <v>839</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,12 +5530,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5416,29 +5552,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>NH FITNESS CLUB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym-suyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5448,12 +5584,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5469,17 +5605,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,12 +5624,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5510,24 +5646,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>가인헬스클럽</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5567,13 +5703,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R55" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,12 +5718,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5599,34 +5735,34 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kdhonepick</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5636,7 +5772,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5657,17 +5793,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,12 +5812,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5693,25 +5829,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>hanwnsdn@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>070-5250-6614</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5751,13 +5891,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,12 +5906,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5783,34 +5923,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>thebarunpt@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h9a1n94</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5830,10 +5970,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7sz75u</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
@@ -5845,13 +5989,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="Q58" t="n">
-        <v>335</v>
+        <v>104</v>
       </c>
       <c r="R58" t="n">
-        <v>450</v>
+        <v>184</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,12 +6004,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5877,44 +6021,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5935,17 +6079,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>967</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,12 +6098,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5976,29 +6120,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6033,13 +6177,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>37</v>
+        <v>1289</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>1951</v>
       </c>
       <c r="R60" t="n">
-        <v>57</v>
+        <v>3240</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,12 +6192,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6065,29 +6209,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>somedayday00@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>070-5250-6614</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6112,10 +6256,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpw1lb4</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>X</t>
@@ -6127,13 +6275,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6142,12 +6290,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1349373253</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349373253</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6164,29 +6312,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>la-lune@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1430-3344</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6196,12 +6340,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6217,17 +6361,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1085</v>
+        <v>7</v>
       </c>
       <c r="Q62" t="n">
-        <v>871</v>
+        <v>7</v>
       </c>
       <c r="R62" t="n">
-        <v>1956</v>
+        <v>14</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6236,12 +6380,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6258,24 +6402,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6300,10 +6444,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcha8q</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6311,17 +6459,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>40</v>
+        <v>1334</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>884</v>
       </c>
       <c r="R63" t="n">
-        <v>44</v>
+        <v>2218</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6330,12 +6478,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6352,34 +6500,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietmode-</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6389,7 +6537,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6405,17 +6553,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>99</v>
+        <v>351</v>
       </c>
       <c r="Q64" t="n">
-        <v>211</v>
+        <v>616</v>
       </c>
       <c r="R64" t="n">
-        <v>310</v>
+        <v>967</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6424,12 +6572,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6441,34 +6589,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6478,7 +6626,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6499,17 +6647,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6518,12 +6666,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6535,44 +6683,44 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>honeymusclegym@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QERxeG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6582,13 +6730,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t1ci</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6597,13 +6749,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>462</v>
+        <v>86</v>
       </c>
       <c r="Q66" t="n">
-        <v>795</v>
+        <v>91</v>
       </c>
       <c r="R66" t="n">
-        <v>1257</v>
+        <v>177</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6612,12 +6764,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6629,29 +6781,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>070-4535-3463</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6676,10 +6828,14 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9qn</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6687,17 +6843,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6706,12 +6862,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6728,29 +6884,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6760,20 +6916,24 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sak0</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6785,13 +6945,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2659</v>
+        <v>1464</v>
       </c>
       <c r="Q68" t="n">
-        <v>4787</v>
+        <v>1729</v>
       </c>
       <c r="R68" t="n">
-        <v>7446</v>
+        <v>3193</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6800,12 +6960,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6817,34 +6977,34 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6879,13 +7039,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>24</v>
+        <v>1936</v>
       </c>
       <c r="Q69" t="n">
-        <v>157</v>
+        <v>828</v>
       </c>
       <c r="R69" t="n">
-        <v>181</v>
+        <v>2764</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6894,12 +7054,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6916,29 +7076,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>헬스&amp;PT 건짐 수유역점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ask4554</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6948,20 +7108,24 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we2yppk</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>X</t>
@@ -6969,17 +7133,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>10</v>
+        <v>426</v>
       </c>
       <c r="Q70" t="n">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="R70" t="n">
-        <v>212</v>
+        <v>647</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6988,12 +7152,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7010,29 +7174,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/herricane</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7042,12 +7206,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7067,13 +7231,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="Q71" t="n">
-        <v>198</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>404</v>
+        <v>44</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7082,12 +7246,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7104,34 +7268,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7141,7 +7305,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7152,7 +7316,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7161,13 +7325,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>162</v>
+        <v>637</v>
       </c>
       <c r="Q72" t="n">
-        <v>548</v>
+        <v>700</v>
       </c>
       <c r="R72" t="n">
-        <v>710</v>
+        <v>1337</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,12 +7340,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7198,39 +7362,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>winnnig@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7240,10 +7404,14 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lqb7</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
@@ -7251,17 +7419,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="Q73" t="n">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="R73" t="n">
-        <v>62</v>
+        <v>244</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7270,12 +7438,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7292,29 +7460,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xtmxjax</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7324,20 +7492,24 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdgwqtj</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7345,17 +7517,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>550</v>
       </c>
       <c r="R74" t="n">
-        <v>43</v>
+        <v>712</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7364,12 +7536,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7386,29 +7558,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1301-9491</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hypedobby</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7418,7 +7590,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7428,10 +7600,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7t3tx8</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7443,13 +7619,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R75" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7458,12 +7634,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7480,25 +7656,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1458-1884</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7508,20 +7688,24 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu8v0g9</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7533,13 +7717,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="Q76" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="R76" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7548,12 +7732,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7570,25 +7754,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>라이프빌딩PT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>life_building_@naver.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1436-2922</t>
+          <t>0507-1404-1363</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_performance</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7598,7 +7786,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7623,13 +7811,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>57</v>
+        <v>532</v>
       </c>
       <c r="Q77" t="n">
-        <v>59</v>
+        <v>2236</v>
       </c>
       <c r="R77" t="n">
-        <v>116</v>
+        <v>2768</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7638,12 +7826,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7660,29 +7848,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1385-0454</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.dailypt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7692,7 +7876,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7713,17 +7897,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="R78" t="n">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7732,12 +7916,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7754,29 +7938,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7786,20 +7970,24 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zcrh</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -7811,13 +7999,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="Q79" t="n">
-        <v>1303</v>
+        <v>29</v>
       </c>
       <c r="R79" t="n">
-        <v>1381</v>
+        <v>61</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7826,12 +8014,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7848,29 +8036,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymseungeun/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7880,7 +8068,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7890,10 +8078,14 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zmep</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr">
         <is>
           <t>X</t>
@@ -7905,13 +8097,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>29</v>
+        <v>193</v>
       </c>
       <c r="Q80" t="n">
-        <v>47</v>
+        <v>501</v>
       </c>
       <c r="R80" t="n">
-        <v>76</v>
+        <v>694</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7920,12 +8112,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7942,29 +8134,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7999,13 +8191,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="Q81" t="n">
-        <v>375</v>
+        <v>1303</v>
       </c>
       <c r="R81" t="n">
-        <v>521</v>
+        <v>1381</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8014,12 +8206,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8036,39 +8228,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8084,22 +8276,22 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>637</v>
+        <v>33</v>
       </c>
       <c r="Q82" t="n">
-        <v>700</v>
+        <v>10</v>
       </c>
       <c r="R82" t="n">
-        <v>1337</v>
+        <v>43</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8108,12 +8300,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8224,29 +8416,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>디와이비퍼포먼스트레이닝</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1437-5900</t>
+          <t>0507-1436-2922</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunghyunle2</t>
+          <t>https://www.instagram.com/dyb_performance</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8281,13 +8473,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="Q84" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="R84" t="n">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8296,12 +8488,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8318,29 +8510,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0507-1404-1363</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8350,7 +8538,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8360,10 +8548,14 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jtey</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr">
         <is>
           <t>X</t>
@@ -8375,13 +8567,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>532</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="n">
-        <v>2236</v>
+        <v>19</v>
       </c>
       <c r="R85" t="n">
-        <v>2768</v>
+        <v>21</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8390,12 +8582,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8412,29 +8604,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/runandlift</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8444,7 +8636,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8460,7 +8652,7 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8469,13 +8661,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="Q86" t="n">
-        <v>501</v>
+        <v>55</v>
       </c>
       <c r="R86" t="n">
-        <v>694</v>
+        <v>77</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8484,12 +8676,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8506,29 +8698,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8538,20 +8730,24 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxl9x94</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr">
         <is>
           <t>X</t>
@@ -8559,17 +8755,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="Q87" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>269</v>
+        <v>41</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8578,12 +8774,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8600,39 +8796,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>https://blog.naver.com/wellcare093</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8653,17 +8849,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="Q88" t="n">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="R88" t="n">
-        <v>244</v>
+        <v>62</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8672,12 +8868,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8694,39 +8890,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0507-1377-5126</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ExmdAX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8742,22 +8934,22 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="R89" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8766,12 +8958,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8788,20 +8980,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1309-1030</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8826,10 +9022,14 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnugfn3</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
@@ -8837,17 +9037,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="Q90" t="n">
-        <v>41</v>
+        <v>375</v>
       </c>
       <c r="R90" t="n">
-        <v>42</v>
+        <v>521</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8856,12 +9056,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8931,13 +9131,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q91" t="n">
         <v>1343</v>
       </c>
       <c r="R91" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8968,25 +9168,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1366-4502</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestgym24/223778254580</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9021,13 +9225,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="Q92" t="n">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="R92" t="n">
-        <v>28</v>
+        <v>269</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9036,12 +9240,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-5250-1469</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1196</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2816</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1910693072</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910693072</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jggy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="Q3" t="n">
-        <v>235</v>
+        <v>297</v>
       </c>
       <c r="R3" t="n">
-        <v>322</v>
+        <v>392</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>팀웨일 트레이닝 미아</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>junggyo777@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1417-7120</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team_whale_mia</t>
+          <t>https://blog.naver.com/ssdaw1234</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="R4" t="n">
-        <v>239</v>
+        <v>117</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1430890119</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430890119</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -845,29 +841,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>070-4535-3463</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43knh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4549</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1205</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5754</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>1779765773</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/1779765773</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,39 +940,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v4ny</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1814</v>
+        <v>1938</v>
       </c>
       <c r="Q6" t="n">
-        <v>1185</v>
+        <v>828</v>
       </c>
       <c r="R6" t="n">
-        <v>2999</v>
+        <v>2766</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,30 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M스피닝 강사 교육</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>m_spinning@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1338-9618</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 157 203호</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.mspinning.co.kr/</t>
+          <t>https://blog.naver.com/spoany87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1084,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc215t</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1103,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>87</v>
+        <v>1465</v>
       </c>
       <c r="Q7" t="n">
-        <v>193</v>
+        <v>1729</v>
       </c>
       <c r="R7" t="n">
-        <v>280</v>
+        <v>3194</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>31222668</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31222668</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,35 +1128,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1354-5063</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1178,17 +1170,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wy43x6v</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1197,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>91</v>
+        <v>351</v>
       </c>
       <c r="Q8" t="n">
-        <v>161</v>
+        <v>617</v>
       </c>
       <c r="R8" t="n">
-        <v>252</v>
+        <v>968</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1234,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>배용덕헬스</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nicenet@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-980-2004</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로46길 15</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1266,12 +1254,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1287,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2661</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>4789</v>
       </c>
       <c r="R9" t="n">
-        <v>13</v>
+        <v>7450</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13158296</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13158296</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,24 +1316,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>0507-1369-2202</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1370,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqzk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1385,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>518</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>660</v>
+        <v>11</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1426,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>삼각산 헬스타운</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-997-2636</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1458,12 +1442,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1474,22 +1458,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38</v>
+        <v>226</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>423</v>
       </c>
       <c r="R11" t="n">
-        <v>54</v>
+        <v>649</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>18612423</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18612423</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1515,29 +1499,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>97_cosat@naver.com</t>
-        </is>
-      </c>
+          <t>배용덕헬스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>02-980-2004</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 솔매로46길 15</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1562,14 +1542,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa2rxwt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1577,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="R12" t="n">
-        <v>182</v>
+        <v>13</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1596,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>13158296</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/13158296</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1618,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>커브스 수유클럽</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02-997-7330</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1650,24 +1626,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4egpq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1679,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="R13" t="n">
-        <v>50</v>
+        <v>305</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1694,12 +1666,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>36906152</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36906152</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1716,34 +1688,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1753,7 +1725,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1764,7 +1736,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1773,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>321</v>
+        <v>1085</v>
       </c>
       <c r="Q14" t="n">
-        <v>581</v>
+        <v>874</v>
       </c>
       <c r="R14" t="n">
-        <v>902</v>
+        <v>1959</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1788,12 +1760,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1805,29 +1777,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>070-4535-0883</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1852,32 +1824,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41vr7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1886,12 +1854,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>1476244634</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/1476244634</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1908,33 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>크로스핏FA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>fa_sport@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>02-990-1317</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>http://www.fasports.kr/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1969,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1145</v>
+        <v>239</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="R16" t="n">
-        <v>1186</v>
+        <v>345</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1984,12 +1948,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1623128626</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1623128626</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2006,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/h9a1n94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2038,12 +2002,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2059,17 +2023,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="Q17" t="n">
-        <v>202</v>
+        <v>335</v>
       </c>
       <c r="R17" t="n">
-        <v>212</v>
+        <v>450</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2078,12 +2042,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2100,34 +2064,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym-suyu</t>
+          <t>http://pf.kakao.com/_QERxeG</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2137,7 +2101,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2148,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2157,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>51</v>
+        <v>462</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="R18" t="n">
-        <v>51</v>
+        <v>1257</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2172,12 +2136,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2194,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sd670</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2226,24 +2190,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sncb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2255,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="Q19" t="n">
-        <v>320</v>
+        <v>236</v>
       </c>
       <c r="R19" t="n">
-        <v>423</v>
+        <v>323</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2270,12 +2230,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2292,29 +2252,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>미아동헬스장</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>uckyfycmko336@naver.com</t>
+          <t>uptfitness@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1380-1962</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 도봉로61길 46</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2324,7 +2280,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2345,17 +2301,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2364,12 +2320,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>18603866</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/18603866</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2386,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>팀웨일 트레이닝 미아</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ddt341@naver.com</t>
+          <t>junggyo777@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>0507-1417-7120</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 솔샘로 330 솔샘빌딩 4층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/team_whale_mia</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2418,7 +2374,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2443,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="R21" t="n">
-        <v>57</v>
+        <v>239</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2458,12 +2414,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>1430890119</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/1430890119</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2480,29 +2436,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2512,12 +2468,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2537,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>689</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="R22" t="n">
-        <v>10</v>
+        <v>1417</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2552,12 +2508,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2569,34 +2525,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>커브스 수유클럽</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>haon8312@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>070-4535-0883</t>
+          <t>02-997-7330</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로 323 3층 301호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://cafe.naver.com/curves</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2606,12 +2562,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2627,17 +2583,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2646,12 +2602,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1476244634</t>
+          <t>36906152</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1476244634</t>
+          <t>https://m.place.naver.com/place/36906152</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2668,39 +2624,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>SK북한산시티 헬스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>tjdghksfl20@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>02-987-0111</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 솔샘로 174</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2721,17 +2677,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1718</v>
+        <v>40</v>
       </c>
       <c r="Q24" t="n">
-        <v>398</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>2116</v>
+        <v>44</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2740,12 +2696,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>1259645750</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/1259645750</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2762,29 +2718,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2794,7 +2750,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2804,17 +2760,13 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40kte</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2823,13 +2775,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2749</v>
+        <v>321</v>
       </c>
       <c r="Q25" t="n">
-        <v>2345</v>
+        <v>581</v>
       </c>
       <c r="R25" t="n">
-        <v>5094</v>
+        <v>902</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2838,12 +2790,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2860,29 +2812,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2892,7 +2844,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2902,14 +2854,10 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rzh6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2921,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>623</v>
+        <v>1719</v>
       </c>
       <c r="Q26" t="n">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="R26" t="n">
-        <v>962</v>
+        <v>2117</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2936,12 +2884,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2953,34 +2901,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2990,27 +2938,23 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwrhsu4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3019,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q27" t="n">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="R27" t="n">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3034,12 +2978,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3056,39 +3000,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제이짐 휘트니스 4.19점</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>herricane@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02-999-9905</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 516 3,4층</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3098,32 +3042,28 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w481k9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>206</v>
+        <v>824</v>
       </c>
       <c r="Q28" t="n">
-        <v>198</v>
+        <v>559</v>
       </c>
       <c r="R28" t="n">
-        <v>404</v>
+        <v>1383</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3132,12 +3072,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>37174895</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37174895</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3154,29 +3094,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3186,7 +3126,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3196,14 +3136,10 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e814</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>X</t>
@@ -3215,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2659</v>
+        <v>695</v>
       </c>
       <c r="Q29" t="n">
-        <v>4787</v>
+        <v>145</v>
       </c>
       <c r="R29" t="n">
-        <v>7446</v>
+        <v>840</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3230,12 +3166,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3247,29 +3183,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>더블플러스휘트니스클럽</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3294,32 +3230,28 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w405s2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
-        <v>584</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>814</v>
+        <v>13</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3328,12 +3260,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3350,29 +3282,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>pressgym@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jjfit_7707</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3382,7 +3314,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3392,14 +3324,10 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5i8bi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3411,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>236</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>281</v>
+        <v>10</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3426,12 +3354,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3448,29 +3376,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany52</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3480,12 +3408,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3501,17 +3429,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>2752</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>2349</v>
       </c>
       <c r="R32" t="n">
-        <v>13</v>
+        <v>5101</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3520,12 +3448,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3542,29 +3470,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>짐초이 헬스&amp;PT 수유역점</t>
+          <t>제이짐 휘트니스 4.19점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gymchoi@naver.com</t>
+          <t>herricane@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1321-8296</t>
+          <t>02-999-9905</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+          <t>서울특별시 강북구 삼양로 516 3,4층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://blog.naver.com/herricane</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3574,24 +3502,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43zk4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>X</t>
@@ -3599,17 +3523,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="Q33" t="n">
-        <v>346</v>
+        <v>198</v>
       </c>
       <c r="R33" t="n">
-        <v>694</v>
+        <v>404</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3618,12 +3542,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1548872331</t>
+          <t>37174895</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548872331</t>
+          <t>https://m.place.naver.com/place/37174895</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3635,29 +3559,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>휘트니스클럽</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>io15io15@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>02-986-0188</t>
+          <t>070-5250-1469</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 39</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3700,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3712,12 +3632,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1185468645</t>
+          <t>1910693072</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185468645</t>
+          <t>https://m.place.naver.com/place/1910693072</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3734,24 +3654,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>휘트니스클럽</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>io15io15@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>02-986-0188</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 숭인로 39</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3776,14 +3696,10 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wy486uk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3791,17 +3707,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>728</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1417</v>
+        <v>3</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3810,12 +3726,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1185468645</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1185468645</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3832,29 +3748,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>https://blog.naver.com/blueskirt0704</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3869,7 +3785,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3889,13 +3805,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="Q36" t="n">
-        <v>219</v>
+        <v>520</v>
       </c>
       <c r="R36" t="n">
-        <v>344</v>
+        <v>662</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3904,12 +3820,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3921,34 +3837,30 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ssdaw1234@naver.com</t>
-        </is>
-      </c>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>070-4535-0870</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssdaw1234</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3958,12 +3870,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3979,17 +3891,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3998,12 +3910,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>1865696490</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/1865696490</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4020,29 +3932,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>419gym</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hegardengym_suyu-@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1433-5131</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4052,24 +3964,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49479</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -4081,13 +3989,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>37</v>
+        <v>4549</v>
       </c>
       <c r="Q38" t="n">
-        <v>56</v>
+        <v>1205</v>
       </c>
       <c r="R38" t="n">
-        <v>93</v>
+        <v>5754</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4096,12 +4004,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1310458215</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310458215</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4118,34 +4026,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>크로스핏FA</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>fa_sport@naver.com</t>
+          <t>codelegend@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02-990-1317</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 403 , 지하1층(수유동, 태일빌딩)</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.fasports.kr/</t>
+          <t>https://www.instagram.com/pressgym___</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4155,7 +4063,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4166,7 +4074,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4175,13 +4083,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q39" t="n">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="R39" t="n">
-        <v>345</v>
+        <v>281</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4190,12 +4098,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1623128626</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623128626</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4212,29 +4120,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4244,24 +4152,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yudn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>O</t>
@@ -4273,13 +4177,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>462</v>
+        <v>25</v>
       </c>
       <c r="Q40" t="n">
-        <v>795</v>
+        <v>45</v>
       </c>
       <c r="R40" t="n">
-        <v>1257</v>
+        <v>70</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4288,12 +4192,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4310,25 +4214,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>미아동헬스장</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>uptfitness@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1370-4554</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로61길 46</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ask4554</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4338,12 +4246,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4363,13 +4271,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="R41" t="n">
-        <v>7</v>
+        <v>212</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4378,12 +4286,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>18603866</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18603866</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4400,29 +4308,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4432,24 +4340,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfi5my</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>X</t>
@@ -4461,13 +4365,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2264</v>
+        <v>54</v>
       </c>
       <c r="Q42" t="n">
-        <v>1435</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3699</v>
+        <v>54</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4476,12 +4380,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4498,29 +4402,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4530,7 +4434,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4540,17 +4444,13 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wellmvw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4559,13 +4459,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>823</v>
+        <v>1339</v>
       </c>
       <c r="Q43" t="n">
-        <v>559</v>
+        <v>884</v>
       </c>
       <c r="R43" t="n">
-        <v>1382</v>
+        <v>2223</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4574,12 +4474,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4591,34 +4491,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070-4535-0870</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/trend_hd4</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4628,12 +4528,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4649,17 +4549,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2268</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1436</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3704</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4668,12 +4568,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1865696490</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865696490</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4690,24 +4590,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>미아동주민자치위원회 헬스장</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>la-lune@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1301-8244</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4732,14 +4628,10 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdf2zxw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4751,13 +4643,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="Q45" t="n">
-        <v>211</v>
+        <v>7</v>
       </c>
       <c r="R45" t="n">
-        <v>310</v>
+        <v>14</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4766,12 +4658,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>1404617649</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/1404617649</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4788,44 +4680,48 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4836,22 +4732,22 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>10</v>
+        <v>1145</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="R46" t="n">
-        <v>11</v>
+        <v>1186</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4860,12 +4756,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4877,34 +4773,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4939,13 +4835,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1085</v>
+        <v>80</v>
       </c>
       <c r="Q47" t="n">
-        <v>874</v>
+        <v>104</v>
       </c>
       <c r="R47" t="n">
-        <v>1959</v>
+        <v>184</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4954,12 +4850,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4971,29 +4867,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>070-4535-8515</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5018,14 +4914,10 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mfvy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>X</t>
@@ -5033,17 +4925,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1196</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2816</v>
+        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5052,12 +4944,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>1239590728</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/1239590728</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5074,29 +4966,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>dietmode-@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dietmode-</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5106,12 +4998,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5127,17 +5019,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="Q49" t="n">
-        <v>335</v>
+        <v>211</v>
       </c>
       <c r="R49" t="n">
-        <v>450</v>
+        <v>310</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5146,12 +5038,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5168,29 +5060,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>크로스핏샤크</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>fatdogxp@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1386-8834</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nyh314</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5200,24 +5092,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wqdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>X</t>
@@ -5225,17 +5113,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>28</v>
+        <v>334</v>
       </c>
       <c r="Q50" t="n">
-        <v>211</v>
+        <v>365</v>
       </c>
       <c r="R50" t="n">
-        <v>239</v>
+        <v>699</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5244,12 +5132,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1209016130</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209016130</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5266,29 +5154,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5323,13 +5211,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>95</v>
+        <v>1290</v>
       </c>
       <c r="Q51" t="n">
-        <v>297</v>
+        <v>1953</v>
       </c>
       <c r="R51" t="n">
-        <v>392</v>
+        <v>3243</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5338,12 +5226,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5360,39 +5248,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5417,13 +5305,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>175</v>
+        <v>1816</v>
       </c>
       <c r="Q52" t="n">
-        <v>130</v>
+        <v>1185</v>
       </c>
       <c r="R52" t="n">
-        <v>305</v>
+        <v>3001</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5432,12 +5320,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5454,29 +5342,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1362-4534</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/f45suyu/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5486,7 +5370,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5496,17 +5380,13 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48ak4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5515,13 +5395,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>694</v>
+        <v>91</v>
       </c>
       <c r="Q53" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="R53" t="n">
-        <v>839</v>
+        <v>252</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5530,12 +5410,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5552,29 +5432,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NH FITNESS CLUB</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jjoseohyun@naver.com</t>
+          <t>bum903@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>02-903-7009</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bum903</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5584,12 +5464,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5605,17 +5485,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R54" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5624,12 +5504,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>37438317</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438317</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5646,29 +5526,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>가인헬스클럽</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1419-2268</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 424 3층</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5678,7 +5558,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5699,17 +5579,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="R55" t="n">
-        <v>10</v>
+        <v>169</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5718,12 +5598,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1434719389</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434719389</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5740,29 +5620,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>가인헬스클럽</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>0507-1419-2268</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 삼양로 424 3층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5772,7 +5652,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5793,17 +5673,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>243</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
-        <v>359</v>
+        <v>10</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5812,12 +5692,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1434719389</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1434719389</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5829,49 +5709,45 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>인터넷상거래</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>M스피닝 강사 교육</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>m_spinning@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>070-5250-6614</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로 157 203호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.mspinning.co.kr/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5887,17 +5763,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5906,12 +5782,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1349373253</t>
+          <t>31222668</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349373253</t>
+          <t>https://m.place.naver.com/place/31222668</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5923,34 +5799,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>NH FITNESS CLUB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>thebarunpt@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>02-903-7009</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 도봉로 373 농협쌍문동지점</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5960,24 +5836,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7sz75u</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
@@ -5985,17 +5857,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="Q58" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6004,12 +5876,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>37438317</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/37438317</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6021,7 +5893,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>카달로그인쇄</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6037,13 +5909,13 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>070-4535-8515</t>
+          <t>070-5250-6614</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6098,12 +5970,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1239590728</t>
+          <t>1349373253</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239590728</t>
+          <t>https://m.place.naver.com/place/1349373253</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6120,29 +5992,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>헬스&amp;PT 건짐 수유역점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>0507-1459-7599</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6157,7 +6029,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6177,13 +6049,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1289</v>
+        <v>426</v>
       </c>
       <c r="Q60" t="n">
-        <v>1951</v>
+        <v>222</v>
       </c>
       <c r="R60" t="n">
-        <v>3240</v>
+        <v>648</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6192,12 +6064,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6214,29 +6086,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>크로스핏샤크</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>somedayday00@naver.com</t>
+          <t>fatdogxp@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1386-8834</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 성북구 장월로38길 4 . 지하1층(장위동, 타워39)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/crossfitshark_jangwi</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6246,7 +6118,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6256,14 +6128,10 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpw1lb4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>X</t>
@@ -6271,17 +6139,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="Q61" t="n">
-        <v>365</v>
+        <v>211</v>
       </c>
       <c r="R61" t="n">
-        <v>699</v>
+        <v>239</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6290,12 +6158,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1209016130</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1209016130</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6312,20 +6180,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>미아동주민자치위원회 헬스장</t>
+          <t>419gym</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>la-lune@naver.com</t>
+          <t>hegardengym_suyu-@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1433-5131</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로49길 14 1층 미아동주민센터</t>
+          <t>서울특별시 강북구 삼양로 522 2f, b1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6350,10 +6222,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49479</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6361,17 +6237,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="Q62" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="R62" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6380,12 +6256,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1404617649</t>
+          <t>1310458215</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404617649</t>
+          <t>https://m.place.naver.com/place/1310458215</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6402,24 +6278,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>삼각산 헬스타운</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>02-997-2636</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 삼양로 441 5층 삼각산헬스타운</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6444,14 +6320,10 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcha8q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6459,17 +6331,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1334</v>
+        <v>38</v>
       </c>
       <c r="Q63" t="n">
-        <v>884</v>
+        <v>16</v>
       </c>
       <c r="R63" t="n">
-        <v>2218</v>
+        <v>54</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6478,12 +6350,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>18612423</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/18612423</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6500,39 +6372,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>프리원핏 수유점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1301-1607</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 노해로 102 지하1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6542,10 +6414,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9qn</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>X</t>
@@ -6557,13 +6433,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>351</v>
+        <v>114</v>
       </c>
       <c r="Q64" t="n">
-        <v>616</v>
+        <v>5</v>
       </c>
       <c r="R64" t="n">
-        <v>967</v>
+        <v>119</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6572,12 +6448,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>1611482879</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/1611482879</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6589,29 +6465,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bizhows@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>070-4535-3463</t>
+          <t>0507-1351-2438</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6636,10 +6512,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rzh6</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>X</t>
@@ -6647,17 +6527,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6666,12 +6546,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1779765773</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779765773</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6688,24 +6568,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6735,12 +6615,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t1ci</t>
+          <t>https://talk.naver.com/ct/w405s2</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6749,13 +6629,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="Q66" t="n">
-        <v>91</v>
+        <v>584</v>
       </c>
       <c r="R66" t="n">
-        <v>177</v>
+        <v>814</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6764,12 +6644,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6786,24 +6666,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>프리원핏 수유점</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1301-1607</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 102 지하1층</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6833,7 +6713,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f9qn</t>
+          <t>https://talk.naver.com/ct/w3azy9n</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6847,13 +6727,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>220</v>
       </c>
       <c r="R67" t="n">
-        <v>119</v>
+        <v>346</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6862,12 +6742,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1611482879</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611482879</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6884,24 +6764,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6931,7 +6811,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sak0</t>
+          <t>https://talk.naver.com/ct/w4toem</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6945,13 +6825,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1464</v>
+        <v>116</v>
       </c>
       <c r="Q68" t="n">
-        <v>1729</v>
+        <v>243</v>
       </c>
       <c r="R68" t="n">
-        <v>3193</v>
+        <v>359</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6960,12 +6840,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6977,34 +6857,34 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>acrogym1@naver.com</t>
+          <t>honeymusclegym@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acrogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7014,20 +6894,24 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t1ci</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>X</t>
@@ -7039,13 +6923,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1936</v>
+        <v>86</v>
       </c>
       <c r="Q69" t="n">
-        <v>828</v>
+        <v>91</v>
       </c>
       <c r="R69" t="n">
-        <v>2764</v>
+        <v>177</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7054,12 +6938,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7076,24 +6960,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 건짐 수유역점</t>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>gymchoi@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1321-8296</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7123,7 +7007,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we2yppk</t>
+          <t>https://talk.naver.com/ct/w43zk4</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7137,13 +7021,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>426</v>
+        <v>348</v>
       </c>
       <c r="Q70" t="n">
-        <v>221</v>
+        <v>346</v>
       </c>
       <c r="R70" t="n">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7152,12 +7036,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>1548872331</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/1548872331</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7174,29 +7058,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SK북한산시티 헬스</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>tjdghksfl20@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>02-987-0111</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 174</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7206,7 +7090,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7227,17 +7111,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>320</v>
       </c>
       <c r="R71" t="n">
-        <v>44</v>
+        <v>423</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7246,12 +7130,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1259645750</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259645750</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7268,34 +7152,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>buckle1234@naver.com</t>
-        </is>
-      </c>
+          <t>디와이비퍼포먼스트레이닝</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1436-2922</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>https://www.instagram.com/dyb_performance</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7316,7 +7196,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7325,13 +7205,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>637</v>
+        <v>57</v>
       </c>
       <c r="Q72" t="n">
-        <v>700</v>
+        <v>58</v>
       </c>
       <c r="R72" t="n">
-        <v>1337</v>
+        <v>115</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7340,12 +7220,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7362,56 +7242,52 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>winnnig@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>https://www.instagram.com/sunghyunle2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lqb7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
@@ -7423,13 +7299,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="Q73" t="n">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="R73" t="n">
-        <v>244</v>
+        <v>61</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7438,12 +7314,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7460,24 +7336,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>핏라인점핑</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>shinycaptain@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1467-8213</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7502,14 +7374,10 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdgwqtj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7517,17 +7385,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>550</v>
+        <v>41</v>
       </c>
       <c r="R74" t="n">
-        <v>712</v>
+        <v>42</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7536,12 +7404,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>1880264222</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/1880264222</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7580,7 +7448,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7590,7 +7458,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7600,14 +7468,10 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7t3tx8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7656,29 +7520,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1404-1363</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7688,7 +7552,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7698,14 +7562,10 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wu8v0g9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7717,13 +7577,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>29</v>
+        <v>532</v>
       </c>
       <c r="Q76" t="n">
-        <v>47</v>
+        <v>2236</v>
       </c>
       <c r="R76" t="n">
-        <v>76</v>
+        <v>2768</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7732,12 +7592,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7754,29 +7614,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1404-1363</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hypedobby</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7786,7 +7646,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7811,13 +7671,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>532</v>
+        <v>42</v>
       </c>
       <c r="Q77" t="n">
-        <v>2236</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2768</v>
+        <v>42</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7826,12 +7686,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7848,25 +7708,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1458-1884</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7876,7 +7740,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7897,17 +7761,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q78" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="R78" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7916,12 +7780,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7938,29 +7802,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1437-5900</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7970,24 +7830,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zcrh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -7995,17 +7851,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q79" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="R79" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -8014,12 +7870,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8036,29 +7892,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0507-1382-4849</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8068,24 +7920,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zmep</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>X</t>
@@ -8097,13 +7945,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="Q80" t="n">
-        <v>501</v>
+        <v>1343</v>
       </c>
       <c r="R80" t="n">
-        <v>694</v>
+        <v>1591</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8112,12 +7960,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8134,29 +7982,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8187,17 +8035,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="Q81" t="n">
-        <v>1303</v>
+        <v>180</v>
       </c>
       <c r="R81" t="n">
-        <v>1381</v>
+        <v>269</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8206,12 +8054,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8250,7 +8098,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/xtmxjax</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8260,12 +8108,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8322,29 +8170,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://smartstore.naver.com/runandlift</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8379,13 +8227,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Q83" t="n">
-        <v>220</v>
+        <v>501</v>
       </c>
       <c r="R83" t="n">
-        <v>298</v>
+        <v>695</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8394,12 +8242,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8416,29 +8264,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1436-2922</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_performance</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8453,7 +8301,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8473,13 +8321,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="Q84" t="n">
-        <v>59</v>
+        <v>553</v>
       </c>
       <c r="R84" t="n">
-        <v>116</v>
+        <v>715</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8488,12 +8336,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8510,25 +8358,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1309-1030</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8538,24 +8390,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jtey</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>X</t>
@@ -8567,13 +8415,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="Q85" t="n">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="R85" t="n">
-        <v>21</v>
+        <v>521</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8582,12 +8430,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8604,29 +8452,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1404-1390</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wellcare093</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8636,12 +8484,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8652,22 +8500,22 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Q86" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R86" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8676,12 +8524,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8698,29 +8546,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0507-1301-9491</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8730,24 +8574,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxl9x94</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>X</t>
@@ -8759,13 +8599,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R87" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8774,12 +8614,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8796,34 +8636,34 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>https://pf.kakao.com/_ExmdAX</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8833,7 +8673,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8844,22 +8684,22 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Q88" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R88" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8868,12 +8708,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8890,25 +8730,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>핏라인점핑</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>shinycaptain@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1362-0934</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 217-1 B1층</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8918,12 +8762,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8939,17 +8783,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="Q89" t="n">
-        <v>41</v>
+        <v>1303</v>
       </c>
       <c r="R89" t="n">
-        <v>42</v>
+        <v>1381</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8958,12 +8802,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1880264222</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880264222</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8980,24 +8824,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1309-1030</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9022,14 +8866,10 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnugfn3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
@@ -9041,13 +8881,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="Q90" t="n">
-        <v>375</v>
+        <v>220</v>
       </c>
       <c r="R90" t="n">
-        <v>521</v>
+        <v>298</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -9056,12 +8896,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -9078,25 +8918,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1485-1323</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9106,23 +8950,27 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4utrl</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9131,13 +8979,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>248</v>
+        <v>637</v>
       </c>
       <c r="Q91" t="n">
-        <v>1343</v>
+        <v>700</v>
       </c>
       <c r="R91" t="n">
-        <v>1591</v>
+        <v>1337</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9146,12 +8994,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9168,39 +9016,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>winnnig@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9210,10 +9058,14 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lqb7</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr">
         <is>
           <t>X</t>
@@ -9221,17 +9073,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Q92" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="R92" t="n">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9240,12 +9092,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">

--- a/naver-place-crawler/results_health/강북_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강북_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48ak4</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1620</v>
+        <v>697</v>
       </c>
       <c r="Q2" t="n">
-        <v>1196</v>
+        <v>145</v>
       </c>
       <c r="R2" t="n">
-        <v>2816</v>
+        <v>842</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc0yw3</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>95</v>
+        <v>1939</v>
       </c>
       <c r="Q3" t="n">
-        <v>297</v>
+        <v>828</v>
       </c>
       <c r="R3" t="n">
-        <v>392</v>
+        <v>2767</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http